--- a/IAG Spatially Resolved Atlas/Data/Values_SPA.xlsx
+++ b/IAG Spatially Resolved Atlas/Data/Values_SPA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Emitted wavelength</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>Bisector slope</t>
-  </si>
-  <si>
-    <t>Blueshift</t>
   </si>
   <si>
     <t>Line Depth</t>
@@ -395,10 +392,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H479"/>
+  <dimension ref="A1:G479"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,11 +417,8 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>4202.1078</v>
       </c>
@@ -441,16 +435,13 @@
         <v>7956737024.65556</v>
       </c>
       <c r="F2">
-        <v>-40214313.45838111</v>
+        <v>-563.6736782736464</v>
       </c>
       <c r="G2">
-        <v>420.9257797480747</v>
-      </c>
-      <c r="H2">
         <v>0.8797386591621212</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>4203.937</v>
       </c>
@@ -467,16 +458,13 @@
         <v>13477870288.37663</v>
       </c>
       <c r="F3">
-        <v>-497932.227819716</v>
+        <v>-6.982419690095779</v>
       </c>
       <c r="G3">
-        <v>149.7558507049375</v>
-      </c>
-      <c r="H3">
         <v>0.748712696178348</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>4206.7233</v>
       </c>
@@ -493,16 +481,13 @@
         <v>9554437129.977875</v>
       </c>
       <c r="F4">
-        <v>-23216491.96908789</v>
+        <v>-325.7768687928219</v>
       </c>
       <c r="G4">
-        <v>277.9337985658759</v>
-      </c>
-      <c r="H4">
         <v>0.8303536874228343</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4208.3123</v>
       </c>
@@ -519,16 +504,13 @@
         <v>10080688837.69621</v>
       </c>
       <c r="F5">
-        <v>-15394828.49956845</v>
+        <v>-216.1038970727488</v>
       </c>
       <c r="G5">
-        <v>334.8193889610315</v>
-      </c>
-      <c r="H5">
         <v>0.8880424500591345</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4209.7896</v>
       </c>
@@ -545,16 +527,13 @@
         <v>7800362735.570836</v>
       </c>
       <c r="F6">
-        <v>-80958934.16898233</v>
+        <v>-1136.855222410316</v>
       </c>
       <c r="G6">
-        <v>477.1282319023201</v>
-      </c>
-      <c r="H6">
         <v>0.8753567856859491</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>4214.8343</v>
       </c>
@@ -571,16 +550,13 @@
         <v>8844417547.961292</v>
       </c>
       <c r="F7">
-        <v>-52201197.65040627</v>
+        <v>-733.906864614707</v>
       </c>
       <c r="G7">
-        <v>469.4443676410949</v>
-      </c>
-      <c r="H7">
         <v>0.8858486581333692</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>4217.3714</v>
       </c>
@@ -597,16 +573,13 @@
         <v>2168686909.108348</v>
       </c>
       <c r="F8">
-        <v>-761061811.9829437</v>
+        <v>-10706.36624888336</v>
       </c>
       <c r="G8">
-        <v>703.7429367153335</v>
-      </c>
-      <c r="H8">
         <v>0.9180377149081295</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>4221.5304</v>
       </c>
@@ -623,16 +596,13 @@
         <v>9873218364.839312</v>
       </c>
       <c r="F9">
-        <v>-27005143.60264176</v>
+        <v>-380.2736685329782</v>
       </c>
       <c r="G9">
-        <v>376.3800984726426</v>
-      </c>
-      <c r="H9">
         <v>0.8679790723885138</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>4223.4023</v>
       </c>
@@ -649,16 +619,13 @@
         <v>3110392109.412148</v>
       </c>
       <c r="F10">
-        <v>-88779112.87913874</v>
+        <v>-1250.700583010646</v>
       </c>
       <c r="G10">
-        <v>553.6723727340368</v>
-      </c>
-      <c r="H10">
         <v>0.928980535650502</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>4233.9182</v>
       </c>
@@ -675,16 +642,13 @@
         <v>17322704975.65882</v>
       </c>
       <c r="F11">
-        <v>-1189420.552938995</v>
+        <v>-16.79800363048833</v>
       </c>
       <c r="G11">
-        <v>325.713734087069</v>
-      </c>
-      <c r="H11">
         <v>0.8182692719924693</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>4234.795</v>
       </c>
@@ -701,16 +665,13 @@
         <v>1950419076.342742</v>
       </c>
       <c r="F12">
-        <v>-515383756.1041059</v>
+        <v>-7280.206824964856</v>
       </c>
       <c r="G12">
-        <v>899.066948116175</v>
-      </c>
-      <c r="H12">
         <v>0.9346851758633459</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>4239.2172</v>
       </c>
@@ -727,16 +688,13 @@
         <v>5862452038.846129</v>
       </c>
       <c r="F13">
-        <v>-82780743.36280161</v>
+        <v>-1170.563323694117</v>
       </c>
       <c r="G13">
-        <v>431.3848305979838</v>
-      </c>
-      <c r="H13">
         <v>0.8855667768332544</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>4240.0035</v>
       </c>
@@ -753,16 +711,13 @@
         <v>4504918476.414181</v>
       </c>
       <c r="F14">
-        <v>-106660733.4159998</v>
+        <v>-1508.519498113904</v>
       </c>
       <c r="G14">
-        <v>586.8573933102427</v>
-      </c>
-      <c r="H14">
         <v>0.920470379930762</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>4241.0415</v>
       </c>
@@ -779,16 +734,13 @@
         <v>6799948284.82059</v>
       </c>
       <c r="F15">
-        <v>-25712770.43708288</v>
+        <v>-363.7485110117343</v>
       </c>
       <c r="G15">
-        <v>367.5797045184399</v>
-      </c>
-      <c r="H15">
         <v>0.8801152740960432</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>4259.5145</v>
       </c>
@@ -805,16 +757,13 @@
         <v>9292847921.861954</v>
       </c>
       <c r="F16">
-        <v>-46281100.63265605</v>
+        <v>-657.572816448646</v>
       </c>
       <c r="G16">
-        <v>534.9019661149667</v>
-      </c>
-      <c r="H16">
         <v>0.8929743788649498</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>4260.1505</v>
       </c>
@@ -831,16 +780,13 @@
         <v>14796067879.2144</v>
       </c>
       <c r="F17">
-        <v>538532.760435399</v>
+        <v>7.652734601238616</v>
       </c>
       <c r="G17">
-        <v>197.0397248583244</v>
-      </c>
-      <c r="H17">
         <v>0.7137097939913537</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>4283.6079</v>
       </c>
@@ -857,16 +803,13 @@
         <v>2262845896.510838</v>
       </c>
       <c r="F18">
-        <v>-270414515.6100931</v>
+        <v>-3863.847720292953</v>
       </c>
       <c r="G18">
-        <v>685.8625151652143</v>
-      </c>
-      <c r="H18">
         <v>0.9365026955216839</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>4289.3523</v>
       </c>
@@ -883,16 +826,13 @@
         <v>12584837079.76077</v>
       </c>
       <c r="F19">
-        <v>-7624853.019028246</v>
+        <v>-109.0945278921591</v>
       </c>
       <c r="G19">
-        <v>328.4935473026585</v>
-      </c>
-      <c r="H19">
         <v>0.821564853644382</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>4292.671</v>
       </c>
@@ -909,16 +849,13 @@
         <v>6985302679.552778</v>
       </c>
       <c r="F20">
-        <v>-99110097.75766833</v>
+        <v>-1419.141520002408</v>
       </c>
       <c r="G20">
-        <v>621.5600673992133</v>
-      </c>
-      <c r="H20">
         <v>0.9077425993669637</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>4327.9699</v>
       </c>
@@ -935,16 +872,13 @@
         <v>12428445947.34683</v>
       </c>
       <c r="F21">
-        <v>-6857236.069430495</v>
+        <v>-98.99495467562625</v>
       </c>
       <c r="G21">
-        <v>297.8550218957526</v>
-      </c>
-      <c r="H21">
         <v>0.7826534793196006</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>4338.2657</v>
       </c>
@@ -961,16 +895,13 @@
         <v>2714857221.02059</v>
       </c>
       <c r="F22">
-        <v>-84448693.85646543</v>
+        <v>-1222.050440416712</v>
       </c>
       <c r="G22">
-        <v>518.2816338250062</v>
-      </c>
-      <c r="H22">
         <v>0.9162888007074663</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>4344.9186</v>
       </c>
@@ -987,16 +918,13 @@
         <v>11218312188.73093</v>
       </c>
       <c r="F23">
-        <v>-4392391.498146226</v>
+        <v>-63.65937254707704</v>
       </c>
       <c r="G23">
-        <v>255.2941025872096</v>
-      </c>
-      <c r="H23">
         <v>0.7658101840076471</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>4347.7745</v>
       </c>
@@ -1013,16 +941,13 @@
         <v>13576108409.71871</v>
       </c>
       <c r="F24">
-        <v>-2148172.59403784</v>
+        <v>-31.1541516255664</v>
       </c>
       <c r="G24">
-        <v>310.2888755791125</v>
-      </c>
-      <c r="H24">
         <v>0.7812443197215735</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>4369.1311</v>
       </c>
@@ -1039,16 +964,13 @@
         <v>10072293021.28594</v>
       </c>
       <c r="F25">
-        <v>-38269065.30384443</v>
+        <v>-557.7286112728519</v>
       </c>
       <c r="G25">
-        <v>480.3122538659831</v>
-      </c>
-      <c r="H25">
         <v>0.8729258774983479</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>4374.7896</v>
       </c>
@@ -1065,16 +987,13 @@
         <v>13896759643.66327</v>
       </c>
       <c r="F26">
-        <v>424467.5708547915</v>
+        <v>6.19414547538952</v>
       </c>
       <c r="G26">
-        <v>287.8146011330351</v>
-      </c>
-      <c r="H26">
         <v>0.7856366453126009</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>4389.1239</v>
       </c>
@@ -1091,16 +1010,13 @@
         <v>11957787337.2151</v>
       </c>
       <c r="F27">
-        <v>-10567769.55463233</v>
+        <v>-154.7180582771188</v>
       </c>
       <c r="G27">
-        <v>368.8388184345498</v>
-      </c>
-      <c r="H27">
         <v>0.8478080794798396</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>4389.6397</v>
       </c>
@@ -1117,16 +1033,13 @@
         <v>7048434815.893798</v>
       </c>
       <c r="F28">
-        <v>-55770388.05755068</v>
+        <v>-816.6059516800304</v>
       </c>
       <c r="G28">
-        <v>484.8977586902467</v>
-      </c>
-      <c r="H28">
         <v>0.8737166948479204</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>4431.433</v>
       </c>
@@ -1143,16 +1056,13 @@
         <v>13287093651.74801</v>
       </c>
       <c r="F29">
-        <v>-1035659.434521177</v>
+        <v>-15.3087905627032</v>
       </c>
       <c r="G29">
-        <v>297.6659728998812</v>
-      </c>
-      <c r="H29">
         <v>0.7604046814986062</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>4431.858</v>
       </c>
@@ -1169,16 +1079,13 @@
         <v>4705696418.273812</v>
       </c>
       <c r="F30">
-        <v>-129397095.5113791</v>
+        <v>-1912.892064733172</v>
       </c>
       <c r="G30">
-        <v>554.6879335489692</v>
-      </c>
-      <c r="H30">
         <v>0.8988192177254859</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>4433.8124</v>
       </c>
@@ -1195,16 +1102,13 @@
         <v>14167851680.4487</v>
       </c>
       <c r="F31">
-        <v>-246272.5144273958</v>
+        <v>-3.642276385088936</v>
       </c>
       <c r="G31">
-        <v>236.6526835544075</v>
-      </c>
-      <c r="H31">
         <v>0.6829994463580147</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>4435.0272</v>
       </c>
@@ -1221,16 +1125,13 @@
         <v>11958666208.79302</v>
       </c>
       <c r="F32">
-        <v>-8061245.307986243</v>
+        <v>-119.2554030867246</v>
       </c>
       <c r="G32">
-        <v>236.5878619838987</v>
-      </c>
-      <c r="H32">
         <v>0.8053268289373746</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>4439.5893</v>
       </c>
@@ -1247,16 +1148,13 @@
         <v>13642101914.55612</v>
       </c>
       <c r="F33">
-        <v>-1991934.486711669</v>
+        <v>-29.49832452612447</v>
       </c>
       <c r="G33">
-        <v>141.8068472985769</v>
-      </c>
-      <c r="H33">
         <v>0.6526839068247271</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>4443.5861</v>
       </c>
@@ -1273,16 +1171,13 @@
         <v>2621735379.924401</v>
       </c>
       <c r="F34">
-        <v>-145546264.1934322</v>
+        <v>-2157.321434358744</v>
       </c>
       <c r="G34">
-        <v>620.6902604093026</v>
-      </c>
-      <c r="H34">
         <v>0.9152122761649583</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>4444.0788</v>
       </c>
@@ -1299,16 +1194,13 @@
         <v>13827591816.74435</v>
       </c>
       <c r="F35">
-        <v>-6716945.087787445</v>
+        <v>-99.57107094072934</v>
       </c>
       <c r="G35">
-        <v>229.3600998066294</v>
-      </c>
-      <c r="H35">
         <v>0.7920486566736112</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>4446.7194</v>
       </c>
@@ -1325,16 +1217,13 @@
         <v>17348283551.68607</v>
       </c>
       <c r="F36">
-        <v>-592838.9650619169</v>
+        <v>-8.793386317852626</v>
       </c>
       <c r="G36">
-        <v>269.6751748805509</v>
-      </c>
-      <c r="H36">
         <v>0.6101842536439906</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>4448.3788</v>
       </c>
@@ -1351,16 +1240,13 @@
         <v>13289540051.79009</v>
       </c>
       <c r="F37">
-        <v>-5013157.461345589</v>
+        <v>-74.38626731828639</v>
       </c>
       <c r="G37">
-        <v>249.3564834071857</v>
-      </c>
-      <c r="H37">
         <v>0.8051857656071628</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>4451.5648</v>
       </c>
@@ -1377,16 +1263,13 @@
         <v>14601570838.37045</v>
       </c>
       <c r="F38">
-        <v>-3154399.450092184</v>
+        <v>-46.83915124418458</v>
       </c>
       <c r="G38">
-        <v>228.9743950366214</v>
-      </c>
-      <c r="H38">
         <v>0.7117458846616594</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4457.5765</v>
       </c>
@@ -1403,16 +1286,13 @@
         <v>14449574952.06922</v>
       </c>
       <c r="F39">
-        <v>1394598.579441746</v>
+        <v>20.73612784397644</v>
       </c>
       <c r="G39">
-        <v>235.3910478027842</v>
-      </c>
-      <c r="H39">
         <v>0.6915226629248759</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4459.3315</v>
       </c>
@@ -1429,16 +1309,13 @@
         <v>12837105993.8848</v>
       </c>
       <c r="F40">
-        <v>-4984721.372462008</v>
+        <v>-74.14644159221739</v>
       </c>
       <c r="G40">
-        <v>255.4668429945003</v>
-      </c>
-      <c r="H40">
         <v>0.7605743075641704</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4462.905</v>
       </c>
@@ -1455,16 +1332,13 @@
         <v>1967040775.459416</v>
       </c>
       <c r="F41">
-        <v>-912186642.4358728</v>
+        <v>-13579.43889608671</v>
       </c>
       <c r="G41">
-        <v>812.8088637041188</v>
-      </c>
-      <c r="H41">
         <v>0.9183434089122136</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4470.6298</v>
       </c>
@@ -1481,16 +1355,13 @@
         <v>5985793066.316721</v>
       </c>
       <c r="F42">
-        <v>-49027236.95077542</v>
+        <v>-731.1157878788216</v>
       </c>
       <c r="G42">
-        <v>509.6424402378982</v>
-      </c>
-      <c r="H42">
         <v>0.8867388899109457</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4481.3936</v>
       </c>
@@ -1507,16 +1378,13 @@
         <v>14025433369.75537</v>
       </c>
       <c r="F43">
-        <v>-2188950.757791318</v>
+        <v>-32.72117147004678</v>
       </c>
       <c r="G43">
-        <v>321.1063179710299</v>
-      </c>
-      <c r="H43">
         <v>0.7724106211931314</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4482.8668</v>
       </c>
@@ -1533,16 +1401,13 @@
         <v>13511155748.38366</v>
       </c>
       <c r="F44">
-        <v>-2447443.452583506</v>
+        <v>-36.59721688716164</v>
       </c>
       <c r="G44">
-        <v>180.5629461444882</v>
-      </c>
-      <c r="H44">
         <v>0.6858464231312844</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4485.478</v>
       </c>
@@ -1559,16 +1424,13 @@
         <v>8577062488.528451</v>
       </c>
       <c r="F45">
-        <v>-29578057.53464424</v>
+        <v>-442.545904631685</v>
       </c>
       <c r="G45">
-        <v>447.8027689461618</v>
-      </c>
-      <c r="H45">
         <v>0.8740867156031099</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4486.9341</v>
       </c>
@@ -1585,16 +1447,13 @@
         <v>11431087962.12382</v>
       </c>
       <c r="F46">
-        <v>-11447846.07574959</v>
+        <v>-171.3378456371489</v>
       </c>
       <c r="G46">
-        <v>367.4799945611327</v>
-      </c>
-      <c r="H46">
         <v>0.8208776845437709</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4490.9987</v>
       </c>
@@ -1611,16 +1470,13 @@
         <v>6321269143.175884</v>
       </c>
       <c r="F47">
-        <v>-48578654.12382686</v>
+        <v>-727.7269187193075</v>
       </c>
       <c r="G47">
-        <v>507.3309597821763</v>
-      </c>
-      <c r="H47">
         <v>0.9037056118213894</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>4495.8241</v>
       </c>
@@ -1637,16 +1493,13 @@
         <v>2158596263.951111</v>
       </c>
       <c r="F48">
-        <v>-292340117.9049614</v>
+        <v>-4384.074876136847</v>
       </c>
       <c r="G48">
-        <v>646.8195325669061</v>
-      </c>
-      <c r="H48">
         <v>0.9188458000498709</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>4503.8539</v>
       </c>
@@ -1663,16 +1516,13 @@
         <v>9824582634.745487</v>
       </c>
       <c r="F49">
-        <v>1464776.612733198</v>
+        <v>22.00570209751152</v>
       </c>
       <c r="G49">
-        <v>166.4088492987254</v>
-      </c>
-      <c r="H49">
         <v>0.3866008661109934</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>4518.7914</v>
       </c>
@@ -1689,16 +1539,13 @@
         <v>13831489249.60563</v>
       </c>
       <c r="F50">
-        <v>2243484.448526053</v>
+        <v>33.81621980186024</v>
       </c>
       <c r="G50">
-        <v>278.6427193197707</v>
-      </c>
-      <c r="H50">
         <v>0.7703387181486956</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>4526.4058</v>
       </c>
@@ -1715,16 +1562,13 @@
         <v>6557251170.669719</v>
       </c>
       <c r="F51">
-        <v>-71844273.92340891</v>
+        <v>-1084.740236112303</v>
       </c>
       <c r="G51">
-        <v>556.3479631289255</v>
-      </c>
-      <c r="H51">
         <v>0.8754819374460251</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>4532.4187</v>
       </c>
@@ -1741,16 +1585,13 @@
         <v>3595884838.794737</v>
       </c>
       <c r="F52">
-        <v>-282967498.2285971</v>
+        <v>-4278.059812738826</v>
       </c>
       <c r="G52">
-        <v>674.6691499345801</v>
-      </c>
-      <c r="H52">
         <v>0.9035775262236376</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>4576</v>
       </c>
@@ -1767,16 +1608,13 @@
         <v>15579381118.19539</v>
       </c>
       <c r="F53">
-        <v>-2152003.175308941</v>
+        <v>-32.84797562661411</v>
       </c>
       <c r="G53">
-        <v>268.6077530148755</v>
-      </c>
-      <c r="H53">
         <v>0.7350099557681258</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>4588.4129</v>
       </c>
@@ -1793,16 +1631,13 @@
         <v>14756574346.82716</v>
       </c>
       <c r="F54">
-        <v>-1763352.050611818</v>
+        <v>-26.98864915407876</v>
       </c>
       <c r="G54">
-        <v>228.6789846124696</v>
-      </c>
-      <c r="H54">
         <v>0.6784707176612326</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>4599.4054</v>
       </c>
@@ -1819,16 +1654,13 @@
         <v>11778708582.58004</v>
       </c>
       <c r="F55">
-        <v>-6233394.524593283</v>
+        <v>-95.63262879146983</v>
       </c>
       <c r="G55">
-        <v>338.9396337718985</v>
-      </c>
-      <c r="H55">
         <v>0.8090185615322717</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>4604.2305</v>
       </c>
@@ -1845,16 +1677,13 @@
         <v>4036148238.048314</v>
       </c>
       <c r="F56">
-        <v>-231239021.3660047</v>
+        <v>-3551.39066482263</v>
       </c>
       <c r="G56">
-        <v>670.6576304898763</v>
-      </c>
-      <c r="H56">
         <v>0.8973216937202337</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>4620.5818</v>
       </c>
@@ -1871,16 +1700,13 @@
         <v>10741087789.72659</v>
       </c>
       <c r="F57">
-        <v>-13844897.4028348</v>
+        <v>-213.3861687467474</v>
       </c>
       <c r="G57">
-        <v>389.2918307329556</v>
-      </c>
-      <c r="H57">
         <v>0.8277727781888289</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>4626.3406</v>
       </c>
@@ -1897,16 +1723,13 @@
         <v>9335336029.122759</v>
       </c>
       <c r="F58">
-        <v>-18739299.00296587</v>
+        <v>-289.1817423447787</v>
       </c>
       <c r="G58">
-        <v>434.1680914004986</v>
-      </c>
-      <c r="H58">
         <v>0.8416137181597374</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>4631.417</v>
       </c>
@@ -1923,16 +1746,13 @@
         <v>13413786979.3248</v>
       </c>
       <c r="F59">
-        <v>-6941828.544688405</v>
+        <v>-107.2426632133454</v>
       </c>
       <c r="G59">
-        <v>362.4890102856461</v>
-      </c>
-      <c r="H59">
         <v>0.8141806091500976</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:7">
       <c r="A60">
         <v>4637.1444</v>
       </c>
@@ -1949,16 +1769,13 @@
         <v>15455655088.19918</v>
       </c>
       <c r="F60">
-        <v>-2592022.329911617</v>
+        <v>-40.09304483275614</v>
       </c>
       <c r="G60">
-        <v>265.0659483337108</v>
-      </c>
-      <c r="H60">
         <v>0.6928727939421042</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:7">
       <c r="A61">
         <v>4638.802</v>
       </c>
@@ -1975,16 +1792,13 @@
         <v>10210400299.78835</v>
       </c>
       <c r="F61">
-        <v>-16827056.91214114</v>
+        <v>-260.3717813232305</v>
       </c>
       <c r="G61">
-        <v>426.5390553607528</v>
-      </c>
-      <c r="H61">
         <v>0.8326779917284546</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>4644.7636</v>
       </c>
@@ -2001,16 +1815,13 @@
         <v>12328939260.77472</v>
       </c>
       <c r="F62">
-        <v>-9968567.408922862</v>
+        <v>-154.4458229011726</v>
       </c>
       <c r="G62">
-        <v>348.5385721603259</v>
-      </c>
-      <c r="H62">
         <v>0.7806024972501133</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>4648.7355</v>
       </c>
@@ -2027,16 +1838,13 @@
         <v>9316096811.345697</v>
       </c>
       <c r="F63">
-        <v>-21758083.13566476</v>
+        <v>-337.3924890915359</v>
       </c>
       <c r="G63">
-        <v>444.9743291182667</v>
-      </c>
-      <c r="H63">
         <v>0.8562500961764069</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>4668.7597</v>
       </c>
@@ -2053,16 +1861,13 @@
         <v>8019581387.743544</v>
       </c>
       <c r="F64">
-        <v>-27352308.31776557</v>
+        <v>-425.9665346478109</v>
       </c>
       <c r="G64">
-        <v>468.7508212037549</v>
-      </c>
-      <c r="H64">
         <v>0.8536444568442502</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>4680.1554</v>
       </c>
@@ -2079,16 +1884,13 @@
         <v>8044038364.816983</v>
       </c>
       <c r="F65">
-        <v>-29351754.43773678</v>
+        <v>-458.2203168852949</v>
       </c>
       <c r="G65">
-        <v>486.8262879988054</v>
-      </c>
-      <c r="H65">
         <v>0.857291182021686</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>4681.6048</v>
       </c>
@@ -2105,16 +1907,13 @@
         <v>16502061746.56462</v>
       </c>
       <c r="F66">
-        <v>-705912.2690772193</v>
+        <v>-11.02364414152402</v>
       </c>
       <c r="G66">
-        <v>281.7595400651596</v>
-      </c>
-      <c r="H66">
         <v>0.6262297650335722</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>4684.8705</v>
       </c>
@@ -2131,16 +1930,13 @@
         <v>15047213904.79412</v>
       </c>
       <c r="F67">
-        <v>-2299702.645966645</v>
+        <v>-35.93759484591009</v>
       </c>
       <c r="G67">
-        <v>300.7606192795334</v>
-      </c>
-      <c r="H67">
         <v>0.6618478383208597</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>4708.5916</v>
       </c>
@@ -2157,16 +1953,13 @@
         <v>6226433696.606266</v>
       </c>
       <c r="F68">
-        <v>-45160166.11724176</v>
+        <v>-709.2945703646126</v>
       </c>
       <c r="G68">
-        <v>541.1885568986736</v>
-      </c>
-      <c r="H68">
         <v>0.8589124318851744</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>4729.8685</v>
       </c>
@@ -2183,16 +1976,13 @@
         <v>12330198806.64964</v>
       </c>
       <c r="F69">
-        <v>-14668864.00734625</v>
+        <v>-231.4330645342694</v>
       </c>
       <c r="G69">
-        <v>386.6352719951028</v>
-      </c>
-      <c r="H69">
         <v>0.7938690867900281</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>4730.3421</v>
       </c>
@@ -2209,16 +1999,13 @@
         <v>11718998157.75992</v>
       </c>
       <c r="F70">
-        <v>30080.47500528535</v>
+        <v>0.4746317183824518</v>
       </c>
       <c r="G70">
-        <v>152.103565471654</v>
-      </c>
-      <c r="H70">
         <v>0.4991345298393296</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>4747.1274</v>
       </c>
@@ -2235,16 +2022,13 @@
         <v>12182460834.18043</v>
       </c>
       <c r="F71">
-        <v>-11130972.60223413</v>
+        <v>-176.2559595884213</v>
       </c>
       <c r="G71">
-        <v>353.6534040947407</v>
-      </c>
-      <c r="H71">
         <v>0.7684042625601248</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>4780.7756</v>
       </c>
@@ -2261,16 +2045,13 @@
         <v>13049881649.99369</v>
       </c>
       <c r="F72">
-        <v>218517.8671369059</v>
+        <v>3.484696170485083</v>
       </c>
       <c r="G72">
-        <v>213.2069025311453</v>
-      </c>
-      <c r="H72">
         <v>0.5229238564028793</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>4788.1452</v>
       </c>
@@ -2287,16 +2068,13 @@
         <v>11527685298.91117</v>
       </c>
       <c r="F73">
-        <v>-13409630.9179356</v>
+        <v>-214.1726473791402</v>
       </c>
       <c r="G73">
-        <v>394.4517984240071</v>
-      </c>
-      <c r="H73">
         <v>0.8164088534870499</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>4789.1654</v>
       </c>
@@ -2313,16 +2091,13 @@
         <v>12214222607.0965</v>
       </c>
       <c r="F74">
-        <v>512679.1934422441</v>
+        <v>8.19002255410669</v>
       </c>
       <c r="G74">
-        <v>187.7941768108143</v>
-      </c>
-      <c r="H74">
         <v>0.4876740644249166</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>4790.9897</v>
       </c>
@@ -2339,16 +2114,13 @@
         <v>10787860978.91849</v>
       </c>
       <c r="F75">
-        <v>-17479227.37828009</v>
+        <v>-279.3362981937369</v>
       </c>
       <c r="G75">
-        <v>419.2472942516421</v>
-      </c>
-      <c r="H75">
         <v>0.8221313482413499</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>4799.6061</v>
       </c>
@@ -2365,16 +2137,13 @@
         <v>12274156159.71665</v>
       </c>
       <c r="F76">
-        <v>-823370.7501867298</v>
+        <v>-13.18197770758739</v>
       </c>
       <c r="G76">
-        <v>168.6470972061475</v>
-      </c>
-      <c r="H76">
         <v>0.5253544179758886</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>4801.9909</v>
       </c>
@@ -2391,16 +2160,13 @@
         <v>12348284630.86265</v>
       </c>
       <c r="F77">
-        <v>-2952737.370836186</v>
+        <v>-47.29615638592789</v>
       </c>
       <c r="G77">
-        <v>274.6958173502403</v>
-      </c>
-      <c r="H77">
         <v>0.6623105769292491</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>4809.0525</v>
       </c>
@@ -2417,16 +2183,13 @@
         <v>12920168340.90231</v>
       </c>
       <c r="F78">
-        <v>-2661302.66838404</v>
+        <v>-42.69072025948257</v>
       </c>
       <c r="G78">
-        <v>274.2924547390904</v>
-      </c>
-      <c r="H78">
         <v>0.587218862852467</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>4837.2191</v>
       </c>
@@ -2443,16 +2206,13 @@
         <v>13058308164.59484</v>
       </c>
       <c r="F79">
-        <v>-1467798.278630122</v>
+        <v>-23.68327426579465</v>
       </c>
       <c r="G79">
-        <v>216.9166997070782</v>
-      </c>
-      <c r="H79">
         <v>0.5799732627472048</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>4840.8967</v>
       </c>
@@ -2469,16 +2229,13 @@
         <v>14557960922.72351</v>
       </c>
       <c r="F80">
-        <v>-4052042.016085098</v>
+        <v>-65.43039690265653</v>
       </c>
       <c r="G80">
-        <v>346.8030549982863</v>
-      </c>
-      <c r="H80">
         <v>0.7211970366081855</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:7">
       <c r="A81">
         <v>4857.0297</v>
       </c>
@@ -2495,16 +2252,13 @@
         <v>12018788255.7709</v>
       </c>
       <c r="F81">
-        <v>-5615693.694136345</v>
+        <v>-90.98169278913106</v>
       </c>
       <c r="G81">
-        <v>376.5128291380712</v>
-      </c>
-      <c r="H81">
         <v>0.7090575026386261</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:7">
       <c r="A82">
         <v>4861.099</v>
       </c>
@@ -2521,16 +2275,13 @@
         <v>3990929038.013825</v>
       </c>
       <c r="F82">
-        <v>-60376487.74711934</v>
+        <v>-978.9995515439643</v>
       </c>
       <c r="G82">
-        <v>610.5502756047948</v>
-      </c>
-      <c r="H82">
         <v>0.8793453162046073</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>4872.6789</v>
       </c>
@@ -2547,16 +2298,13 @@
         <v>2887925513.549094</v>
       </c>
       <c r="F83">
-        <v>-89694975.31203865</v>
+        <v>-1457.86119580841</v>
       </c>
       <c r="G83">
-        <v>670.6244879635998</v>
-      </c>
-      <c r="H83">
         <v>0.9013135147440396</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>4873.4986</v>
       </c>
@@ -2573,16 +2321,13 @@
         <v>3671614702.285092</v>
       </c>
       <c r="F84">
-        <v>-80187308.53974813</v>
+        <v>-1303.547088872066</v>
       </c>
       <c r="G84">
-        <v>652.0572418087476</v>
-      </c>
-      <c r="H84">
         <v>0.8922371223508457</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:7">
       <c r="A85">
         <v>4877.2394</v>
       </c>
@@ -2599,16 +2344,13 @@
         <v>13200198810.67547</v>
       </c>
       <c r="F85">
-        <v>-3943535.419819425</v>
+        <v>-64.15633594145454</v>
       </c>
       <c r="G85">
-        <v>301.19149868148</v>
-      </c>
-      <c r="H85">
         <v>0.6668492290836959</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:7">
       <c r="A86">
         <v>4883.0812</v>
       </c>
@@ -2625,16 +2367,13 @@
         <v>14394037156.56203</v>
       </c>
       <c r="F86">
-        <v>-5560008.59144887</v>
+        <v>-90.56265778636191</v>
       </c>
       <c r="G86">
-        <v>313.1099961994693</v>
-      </c>
-      <c r="H86">
         <v>0.7119238526230245</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:7">
       <c r="A87">
         <v>4883.5069</v>
       </c>
@@ -2651,16 +2390,13 @@
         <v>12120040484.85664</v>
       </c>
       <c r="F87">
-        <v>-7112166.979426265</v>
+        <v>-115.8546891658261</v>
       </c>
       <c r="G87">
-        <v>392.8880966500864</v>
-      </c>
-      <c r="H87">
         <v>0.7460472168261336</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:7">
       <c r="A88">
         <v>4886.795</v>
       </c>
@@ -2677,16 +2413,13 @@
         <v>12911355426.8304</v>
       </c>
       <c r="F88">
-        <v>-9510939.954688711</v>
+        <v>-155.0341502564576</v>
       </c>
       <c r="G88">
-        <v>355.8152646964811</v>
-      </c>
-      <c r="H88">
         <v>0.7517017559802283</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:7">
       <c r="A89">
         <v>4887.6964</v>
       </c>
@@ -2703,16 +2436,13 @@
         <v>11782764113.10058</v>
       </c>
       <c r="F89">
-        <v>-11828273.26366744</v>
+        <v>-192.8436719907606</v>
       </c>
       <c r="G89">
-        <v>361.8832589915302</v>
-      </c>
-      <c r="H89">
         <v>0.7550679792677039</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:7">
       <c r="A90">
         <v>4892.1209</v>
       </c>
@@ -2729,16 +2459,13 @@
         <v>2864040679.575552</v>
       </c>
       <c r="F90">
-        <v>-21980433.78721678</v>
+        <v>-358.6853459932291</v>
       </c>
       <c r="G90">
-        <v>618.9347908313625</v>
-      </c>
-      <c r="H90">
         <v>0.8997948056053549</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>4892.8584</v>
       </c>
@@ -2755,16 +2482,13 @@
         <v>2330706117.056531</v>
       </c>
       <c r="F91">
-        <v>-4926185.701093145</v>
+        <v>-80.39955041840666</v>
       </c>
       <c r="G91">
-        <v>618.8414988269474</v>
-      </c>
-      <c r="H91">
         <v>0.9136292872785773</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:7">
       <c r="A92">
         <v>4894.2253</v>
       </c>
@@ -2781,16 +2505,13 @@
         <v>12750199825.13306</v>
       </c>
       <c r="F92">
-        <v>-4331823.323476498</v>
+        <v>-70.71870956079017</v>
       </c>
       <c r="G92">
-        <v>232.76642785476</v>
-      </c>
-      <c r="H92">
         <v>0.5975439838206209</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:7">
       <c r="A93">
         <v>4909.1021</v>
       </c>
@@ -2807,16 +2528,13 @@
         <v>13419444026.11343</v>
       </c>
       <c r="F93">
-        <v>-4360078.836726672</v>
+        <v>-71.39637239951729</v>
       </c>
       <c r="G93">
-        <v>305.3434741262351</v>
-      </c>
-      <c r="H93">
         <v>0.6748750701107361</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:7">
       <c r="A94">
         <v>4910.7542</v>
       </c>
@@ -2833,16 +2551,13 @@
         <v>13210263293.32272</v>
       </c>
       <c r="F94">
-        <v>-5340941.849509899</v>
+        <v>-87.48744835925461</v>
       </c>
       <c r="G94">
-        <v>280.8214890136861</v>
-      </c>
-      <c r="H94">
         <v>0.6825713804301581</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:7">
       <c r="A95">
         <v>4911.3878</v>
       </c>
@@ -2859,16 +2574,13 @@
         <v>10686966886.8106</v>
       </c>
       <c r="F95">
-        <v>-13553818.84988412</v>
+        <v>-222.0474517518288</v>
       </c>
       <c r="G95">
-        <v>408.9698371265093</v>
-      </c>
-      <c r="H95">
         <v>0.7839709145668129</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:7">
       <c r="A96">
         <v>4911.6968</v>
       </c>
@@ -2885,16 +2597,13 @@
         <v>12210749227.02507</v>
       </c>
       <c r="F96">
-        <v>-10309280.75574248</v>
+        <v>-168.9039397971738</v>
       </c>
       <c r="G96">
-        <v>390.6331781611177</v>
-      </c>
-      <c r="H96">
         <v>0.7481693699321313</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:7">
       <c r="A97">
         <v>4911.9359</v>
       </c>
@@ -2911,16 +2620,13 @@
         <v>12235368289.28755</v>
       </c>
       <c r="F97">
-        <v>-11180923.87183375</v>
+        <v>-183.1935738725208</v>
       </c>
       <c r="G97">
-        <v>384.5108168893962</v>
-      </c>
-      <c r="H97">
         <v>0.7365628135844482</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:7">
       <c r="A98">
         <v>4918.6028</v>
       </c>
@@ -2937,16 +2643,13 @@
         <v>13184427309.72393</v>
       </c>
       <c r="F98">
-        <v>-6063520.314739813</v>
+        <v>-99.4824109166936</v>
       </c>
       <c r="G98">
-        <v>286.4684565991175</v>
-      </c>
-      <c r="H98">
         <v>0.6804148572440983</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:7">
       <c r="A99">
         <v>4919.3855</v>
       </c>
@@ -2963,16 +2666,13 @@
         <v>12731335140.48432</v>
       </c>
       <c r="F99">
-        <v>-3168989.853925667</v>
+        <v>-52.00095509211416</v>
       </c>
       <c r="G99">
-        <v>219.3877363176368</v>
-      </c>
-      <c r="H99">
         <v>0.6060579973590594</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:7">
       <c r="A100">
         <v>4921.8768</v>
       </c>
@@ -2989,16 +2689,13 @@
         <v>2218762979.587776</v>
       </c>
       <c r="F100">
-        <v>-5515895.202225931</v>
+        <v>-90.5580249427028</v>
       </c>
       <c r="G100">
-        <v>621.2839523717316</v>
-      </c>
-      <c r="H100">
         <v>0.921071058316754</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:7">
       <c r="A101">
         <v>4926.1443</v>
       </c>
@@ -3015,16 +2712,13 @@
         <v>8513857046.440112</v>
       </c>
       <c r="F101">
-        <v>-25841430.53253341</v>
+        <v>-424.6232170323244</v>
       </c>
       <c r="G101">
-        <v>523.3738562432578</v>
-      </c>
-      <c r="H101">
         <v>0.821472652747837</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:7">
       <c r="A102">
         <v>4939.5522</v>
       </c>
@@ -3041,16 +2735,13 @@
         <v>12138028284.99991</v>
       </c>
       <c r="F102">
-        <v>-8870398.07404653</v>
+        <v>-146.1539294955883</v>
       </c>
       <c r="G102">
-        <v>352.0149572303775</v>
-      </c>
-      <c r="H102">
         <v>0.7489655451128316</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>4940.1923</v>
       </c>
@@ -3067,16 +2758,13 @@
         <v>5088299376.296271</v>
       </c>
       <c r="F103">
-        <v>-80860974.58168915</v>
+        <v>-1332.487065464143</v>
       </c>
       <c r="G103">
-        <v>606.8437012180223</v>
-      </c>
-      <c r="H103">
         <v>0.8527192965992141</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>4941.0654</v>
       </c>
@@ -3093,16 +2781,13 @@
         <v>6499972628.710576</v>
       </c>
       <c r="F104">
-        <v>-59187035.58841902</v>
+        <v>-975.5000119376791</v>
       </c>
       <c r="G104">
-        <v>546.0628232056733</v>
-      </c>
-      <c r="H104">
         <v>0.8491216195357875</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:7">
       <c r="A105">
         <v>4947.0177</v>
       </c>
@@ -3119,16 +2804,13 @@
         <v>11484256212.068</v>
       </c>
       <c r="F105">
-        <v>-730298.6232787917</v>
+        <v>-12.05101117147503</v>
       </c>
       <c r="G105">
-        <v>169.6818028425222</v>
-      </c>
-      <c r="H105">
         <v>0.4838016924799176</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>4947.7686</v>
       </c>
@@ -3145,16 +2827,13 @@
         <v>7913722701.031931</v>
       </c>
       <c r="F106">
-        <v>-29329980.98010488</v>
+        <v>-484.0622284894184</v>
       </c>
       <c r="G106">
-        <v>508.9681532508874</v>
-      </c>
-      <c r="H106">
         <v>0.8071353558196513</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:7">
       <c r="A107">
         <v>4951.4876</v>
       </c>
@@ -3171,16 +2850,13 @@
         <v>12291723081.39206</v>
       </c>
       <c r="F107">
-        <v>-8880223.753240881</v>
+        <v>-146.6693615643696</v>
       </c>
       <c r="G107">
-        <v>345.1118428330054</v>
-      </c>
-      <c r="H107">
         <v>0.7403304411567413</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:7">
       <c r="A108">
         <v>4967.4747</v>
       </c>
@@ -3197,16 +2873,13 @@
         <v>5827675215.503829</v>
       </c>
       <c r="F108">
-        <v>-54723184.04902476</v>
+        <v>-906.7491173006898</v>
       </c>
       <c r="G108">
-        <v>567.30014252463</v>
-      </c>
-      <c r="H108">
         <v>0.844326646881619</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:7">
       <c r="A109">
         <v>4969.2836</v>
       </c>
@@ -3223,16 +2896,13 @@
         <v>11413951763.73825</v>
       </c>
       <c r="F109">
-        <v>-13459948.09042961</v>
+        <v>-223.1090023427121</v>
       </c>
       <c r="G109">
-        <v>434.3695935401912</v>
-      </c>
-      <c r="H109">
         <v>0.7609090127340565</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:7">
       <c r="A110">
         <v>4971.3044</v>
       </c>
@@ -3249,16 +2919,13 @@
         <v>12218846023.7999</v>
       </c>
       <c r="F110">
-        <v>-10676377.70953258</v>
+        <v>-177.0411033546665</v>
       </c>
       <c r="G110">
-        <v>361.8275211944923</v>
-      </c>
-      <c r="H110">
         <v>0.7447557560289856</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:7">
       <c r="A111">
         <v>4971.8828</v>
       </c>
@@ -3275,16 +2942,13 @@
         <v>14196888590.4441</v>
       </c>
       <c r="F111">
-        <v>-4488675.63201231</v>
+        <v>-74.44213528288348</v>
       </c>
       <c r="G111">
-        <v>289.428342609861</v>
-      </c>
-      <c r="H111">
         <v>0.6370136085299584</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:7">
       <c r="A112">
         <v>4983.8901</v>
       </c>
@@ -3301,16 +2965,13 @@
         <v>6020396105.175292</v>
       </c>
       <c r="F112">
-        <v>-37993097.77694524</v>
+        <v>-631.6161249776679</v>
       </c>
       <c r="G112">
-        <v>517.3097895519192</v>
-      </c>
-      <c r="H112">
         <v>0.8468090952332923</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:7">
       <c r="A113">
         <v>4984.6411</v>
       </c>
@@ -3327,16 +2988,13 @@
         <v>7952955952.670198</v>
       </c>
       <c r="F113">
-        <v>-24282917.29136499</v>
+        <v>-403.7520253715323</v>
       </c>
       <c r="G113">
-        <v>457.0886118432708</v>
-      </c>
-      <c r="H113">
         <v>0.8175133018182108</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:7">
       <c r="A114">
         <v>4985.2434</v>
       </c>
@@ -3353,16 +3011,13 @@
         <v>6995084271.945768</v>
       </c>
       <c r="F114">
-        <v>-37469353.74368952</v>
+        <v>-623.0783353368322</v>
       </c>
       <c r="G114">
-        <v>541.2237488989177</v>
-      </c>
-      <c r="H114">
         <v>0.8370378768954065</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:7">
       <c r="A115">
         <v>4986.6438</v>
       </c>
@@ -3379,16 +3034,13 @@
         <v>9069213212.450693</v>
       </c>
       <c r="F115">
-        <v>-21850992.02410202</v>
+        <v>-363.4623935021594</v>
       </c>
       <c r="G115">
-        <v>468.9288560410837</v>
-      </c>
-      <c r="H115">
         <v>0.8163024037643201</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:7">
       <c r="A116">
         <v>4987.6138</v>
       </c>
@@ -3405,16 +3057,13 @@
         <v>12563664532.54956</v>
       </c>
       <c r="F116">
-        <v>-2312462.893460947</v>
+        <v>-38.47221742573905</v>
       </c>
       <c r="G116">
-        <v>228.4080897259217</v>
-      </c>
-      <c r="H116">
         <v>0.5462601285278765</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:7">
       <c r="A117">
         <v>4990.3419</v>
       </c>
@@ -3431,16 +3080,13 @@
         <v>11145836800.61831</v>
       </c>
       <c r="F117">
-        <v>-13980746.21134952</v>
+        <v>-232.7236527234075</v>
       </c>
       <c r="G117">
-        <v>396.4919162247787</v>
-      </c>
-      <c r="H117">
         <v>0.7781577339076411</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:7">
       <c r="A118">
         <v>4992.6608</v>
       </c>
@@ -3457,16 +3103,13 @@
         <v>10936059724.60959</v>
       </c>
       <c r="F118">
-        <v>-13693696.47602005</v>
+        <v>-228.0513452766375</v>
       </c>
       <c r="G118">
-        <v>402.3124239570178</v>
-      </c>
-      <c r="H118">
         <v>0.772420618937437</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:7">
       <c r="A119">
         <v>4995.5228</v>
       </c>
@@ -3483,16 +3126,13 @@
         <v>4732275773.443843</v>
       </c>
       <c r="F119">
-        <v>-184713694.693187</v>
+        <v>-3077.940900767949</v>
       </c>
       <c r="G119">
-        <v>648.1320726640671</v>
-      </c>
-      <c r="H119">
         <v>0.8568798187925261</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:7">
       <c r="A120">
         <v>5000.5071</v>
       </c>
@@ -3509,16 +3149,13 @@
         <v>9404691162.248508</v>
       </c>
       <c r="F120">
-        <v>3200937.919831602</v>
+        <v>53.39133273512572</v>
       </c>
       <c r="G120">
-        <v>113.909581325338</v>
-      </c>
-      <c r="H120">
         <v>0.374418684945979</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:7">
       <c r="A121">
         <v>5003.2589</v>
       </c>
@@ -3535,16 +3172,13 @@
         <v>5244412345.080046</v>
       </c>
       <c r="F121">
-        <v>-52561305.58710208</v>
+        <v>-877.2012162975434</v>
       </c>
       <c r="G121">
-        <v>557.2507669958649</v>
-      </c>
-      <c r="H121">
         <v>0.855292008588283</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:7">
       <c r="A122">
         <v>5004.1883</v>
       </c>
@@ -3561,16 +3195,13 @@
         <v>11612696686.44507</v>
       </c>
       <c r="F122">
-        <v>-10061021.32324428</v>
+        <v>-167.9405510210272</v>
       </c>
       <c r="G122">
-        <v>389.4040072806783</v>
-      </c>
-      <c r="H122">
         <v>0.7515000938532119</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:7">
       <c r="A123">
         <v>5005.4402</v>
       </c>
@@ -3587,16 +3218,13 @@
         <v>11930085401.63706</v>
       </c>
       <c r="F123">
-        <v>-808416.7638754812</v>
+        <v>-13.49761973570034</v>
       </c>
       <c r="G123">
-        <v>209.6266383939193</v>
-      </c>
-      <c r="H123">
         <v>0.539179559299829</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:7">
       <c r="A124">
         <v>5007.1086</v>
       </c>
@@ -3613,16 +3241,13 @@
         <v>6167118795.504225</v>
       </c>
       <c r="F124">
-        <v>-38246998.85125896</v>
+        <v>-638.7993037700727</v>
       </c>
       <c r="G124">
-        <v>526.8856422683017</v>
-      </c>
-      <c r="H124">
         <v>0.8471808253999096</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:7">
       <c r="A125">
         <v>5016.3412</v>
       </c>
@@ -3639,16 +3264,13 @@
         <v>6977401631.047334</v>
       </c>
       <c r="F125">
-        <v>-39624524.16367897</v>
+        <v>-663.0269723160393</v>
       </c>
       <c r="G125">
-        <v>531.8922237942238</v>
-      </c>
-      <c r="H125">
         <v>0.8322402011036238</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:7">
       <c r="A126">
         <v>5023.6362</v>
       </c>
@@ -3665,16 +3287,13 @@
         <v>8587246640.611396</v>
       </c>
       <c r="F126">
-        <v>-32711857.83009788</v>
+        <v>-548.1550328826257</v>
       </c>
       <c r="G126">
-        <v>495.3140120929924</v>
-      </c>
-      <c r="H126">
         <v>0.8100424194730144</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:7">
       <c r="A127">
         <v>5024.5876</v>
       </c>
@@ -3691,16 +3310,13 @@
         <v>10902535318.958</v>
       </c>
       <c r="F127">
-        <v>838722.8046989171</v>
+        <v>14.05718501936954</v>
       </c>
       <c r="G127">
-        <v>131.2631921423011</v>
-      </c>
-      <c r="H127">
         <v>0.4354980829097452</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:7">
       <c r="A128">
         <v>5029.1588</v>
       </c>
@@ -3717,16 +3333,13 @@
         <v>12081670741.20598</v>
       </c>
       <c r="F128">
-        <v>-2477071.791400491</v>
+        <v>-41.55407421677781</v>
       </c>
       <c r="G128">
-        <v>256.3266782031861</v>
-      </c>
-      <c r="H128">
         <v>0.6090934309477531</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:7">
       <c r="A129">
         <v>5029.5286</v>
       </c>
@@ -3743,16 +3356,13 @@
         <v>11905670547.78912</v>
       </c>
       <c r="F129">
-        <v>-12430543.20440599</v>
+        <v>-208.5438121995939</v>
       </c>
       <c r="G129">
-        <v>429.1666017403272</v>
-      </c>
-      <c r="H129">
         <v>0.7770234049437367</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:7">
       <c r="A130">
         <v>5031.0203</v>
       </c>
@@ -3769,16 +3379,13 @@
         <v>14335169824.14295</v>
       </c>
       <c r="F130">
-        <v>-1644777.421210033</v>
+        <v>-27.60214647787022</v>
       </c>
       <c r="G130">
-        <v>244.3140763600454</v>
-      </c>
-      <c r="H130">
         <v>0.5814699288102826</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:7">
       <c r="A131">
         <v>5032.1816</v>
       </c>
@@ -3795,16 +3402,13 @@
         <v>7507382581.9926</v>
       </c>
       <c r="F131">
-        <v>-593587.1037824171</v>
+        <v>-9.963691368981067</v>
       </c>
       <c r="G131">
-        <v>142.9801140968682</v>
-      </c>
-      <c r="H131">
         <v>0.2661876790722415</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:7">
       <c r="A132">
         <v>5045.6179</v>
       </c>
@@ -3821,16 +3425,13 @@
         <v>12743712725.3684</v>
       </c>
       <c r="F132">
-        <v>-5330237.979999029</v>
+        <v>-89.70999133570535</v>
       </c>
       <c r="G132">
-        <v>386.2066084853685</v>
-      </c>
-      <c r="H132">
         <v>0.7475411076972691</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:7">
       <c r="A133">
         <v>5056.0519</v>
       </c>
@@ -3847,16 +3448,13 @@
         <v>11394193186.60372</v>
       </c>
       <c r="F133">
-        <v>433245.7159828548</v>
+        <v>7.306769055453811</v>
       </c>
       <c r="G133">
-        <v>195.6694928810959</v>
-      </c>
-      <c r="H133">
         <v>0.4609639689790187</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:7">
       <c r="A134">
         <v>5070.1789</v>
       </c>
@@ -3873,16 +3471,13 @@
         <v>5258090068.64201</v>
       </c>
       <c r="F134">
-        <v>-59752232.8417443</v>
+        <v>-1010.549324352464</v>
       </c>
       <c r="G134">
-        <v>549.8957560367161</v>
-      </c>
-      <c r="H134">
         <v>0.8478931892729015</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:7">
       <c r="A135">
         <v>5074.0862</v>
       </c>
@@ -3899,16 +3494,13 @@
         <v>12729679509.34903</v>
       </c>
       <c r="F135">
-        <v>-2892619.543676231</v>
+        <v>-48.95858778247042</v>
       </c>
       <c r="G135">
-        <v>295.4152197930109</v>
-      </c>
-      <c r="H135">
         <v>0.6718089219455455</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:7">
       <c r="A136">
         <v>5080.3906</v>
       </c>
@@ -3925,16 +3517,13 @@
         <v>9236533839.163744</v>
       </c>
       <c r="F136">
-        <v>-19637213.37079386</v>
+        <v>-332.7798034342982</v>
       </c>
       <c r="G136">
-        <v>483.8797543895105</v>
-      </c>
-      <c r="H136">
         <v>0.797563945451028</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:7">
       <c r="A137">
         <v>5084.7555</v>
       </c>
@@ -3951,16 +3540,13 @@
         <v>4186917046.701827</v>
       </c>
       <c r="F137">
-        <v>-251237432.5684242</v>
+        <v>-4261.227215945856</v>
       </c>
       <c r="G137">
-        <v>672.1334036531405</v>
-      </c>
-      <c r="H137">
         <v>0.8562221996798296</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:7">
       <c r="A138">
         <v>5092.1929</v>
       </c>
@@ -3977,16 +3563,13 @@
         <v>10301363760.41961</v>
       </c>
       <c r="F138">
-        <v>-11040487.82364796</v>
+        <v>-187.5309791803666</v>
       </c>
       <c r="G138">
-        <v>423.885296576584</v>
-      </c>
-      <c r="H138">
         <v>0.7766541755500417</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:7">
       <c r="A139">
         <v>5100.1192</v>
       </c>
@@ -4003,16 +3586,13 @@
         <v>5502145211.990395</v>
       </c>
       <c r="F139">
-        <v>-119172833.5378027</v>
+        <v>-2027.392017498997</v>
       </c>
       <c r="G139">
-        <v>581.9364641927928</v>
-      </c>
-      <c r="H139">
         <v>0.8346256617895024</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:7">
       <c r="A140">
         <v>5100.4984</v>
       </c>
@@ -4029,16 +3609,13 @@
         <v>11989686442.97081</v>
       </c>
       <c r="F140">
-        <v>-4192157.300135178</v>
+        <v>-71.32302932863757</v>
       </c>
       <c r="G140">
-        <v>205.7198180589327</v>
-      </c>
-      <c r="H140">
         <v>0.5811203322790391</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:7">
       <c r="A141">
         <v>5108.8708</v>
       </c>
@@ -4055,16 +3632,13 @@
         <v>5357166275.682172</v>
       </c>
       <c r="F141">
-        <v>-73365016.91506253</v>
+        <v>-1250.241891096973</v>
       </c>
       <c r="G141">
-        <v>557.4672882490107</v>
-      </c>
-      <c r="H141">
         <v>0.849262856413401</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:7">
       <c r="A142">
         <v>5117.2037</v>
       </c>
@@ -4081,16 +3655,13 @@
         <v>7550263722.149791</v>
       </c>
       <c r="F142">
-        <v>5231827.185733397</v>
+        <v>89.30290697633487</v>
       </c>
       <c r="G142">
-        <v>140.6045061678527</v>
-      </c>
-      <c r="H142">
         <v>0.2984698530348242</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:7">
       <c r="A143">
         <v>5128.788</v>
       </c>
@@ -4107,16 +3678,13 @@
         <v>6499194775.788782</v>
       </c>
       <c r="F143">
-        <v>-63704048.90448733</v>
+        <v>-1089.837825042308</v>
       </c>
       <c r="G143">
-        <v>549.4571242738238</v>
-      </c>
-      <c r="H143">
         <v>0.8407363754475672</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:7">
       <c r="A144">
         <v>5132.8984</v>
       </c>
@@ -4133,16 +3701,13 @@
         <v>11709799281.48086</v>
       </c>
       <c r="F144">
-        <v>-11767047.0369142</v>
+        <v>-201.4698463646326</v>
       </c>
       <c r="G144">
-        <v>414.6831450819184</v>
-      </c>
-      <c r="H144">
         <v>0.7873530160644492</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:7">
       <c r="A145">
         <v>5138.8135</v>
       </c>
@@ -4159,16 +3724,13 @@
         <v>8486841868.498534</v>
       </c>
       <c r="F145">
-        <v>-24557776.87316553</v>
+        <v>-420.9513966159382</v>
       </c>
       <c r="G145">
-        <v>519.2157442921462</v>
-      </c>
-      <c r="H145">
         <v>0.8182063151461183</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:7">
       <c r="A146">
         <v>5143.1715</v>
       </c>
@@ -4185,16 +3747,13 @@
         <v>10382454373.46235</v>
       </c>
       <c r="F146">
-        <v>-17357029.61000842</v>
+        <v>-297.7737661609422</v>
       </c>
       <c r="G146">
-        <v>501.2889690035408</v>
-      </c>
-      <c r="H146">
         <v>0.790854144056891</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:7">
       <c r="A147">
         <v>5149.477</v>
       </c>
@@ -4211,16 +3770,13 @@
         <v>12141746973.97937</v>
       </c>
       <c r="F147">
-        <v>-7869201.182299123</v>
+        <v>-135.1679129283156</v>
       </c>
       <c r="G147">
-        <v>372.595456089051</v>
-      </c>
-      <c r="H147">
         <v>0.7305179513332208</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:7">
       <c r="A148">
         <v>5149.6634</v>
       </c>
@@ -4237,16 +3793,13 @@
         <v>10734302222.78239</v>
       </c>
       <c r="F148">
-        <v>-14799714.47886929</v>
+        <v>-254.2213822479019</v>
       </c>
       <c r="G148">
-        <v>413.3331222706581</v>
-      </c>
-      <c r="H148">
         <v>0.7735137760121482</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:7">
       <c r="A149">
         <v>5160.4947</v>
       </c>
@@ -4263,16 +3816,13 @@
         <v>12967687713.93533</v>
       </c>
       <c r="F149">
-        <v>-9042681.817730691</v>
+        <v>-155.6569281153229</v>
       </c>
       <c r="G149">
-        <v>395.0374591750795</v>
-      </c>
-      <c r="H149">
         <v>0.699779207291259</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:7">
       <c r="A150">
         <v>5163.7108</v>
       </c>
@@ -4289,16 +3839,13 @@
         <v>5217585901.814314</v>
       </c>
       <c r="F150">
-        <v>-28117945.07311838</v>
+        <v>-484.3123776808198</v>
       </c>
       <c r="G150">
-        <v>539.9353231382562</v>
-      </c>
-      <c r="H150">
         <v>0.845240834541533</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:7">
       <c r="A151">
         <v>5166.8495</v>
       </c>
@@ -4315,16 +3862,13 @@
         <v>10922222733.97431</v>
       </c>
       <c r="F151">
-        <v>-15338981.41843395</v>
+        <v>-264.3639620207099</v>
       </c>
       <c r="G151">
-        <v>429.3649716223846</v>
-      </c>
-      <c r="H151">
         <v>0.7638897176322621</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:7">
       <c r="A152">
         <v>5196.3884</v>
       </c>
@@ -4341,16 +3885,13 @@
         <v>3114656976.93574</v>
       </c>
       <c r="F152">
-        <v>-367665834.911483</v>
+        <v>-6372.872012455802</v>
       </c>
       <c r="G152">
-        <v>703.8480779650433</v>
-      </c>
-      <c r="H152">
         <v>0.8566513920341772</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:7">
       <c r="A153">
         <v>5196.9191</v>
       </c>
@@ -4367,16 +3908,13 @@
         <v>8834633591.545847</v>
       </c>
       <c r="F153">
-        <v>-26189932.0407669</v>
+        <v>-454.004729364312</v>
       </c>
       <c r="G153">
-        <v>519.1791656285195</v>
-      </c>
-      <c r="H153">
         <v>0.8035873779288836</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:7">
       <c r="A154">
         <v>5197.5065</v>
       </c>
@@ -4393,16 +3931,13 @@
         <v>12803574953.95595</v>
       </c>
       <c r="F154">
-        <v>-9880701.13207834</v>
+        <v>-171.3020634250619</v>
       </c>
       <c r="G154">
-        <v>340.3123212836119</v>
-      </c>
-      <c r="H154">
         <v>0.7161659757329624</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:7">
       <c r="A155">
         <v>5200.1588</v>
       </c>
@@ -4419,16 +3954,13 @@
         <v>7638669779.545975</v>
       </c>
       <c r="F155">
-        <v>-39702579.89995347</v>
+        <v>-688.676623483888</v>
       </c>
       <c r="G155">
-        <v>490.0303992407331</v>
-      </c>
-      <c r="H155">
         <v>0.8194174810846763</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:7">
       <c r="A156">
         <v>5216.6327</v>
       </c>
@@ -4445,16 +3977,13 @@
         <v>6505538133.629124</v>
       </c>
       <c r="F156">
-        <v>-32166149.9072182</v>
+        <v>-559.7181465267067</v>
       </c>
       <c r="G156">
-        <v>517.2171929760651</v>
-      </c>
-      <c r="H156">
         <v>0.8283048241256601</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:7">
       <c r="A157">
         <v>5217.7263</v>
       </c>
@@ -4471,16 +4000,13 @@
         <v>3722585579.749247</v>
       </c>
       <c r="F157">
-        <v>-171717254.0896718</v>
+        <v>-2988.652298540831</v>
       </c>
       <c r="G157">
-        <v>597.5479325376913</v>
-      </c>
-      <c r="H157">
         <v>0.8510798430438764</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:7">
       <c r="A158">
         <v>5218.842</v>
       </c>
@@ -4497,16 +4023,13 @@
         <v>7569734722.561796</v>
       </c>
       <c r="F158">
-        <v>-31503722.14269883</v>
+        <v>-548.4235090668823</v>
       </c>
       <c r="G158">
-        <v>516.9982386881812</v>
-      </c>
-      <c r="H158">
         <v>0.8175383912785</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:7">
       <c r="A159">
         <v>5224.6397</v>
       </c>
@@ -4523,16 +4046,13 @@
         <v>9835886170.377907</v>
       </c>
       <c r="F159">
-        <v>3310283.353837809</v>
+        <v>57.69005080200691</v>
       </c>
       <c r="G159">
-        <v>74.59465487300163</v>
-      </c>
-      <c r="H159">
         <v>0.3527713916043146</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:7">
       <c r="A160">
         <v>5226.9809</v>
       </c>
@@ -4549,16 +4069,13 @@
         <v>14125888016.79154</v>
       </c>
       <c r="F160">
-        <v>-8103001.370698667</v>
+        <v>-141.2787262337548</v>
       </c>
       <c r="G160">
-        <v>447.3674607553189</v>
-      </c>
-      <c r="H160">
         <v>0.7823174883676389</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:7">
       <c r="A161">
         <v>5229.8323</v>
       </c>
@@ -4575,16 +4092,13 @@
         <v>13022276869.73432</v>
       </c>
       <c r="F161">
-        <v>-3797962.74363583</v>
+        <v>-66.25491746728024</v>
       </c>
       <c r="G161">
-        <v>246.4911865977916</v>
-      </c>
-      <c r="H161">
         <v>0.6277198798228258</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:7">
       <c r="A162">
         <v>5234.3971</v>
       </c>
@@ -4601,16 +4115,13 @@
         <v>2710103470.659324</v>
       </c>
       <c r="F162">
-        <v>-27837535.0133892</v>
+        <v>-486.0463311776343</v>
       </c>
       <c r="G162">
-        <v>641.4636615118862</v>
-      </c>
-      <c r="H162">
         <v>0.8960555193100996</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:7">
       <c r="A163">
         <v>5243.9504</v>
       </c>
@@ -4627,16 +4138,13 @@
         <v>10023297965.74026</v>
       </c>
       <c r="F163">
-        <v>-18650091.3927904</v>
+        <v>-326.2267531929478</v>
       </c>
       <c r="G163">
-        <v>508.8058949962946</v>
-      </c>
-      <c r="H163">
         <v>0.7837258549564907</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:7">
       <c r="A164">
         <v>5245.2366</v>
       </c>
@@ -4653,16 +4161,13 @@
         <v>13135640650.21904</v>
       </c>
       <c r="F164">
-        <v>-6570350.084674701</v>
+        <v>-114.9564505584537</v>
       </c>
       <c r="G164">
-        <v>314.3535067409522</v>
-      </c>
-      <c r="H164">
         <v>0.6432035886639236</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:7">
       <c r="A165">
         <v>5248.511</v>
       </c>
@@ -4679,16 +4184,13 @@
         <v>15977071050.12762</v>
       </c>
       <c r="F165">
-        <v>-5032005.68936869</v>
+        <v>-88.0961903423038</v>
       </c>
       <c r="G165">
-        <v>411.260583732821</v>
-      </c>
-      <c r="H165">
         <v>0.7567043574720576</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:7">
       <c r="A166">
         <v>5251.6703</v>
       </c>
@@ -4705,16 +4207,13 @@
         <v>15918382172.06753</v>
       </c>
       <c r="F166">
-        <v>-5510986.002642492</v>
+        <v>-96.53986123656826</v>
       </c>
       <c r="G166">
-        <v>422.4302103327851</v>
-      </c>
-      <c r="H166">
         <v>0.7566019701073616</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:7">
       <c r="A167">
         <v>5252.1075</v>
       </c>
@@ -4731,16 +4230,13 @@
         <v>6619638097.257519</v>
       </c>
       <c r="F167">
-        <v>-50739804.61292195</v>
+        <v>-888.9194258662811</v>
       </c>
       <c r="G167">
-        <v>485.1834988164658</v>
-      </c>
-      <c r="H167">
         <v>0.8195833569663222</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:7">
       <c r="A168">
         <v>5254.924</v>
       </c>
@@ -4757,16 +4253,13 @@
         <v>12360060888.92305</v>
       </c>
       <c r="F168">
-        <v>-10685300.02188325</v>
+        <v>-187.2979550716215</v>
       </c>
       <c r="G168">
-        <v>399.3487262362295</v>
-      </c>
-      <c r="H168">
         <v>0.7392427507339475</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:7">
       <c r="A169">
         <v>5271.0039</v>
       </c>
@@ -4783,16 +4276,13 @@
         <v>1306177988.807577</v>
       </c>
       <c r="F169">
-        <v>46600732.58203628</v>
+        <v>819.3439825316825</v>
       </c>
       <c r="G169">
-        <v>614.2584235759223</v>
-      </c>
-      <c r="H169">
         <v>0.9116238181148668</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:7">
       <c r="A170">
         <v>5283.2601</v>
       </c>
@@ -4809,16 +4299,13 @@
         <v>4651815203.089018</v>
       </c>
       <c r="F170">
-        <v>-89965096.61527938</v>
+        <v>-1585.463334016445</v>
       </c>
       <c r="G170">
-        <v>595.810304460068</v>
-      </c>
-      <c r="H170">
         <v>0.8398793500122246</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:7">
       <c r="A171">
         <v>5323.5213</v>
       </c>
@@ -4835,16 +4322,13 @@
         <v>14784546670.91646</v>
       </c>
       <c r="F171">
-        <v>-2992602.764418385</v>
+        <v>-53.14078050548967</v>
       </c>
       <c r="G171">
-        <v>388.5713691400574</v>
-      </c>
-      <c r="H171">
         <v>0.6669704991980717</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:7">
       <c r="A172">
         <v>5325.6601</v>
       </c>
@@ -4861,16 +4345,13 @@
         <v>3126428420.177254</v>
       </c>
       <c r="F172">
-        <v>-38633463.43907055</v>
+        <v>-686.3052282669623</v>
       </c>
       <c r="G172">
-        <v>636.1004480173411</v>
-      </c>
-      <c r="H172">
         <v>0.8721581314611457</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:7">
       <c r="A173">
         <v>5327.6244</v>
       </c>
@@ -4887,16 +4368,13 @@
         <v>11202909959.73729</v>
       </c>
       <c r="F173">
-        <v>2110626.258592449</v>
+        <v>37.50805279347537</v>
       </c>
       <c r="G173">
-        <v>196.949620428969</v>
-      </c>
-      <c r="H173">
         <v>0.4120291360757221</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:7">
       <c r="A174">
         <v>5329.5208</v>
       </c>
@@ -4913,16 +4391,13 @@
         <v>1373798496.731372</v>
       </c>
       <c r="F174">
-        <v>-71835567.56832862</v>
+        <v>-1277.0501597424</v>
       </c>
       <c r="G174">
-        <v>669.3904356366385</v>
-      </c>
-      <c r="H174">
         <v>0.9045599968939118</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:7">
       <c r="A175">
         <v>5330.0139</v>
       </c>
@@ -4939,16 +4414,13 @@
         <v>2330698961.694452</v>
       </c>
       <c r="F175">
-        <v>-511160649.9937</v>
+        <v>-9087.954163676914</v>
       </c>
       <c r="G175">
-        <v>742.448428838096</v>
-      </c>
-      <c r="H175">
         <v>0.8571259333275768</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:7">
       <c r="A176">
         <v>5331.4717</v>
       </c>
@@ -4965,16 +4437,13 @@
         <v>13882933541.68882</v>
       </c>
       <c r="F176">
-        <v>-5673291.077407782</v>
+        <v>-100.8932072450339</v>
       </c>
       <c r="G176">
-        <v>314.8919959077166</v>
-      </c>
-      <c r="H176">
         <v>0.6172082715106413</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:7">
       <c r="A177">
         <v>5334.3831</v>
       </c>
@@ -4991,16 +4460,13 @@
         <v>8514532137.6654</v>
       </c>
       <c r="F177">
-        <v>-33855656.10957447</v>
+        <v>-602.4145580929364</v>
       </c>
       <c r="G177">
-        <v>500.1802131727463</v>
-      </c>
-      <c r="H177">
         <v>0.8023789558803434</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:7">
       <c r="A178">
         <v>5341.4147</v>
       </c>
@@ -5017,16 +4483,13 @@
         <v>4842457172.657739</v>
       </c>
       <c r="F178">
-        <v>-58508118.79221967</v>
+        <v>-1042.443675560976</v>
       </c>
       <c r="G178">
-        <v>600.5486337546013</v>
-      </c>
-      <c r="H178">
         <v>0.834620461466053</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:7">
       <c r="A179">
         <v>5366.8911</v>
       </c>
@@ -5043,16 +4506,13 @@
         <v>12590909595.68492</v>
       </c>
       <c r="F179">
-        <v>-11939727.53198911</v>
+        <v>-213.7455645057841</v>
       </c>
       <c r="G179">
-        <v>424.5330561625467</v>
-      </c>
-      <c r="H179">
         <v>0.7428392420894467</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:7">
       <c r="A180">
         <v>5371.4552</v>
       </c>
@@ -5069,16 +4529,13 @@
         <v>4660942873.512526</v>
       </c>
       <c r="F180">
-        <v>-62274035.04002401</v>
+        <v>-1115.781693978238</v>
       </c>
       <c r="G180">
-        <v>669.7457880486612</v>
-      </c>
-      <c r="H180">
         <v>0.8272606224990258</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:7">
       <c r="A181">
         <v>5372.9834</v>
       </c>
@@ -5095,16 +4552,13 @@
         <v>1526690484.806616</v>
       </c>
       <c r="F181">
-        <v>-221607823.0460393</v>
+        <v>-3971.740832769973</v>
       </c>
       <c r="G181">
-        <v>703.0330618523579</v>
-      </c>
-      <c r="H181">
         <v>0.8940244532953772</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:7">
       <c r="A182">
         <v>5375.2029</v>
       </c>
@@ -5121,16 +4575,13 @@
         <v>12914418430.17832</v>
       </c>
       <c r="F182">
-        <v>-7541722.333241968</v>
+        <v>-135.2213211874688</v>
       </c>
       <c r="G182">
-        <v>329.0620903396443</v>
-      </c>
-      <c r="H182">
         <v>0.6373180872324519</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:7">
       <c r="A183">
         <v>5381.0699</v>
       </c>
@@ -5147,16 +4598,13 @@
         <v>13646285042.88204</v>
       </c>
       <c r="F183">
-        <v>-5335899.772438633</v>
+        <v>-95.77587462798972</v>
       </c>
       <c r="G183">
-        <v>367.7020108115853</v>
-      </c>
-      <c r="H183">
         <v>0.6448746002109773</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:7">
       <c r="A184">
         <v>5384.8661</v>
       </c>
@@ -5173,16 +4621,13 @@
         <v>4353498554.83496</v>
       </c>
       <c r="F184">
-        <v>-40829335.3814453</v>
+        <v>-733.3772806298074</v>
       </c>
       <c r="G184">
-        <v>645.8085397330899</v>
-      </c>
-      <c r="H184">
         <v>0.8438469592447372</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:7">
       <c r="A185">
         <v>5390.9777</v>
       </c>
@@ -5199,16 +4644,13 @@
         <v>11149734484.12477</v>
       </c>
       <c r="F185">
-        <v>-14357162.42865377</v>
+        <v>-258.1761468215404</v>
       </c>
       <c r="G185">
-        <v>461.5632895720748</v>
-      </c>
-      <c r="H185">
         <v>0.734185402183704</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:7">
       <c r="A186">
         <v>5394.6671</v>
       </c>
@@ -5225,16 +4667,13 @@
         <v>5153111374.358268</v>
       </c>
       <c r="F186">
-        <v>-51987300.25461452</v>
+        <v>-935.496228429413</v>
       </c>
       <c r="G186">
-        <v>572.3916342336527</v>
-      </c>
-      <c r="H186">
         <v>0.8210208442076714</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:7">
       <c r="A187">
         <v>5399.1185</v>
       </c>
@@ -5251,16 +4690,13 @@
         <v>8143067522.921221</v>
       </c>
       <c r="F187">
-        <v>-29021.51807901958</v>
+        <v>-0.5226639812132438</v>
       </c>
       <c r="G187">
-        <v>199.8942695846278</v>
-      </c>
-      <c r="H187">
         <v>0.287857588119788</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:7">
       <c r="A188">
         <v>5399.7803</v>
       </c>
@@ -5277,16 +4713,13 @@
         <v>12673378352.46169</v>
       </c>
       <c r="F188">
-        <v>-9970075.815367874</v>
+        <v>-179.5785328424379</v>
       </c>
       <c r="G188">
-        <v>394.1876027371848</v>
-      </c>
-      <c r="H188">
         <v>0.6891616669844864</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:7">
       <c r="A189">
         <v>5405.3239</v>
       </c>
@@ -5303,16 +4736,13 @@
         <v>12905788411.36051</v>
       </c>
       <c r="F189">
-        <v>-5549750.559369981</v>
+        <v>-100.0633517800333</v>
       </c>
       <c r="G189">
-        <v>388.2370871417029</v>
-      </c>
-      <c r="H189">
         <v>0.6617634911992627</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:7">
       <c r="A190">
         <v>5407.2781</v>
       </c>
@@ -5329,16 +4759,13 @@
         <v>1567365596.041324</v>
       </c>
       <c r="F190">
-        <v>-189201983.6063914</v>
+        <v>-3412.594294735062</v>
       </c>
       <c r="G190">
-        <v>670.853001182327</v>
-      </c>
-      <c r="H190">
         <v>0.8816926188780145</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:7">
       <c r="A191">
         <v>5410.6373</v>
       </c>
@@ -5355,16 +4782,13 @@
         <v>12367094891.97452</v>
       </c>
       <c r="F191">
-        <v>-4287876.176824187</v>
+        <v>-77.38742644490719</v>
       </c>
       <c r="G191">
-        <v>310.2846618025884</v>
-      </c>
-      <c r="H191">
         <v>0.5541189401764852</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:7">
       <c r="A192">
         <v>5412.414</v>
       </c>
@@ -5381,16 +4805,13 @@
         <v>5906249874.502076</v>
       </c>
       <c r="F192">
-        <v>-42117111.40188096</v>
+        <v>-760.3783763886896</v>
       </c>
       <c r="G192">
-        <v>603.7486770689545</v>
-      </c>
-      <c r="H192">
         <v>0.8020125888088112</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:7">
       <c r="A193">
         <v>5416.7047</v>
       </c>
@@ -5407,16 +4828,13 @@
         <v>4232863799.839677</v>
       </c>
       <c r="F193">
-        <v>-64447134.53422201</v>
+        <v>-1164.445180232299</v>
       </c>
       <c r="G193">
-        <v>675.2201181398445</v>
-      </c>
-      <c r="H193">
         <v>0.8289327234798494</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:7">
       <c r="A194">
         <v>5425.5759</v>
       </c>
@@ -5433,16 +4851,13 @@
         <v>4121562916.146234</v>
       </c>
       <c r="F194">
-        <v>-27183168.07370747</v>
+        <v>-491.9559248529326</v>
       </c>
       <c r="G194">
-        <v>679.641627236473</v>
-      </c>
-      <c r="H194">
         <v>0.8464184414171511</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:7">
       <c r="A195">
         <v>5434.458</v>
       </c>
@@ -5459,16 +4874,13 @@
         <v>11359712290.86633</v>
       </c>
       <c r="F195">
-        <v>-8282724.400745911</v>
+        <v>-150.1444377983403</v>
       </c>
       <c r="G195">
-        <v>347.5401751906177</v>
-      </c>
-      <c r="H195">
         <v>0.6537951432742402</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:7">
       <c r="A196">
         <v>5436.0344</v>
       </c>
@@ -5485,16 +4897,13 @@
         <v>1843734540.786068</v>
       </c>
       <c r="F196">
-        <v>-403643587.2450528</v>
+        <v>-7319.14901264842</v>
       </c>
       <c r="G196">
-        <v>716.9384274599745</v>
-      </c>
-      <c r="H196">
         <v>0.8691136985161847</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:7">
       <c r="A197">
         <v>5446.5558</v>
       </c>
@@ -5511,16 +4920,13 @@
         <v>7275768074.80712</v>
       </c>
       <c r="F197">
-        <v>-31436809.1602902</v>
+        <v>-571.1373344554517</v>
       </c>
       <c r="G197">
-        <v>577.9470411635199</v>
-      </c>
-      <c r="H197">
         <v>0.7937729383754594</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:7">
       <c r="A198">
         <v>5464.4776</v>
       </c>
@@ -5537,16 +4943,13 @@
         <v>9792396432.13871</v>
       </c>
       <c r="F198">
-        <v>-19591069.811365</v>
+        <v>-357.097530119642</v>
       </c>
       <c r="G198">
-        <v>515.7032952568153</v>
-      </c>
-      <c r="H198">
         <v>0.7503593030433957</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:7">
       <c r="A199">
         <v>5464.7944</v>
       </c>
@@ -5563,16 +4966,13 @@
         <v>8437118594.548758</v>
       </c>
       <c r="F199">
-        <v>-23515322.06017706</v>
+        <v>-428.6520036918503</v>
       </c>
       <c r="G199">
-        <v>554.0746100250157</v>
-      </c>
-      <c r="H199">
         <v>0.7789101631867273</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:7">
       <c r="A200">
         <v>5465.798</v>
       </c>
@@ -5589,16 +4989,13 @@
         <v>11237963008.76139</v>
       </c>
       <c r="F200">
-        <v>184435.4658979074</v>
+        <v>3.362618558753317</v>
       </c>
       <c r="G200">
-        <v>202.9405577513195</v>
-      </c>
-      <c r="H200">
         <v>0.4270569785199546</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:7">
       <c r="A201">
         <v>5467.9152</v>
       </c>
@@ -5615,16 +5012,13 @@
         <v>11979661081.62338</v>
       </c>
       <c r="F201">
-        <v>-11214074.06338916</v>
+        <v>-204.5337945402195</v>
       </c>
       <c r="G201">
-        <v>405.7239565693343</v>
-      </c>
-      <c r="H201">
         <v>0.7065033376643086</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:7">
       <c r="A202">
         <v>5468.507</v>
       </c>
@@ -5641,16 +5035,13 @@
         <v>10581415454.18473</v>
       </c>
       <c r="F202">
-        <v>-2919471.34472396</v>
+        <v>-53.25404051049242</v>
       </c>
       <c r="G202">
-        <v>191.8756990250914</v>
-      </c>
-      <c r="H202">
         <v>0.3752252776329356</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:7">
       <c r="A203">
         <v>5475.4215</v>
       </c>
@@ -5667,16 +5058,13 @@
         <v>12045073924.69949</v>
       </c>
       <c r="F203">
-        <v>-13759448.8602562</v>
+        <v>-251.3034711282287</v>
       </c>
       <c r="G203">
-        <v>410.6429861223715</v>
-      </c>
-      <c r="H203">
         <v>0.7125699129741377</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:7">
       <c r="A204">
         <v>5478.086</v>
       </c>
@@ -5693,16 +5081,13 @@
         <v>8252685756.299269</v>
       </c>
       <c r="F204">
-        <v>-25912469.66578241</v>
+        <v>-473.4975049931448</v>
       </c>
       <c r="G204">
-        <v>514.4222097389581</v>
-      </c>
-      <c r="H204">
         <v>0.7765978621395745</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:7">
       <c r="A205">
         <v>5484.6223</v>
       </c>
@@ -5719,16 +5104,13 @@
         <v>12311670360.79078</v>
       </c>
       <c r="F205">
-        <v>-3151584.137868674</v>
+        <v>-57.65742633984399</v>
       </c>
       <c r="G205">
-        <v>224.1082449474177</v>
-      </c>
-      <c r="H205">
         <v>0.5007895309312718</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:7">
       <c r="A206">
         <v>5495.0251</v>
       </c>
@@ -5745,16 +5127,13 @@
         <v>10445730066.95593</v>
       </c>
       <c r="F206">
-        <v>-1981927.47004629</v>
+        <v>-36.32762215808068</v>
       </c>
       <c r="G206">
-        <v>163.6712040033631</v>
-      </c>
-      <c r="H206">
         <v>0.4137970308145992</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:7">
       <c r="A207">
         <v>5499.0434</v>
       </c>
@@ -5771,16 +5150,13 @@
         <v>3405315274.532257</v>
       </c>
       <c r="F207">
-        <v>-313219047.5269222</v>
+        <v>-5745.338167564248</v>
       </c>
       <c r="G207">
-        <v>681.4650208204075</v>
-      </c>
-      <c r="H207">
         <v>0.8263359788918466</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:7">
       <c r="A208">
         <v>5502.9937</v>
       </c>
@@ -5797,16 +5173,13 @@
         <v>4272510666.098863</v>
       </c>
       <c r="F208">
-        <v>-114104281.716613</v>
+        <v>-2094.503615451918</v>
       </c>
       <c r="G208">
-        <v>593.8109273766565</v>
-      </c>
-      <c r="H208">
         <v>0.8196025665560311</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:7">
       <c r="A209">
         <v>5508.309</v>
       </c>
@@ -5823,16 +5196,13 @@
         <v>3015684467.253445</v>
       </c>
       <c r="F209">
-        <v>-368992270.7923399</v>
+        <v>-6779.783828115075</v>
       </c>
       <c r="G209">
-        <v>680.3187193694172</v>
-      </c>
-      <c r="H209">
         <v>0.8289500641165071</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:7">
       <c r="A210">
         <v>5523.9805</v>
       </c>
@@ -5849,16 +5219,13 @@
         <v>11833387629.67553</v>
       </c>
       <c r="F210">
-        <v>-2400122.787641696</v>
+        <v>-44.2247286854041</v>
       </c>
       <c r="G210">
-        <v>195.3759338266332</v>
-      </c>
-      <c r="H210">
         <v>0.4675639065429461</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:7">
       <c r="A211">
         <v>5527.0791</v>
       </c>
@@ -5875,16 +5242,13 @@
         <v>12805598397.73617</v>
       </c>
       <c r="F211">
-        <v>-4056788.930199686</v>
+        <v>-74.79244712943455</v>
       </c>
       <c r="G211">
-        <v>244.0830023639354</v>
-      </c>
-      <c r="H211">
         <v>0.559525276713932</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:7">
       <c r="A212">
         <v>5544.7292</v>
       </c>
@@ -5901,16 +5265,13 @@
         <v>12719578267.37571</v>
       </c>
       <c r="F212">
-        <v>-7216303.456150872</v>
+        <v>-133.467308603313</v>
       </c>
       <c r="G212">
-        <v>329.8148435956174</v>
-      </c>
-      <c r="H212">
         <v>0.6039017334719752</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:7">
       <c r="A213">
         <v>5545.4754</v>
       </c>
@@ -5927,16 +5288,13 @@
         <v>12778905358.26233</v>
       </c>
       <c r="F213">
-        <v>-5864642.394640255</v>
+        <v>-108.4826000430237</v>
       </c>
       <c r="G213">
-        <v>324.3643904619492</v>
-      </c>
-      <c r="H213">
         <v>0.6146113816747403</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:7">
       <c r="A214">
         <v>5561.7557</v>
       </c>
@@ -5953,16 +5311,13 @@
         <v>12682549762.33303</v>
       </c>
       <c r="F214">
-        <v>-3993042.750522017</v>
+        <v>-74.07907188032208</v>
       </c>
       <c r="G214">
-        <v>253.341683606782</v>
-      </c>
-      <c r="H214">
         <v>0.542108343913299</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:7">
       <c r="A215">
         <v>5564.2512</v>
       </c>
@@ -5979,16 +5334,13 @@
         <v>12780577453.09915</v>
       </c>
       <c r="F215">
-        <v>-6092841.79958324</v>
+        <v>-113.0853728755675</v>
       </c>
       <c r="G215">
-        <v>350.2090231170371</v>
-      </c>
-      <c r="H215">
         <v>0.5964148216874821</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:7">
       <c r="A216">
         <v>5567.2496</v>
       </c>
@@ -6005,16 +5357,13 @@
         <v>10549583470.00189</v>
       </c>
       <c r="F216">
-        <v>-15901347.64161203</v>
+        <v>-295.2939851440493</v>
       </c>
       <c r="G216">
-        <v>468.488853923797</v>
-      </c>
-      <c r="H216">
         <v>0.7101584138005879</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:7">
       <c r="A217">
         <v>5577.6371</v>
       </c>
@@ -6031,16 +5380,13 @@
         <v>7176422338.194611</v>
       </c>
       <c r="F217">
-        <v>-31235422.19830094</v>
+        <v>-581.135948842975</v>
       </c>
       <c r="G217">
-        <v>558.9896774259148</v>
-      </c>
-      <c r="H217">
         <v>0.7888838103736152</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:7">
       <c r="A218">
         <v>5588.3071</v>
       </c>
@@ -6057,16 +5403,13 @@
         <v>3433859714.865366</v>
       </c>
       <c r="F218">
-        <v>-34472865.50839001</v>
+        <v>-642.5957485665663</v>
       </c>
       <c r="G218">
-        <v>622.2980323971223</v>
-      </c>
-      <c r="H218">
         <v>0.8444069005414708</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:7">
       <c r="A219">
         <v>5589.1254</v>
       </c>
@@ -6083,16 +5426,13 @@
         <v>10281167968.48408</v>
       </c>
       <c r="F219">
-        <v>-910345.1037276204</v>
+        <v>-16.97186076346861</v>
       </c>
       <c r="G219">
-        <v>171.6432888880289</v>
-      </c>
-      <c r="H219">
         <v>0.4022140445113204</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:7">
       <c r="A220">
         <v>5617.2028</v>
       </c>
@@ -6109,16 +5449,13 @@
         <v>3296325462.464709</v>
       </c>
       <c r="F220">
-        <v>-26152691.87105436</v>
+        <v>-490.0233028984186</v>
       </c>
       <c r="G220">
-        <v>645.7820504085362</v>
-      </c>
-      <c r="H220">
         <v>0.8542180943277856</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:7">
       <c r="A221">
         <v>5620.1925</v>
       </c>
@@ -6135,16 +5472,13 @@
         <v>12740007782.15816</v>
       </c>
       <c r="F221">
-        <v>-4013588.423720449</v>
+        <v>-75.24258138924256</v>
       </c>
       <c r="G221">
-        <v>250.7075251640749</v>
-      </c>
-      <c r="H221">
         <v>0.5294172495756938</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:7">
       <c r="A222">
         <v>5625.5831</v>
       </c>
@@ -6161,16 +5495,13 @@
         <v>12150301122.18524</v>
       </c>
       <c r="F222">
-        <v>-3127837.764221967</v>
+        <v>-58.69369958952264</v>
       </c>
       <c r="G222">
-        <v>293.1000200226537</v>
-      </c>
-      <c r="H222">
         <v>0.5111060858887471</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:7">
       <c r="A223">
         <v>5637.3869</v>
       </c>
@@ -6187,16 +5518,13 @@
         <v>9859693207.608702</v>
       </c>
       <c r="F223">
-        <v>-201477.6097796771</v>
+        <v>-3.788647354468723</v>
       </c>
       <c r="G223">
-        <v>175.4917888145211</v>
-      </c>
-      <c r="H223">
         <v>0.375826247406995</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:7">
       <c r="A224">
         <v>5638.2607</v>
       </c>
@@ -6213,16 +5541,13 @@
         <v>6989428374.619141</v>
       </c>
       <c r="F224">
-        <v>3236133.423616712</v>
+        <v>60.86269146913705</v>
       </c>
       <c r="G224">
-        <v>196.7330270168722</v>
-      </c>
-      <c r="H224">
         <v>0.2284745622604061</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:7">
       <c r="A225">
         <v>5644.3175</v>
       </c>
@@ -6239,16 +5564,13 @@
         <v>3028331310.868876</v>
       </c>
       <c r="F225">
-        <v>-6845332.131148668</v>
+        <v>-128.8799882922709</v>
       </c>
       <c r="G225">
-        <v>159.3420947762234</v>
-      </c>
-      <c r="H225">
         <v>0.110602302589226</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:7">
       <c r="A226">
         <v>5651.5554</v>
       </c>
@@ -6265,16 +5587,13 @@
         <v>9087517066.428583</v>
       </c>
       <c r="F226">
-        <v>-1608087.826350056</v>
+        <v>-30.31497589337262</v>
       </c>
       <c r="G226">
-        <v>122.0058204779061</v>
-      </c>
-      <c r="H226">
         <v>0.3720456140310324</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:7">
       <c r="A227">
         <v>5653.0375</v>
       </c>
@@ -6291,16 +5610,13 @@
         <v>5828059161.289463</v>
       </c>
       <c r="F227">
-        <v>4986684.82166788</v>
+        <v>94.03150078012695</v>
       </c>
       <c r="G227">
-        <v>196.2187752029738</v>
-      </c>
-      <c r="H227">
         <v>0.2041294981135466</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:7">
       <c r="A228">
         <v>5653.8867</v>
       </c>
@@ -6317,16 +5633,13 @@
         <v>7991770743.239759</v>
       </c>
       <c r="F228">
-        <v>1432948.503959238</v>
+        <v>27.0244711889006</v>
       </c>
       <c r="G228">
-        <v>153.7699947650628</v>
-      </c>
-      <c r="H228">
         <v>0.2839750216764054</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:7">
       <c r="A229">
         <v>5656.7459</v>
       </c>
@@ -6343,16 +5656,13 @@
         <v>10618267654.22149</v>
       </c>
       <c r="F229">
-        <v>-5929749.582284604</v>
+        <v>-111.8877725623554</v>
       </c>
       <c r="G229">
-        <v>211.9893403883534</v>
-      </c>
-      <c r="H229">
         <v>0.4988726564022297</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:7">
       <c r="A230">
         <v>5661.1454</v>
       </c>
@@ -6369,16 +5679,13 @@
         <v>5156385501.395305</v>
       </c>
       <c r="F230">
-        <v>-34078.86381077689</v>
+        <v>-0.6435299661964716</v>
       </c>
       <c r="G230">
-        <v>42.36491902258877</v>
-      </c>
-      <c r="H230">
         <v>0.206542024531806</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:7">
       <c r="A231">
         <v>5662.9166</v>
       </c>
@@ -6395,16 +5702,13 @@
         <v>6815501255.720757</v>
       </c>
       <c r="F231">
-        <v>2008396.605063936</v>
+        <v>37.93753977143201</v>
       </c>
       <c r="G231">
-        <v>153.5247981838676</v>
-      </c>
-      <c r="H231">
         <v>0.2413640935618385</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:7">
       <c r="A232">
         <v>5664.0877</v>
       </c>
@@ -6421,16 +5725,13 @@
         <v>9983117073.607582</v>
       </c>
       <c r="F232">
-        <v>-19837515.83290631</v>
+        <v>-374.7979544914238</v>
       </c>
       <c r="G232">
-        <v>455.1863027942478</v>
-      </c>
-      <c r="H232">
         <v>0.7385044210989538</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:7">
       <c r="A233">
         <v>5679.2603</v>
       </c>
@@ -6447,16 +5748,13 @@
         <v>2247083260.588636</v>
       </c>
       <c r="F233">
-        <v>29930100.34894649</v>
+        <v>566.9952994316786</v>
       </c>
       <c r="G233">
-        <v>147.8042628837914</v>
-      </c>
-      <c r="H233">
         <v>0.07544798434799482</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:7">
       <c r="A234">
         <v>5679.9544</v>
       </c>
@@ -6473,16 +5771,13 @@
         <v>1528419535.869844</v>
       </c>
       <c r="F234">
-        <v>28945235.59878176</v>
+        <v>548.4052575131544</v>
       </c>
       <c r="G234">
-        <v>258.625851696873</v>
-      </c>
-      <c r="H234">
         <v>0.05424805620580386</v>
       </c>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:7">
       <c r="A235">
         <v>5680.5988</v>
       </c>
@@ -6499,16 +5794,13 @@
         <v>12001293394.51251</v>
       </c>
       <c r="F235">
-        <v>-7206454.367616752</v>
+        <v>-136.5512075498792</v>
       </c>
       <c r="G235">
-        <v>337.7587115346472</v>
-      </c>
-      <c r="H235">
         <v>0.5710982904479225</v>
       </c>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:7">
       <c r="A236">
         <v>5681.8166</v>
       </c>
@@ -6525,16 +5817,13 @@
         <v>3398931128.823686</v>
       </c>
       <c r="F236">
-        <v>7284116.232829064</v>
+        <v>138.0523110574135</v>
       </c>
       <c r="G236">
-        <v>211.0539491664019</v>
-      </c>
-      <c r="H236">
         <v>0.116806071895313</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:7">
       <c r="A237">
         <v>5688.1081</v>
       </c>
@@ -6551,16 +5840,13 @@
         <v>12295416466.61321</v>
       </c>
       <c r="F237">
-        <v>-11165121.89909092</v>
+        <v>-211.841600427221</v>
       </c>
       <c r="G237">
-        <v>442.7230641088756</v>
-      </c>
-      <c r="H237">
         <v>0.6489514514809104</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:7">
       <c r="A238">
         <v>5693.0762</v>
       </c>
@@ -6577,16 +5863,13 @@
         <v>10896165683.94891</v>
       </c>
       <c r="F238">
-        <v>-2016269.830171298</v>
+        <v>-38.28910815363335</v>
       </c>
       <c r="G238">
-        <v>210.6365328673202</v>
-      </c>
-      <c r="H238">
         <v>0.4287399247731091</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:7">
       <c r="A239">
         <v>5697.67</v>
       </c>
@@ -6603,16 +5886,13 @@
         <v>4186902150.103707</v>
       </c>
       <c r="F239">
-        <v>4012881.704719041</v>
+        <v>76.26640613889639</v>
       </c>
       <c r="G239">
-        <v>231.5133756899312</v>
-      </c>
-      <c r="H239">
         <v>0.1437331620910733</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:7">
       <c r="A240">
         <v>5699.6009</v>
       </c>
@@ -6629,16 +5909,13 @@
         <v>4903801684.674041</v>
       </c>
       <c r="F240">
-        <v>10836320.00220386</v>
+        <v>206.018344308799</v>
       </c>
       <c r="G240">
-        <v>226.1750588973376</v>
-      </c>
-      <c r="H240">
         <v>0.1650267627940821</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:7">
       <c r="A241">
         <v>5703.1265</v>
       </c>
@@ -6655,16 +5932,13 @@
         <v>9915790039.894182</v>
       </c>
       <c r="F241">
-        <v>-18036890.55653952</v>
+        <v>-343.126867707315</v>
       </c>
       <c r="G241">
-        <v>520.4067162609281</v>
-      </c>
-      <c r="H241">
         <v>0.7267108256875683</v>
       </c>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:7">
       <c r="A242">
         <v>5706.3164</v>
       </c>
@@ -6681,16 +5955,13 @@
         <v>5364632842.702776</v>
       </c>
       <c r="F242">
-        <v>4316092.039936804</v>
+        <v>82.15347854260864</v>
       </c>
       <c r="G242">
-        <v>78.80542461884487</v>
-      </c>
-      <c r="H242">
         <v>0.2054965874237704</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:7">
       <c r="A243">
         <v>5707.0475</v>
       </c>
@@ -6707,16 +5978,13 @@
         <v>10598297693.42808</v>
       </c>
       <c r="F243">
-        <v>-749990.8189671782</v>
+        <v>-14.27733149768546</v>
       </c>
       <c r="G243">
-        <v>215.373900064697</v>
-      </c>
-      <c r="H243">
         <v>0.4049581046399371</v>
       </c>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:7">
       <c r="A244">
         <v>5710.9623</v>
       </c>
@@ -6733,16 +6001,13 @@
         <v>7659928564.075643</v>
       </c>
       <c r="F244">
-        <v>-23842539.29738018</v>
+        <v>-454.194462544611</v>
       </c>
       <c r="G244">
-        <v>509.1938432839436</v>
-      </c>
-      <c r="H244">
         <v>0.7572922542213694</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:7">
       <c r="A245">
         <v>5711.5164</v>
       </c>
@@ -6759,16 +6024,13 @@
         <v>3119747818.039159</v>
       </c>
       <c r="F245">
-        <v>4723777.351215108</v>
+        <v>89.99540482388329</v>
       </c>
       <c r="G245">
-        <v>131.2227948456307</v>
-      </c>
-      <c r="H245">
         <v>0.1148579951162548</v>
       </c>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:7">
       <c r="A246">
         <v>5713.7163</v>
       </c>
@@ -6785,16 +6047,13 @@
         <v>13263625019.53271</v>
       </c>
       <c r="F246">
-        <v>-3722096.286740248</v>
+        <v>-70.93914934587029</v>
       </c>
       <c r="G246">
-        <v>278.0852152709296</v>
-      </c>
-      <c r="H246">
         <v>0.5375813788555228</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:7">
       <c r="A247">
         <v>5716.1345</v>
       </c>
@@ -6811,16 +6070,13 @@
         <v>1867823911.037834</v>
       </c>
       <c r="F247">
-        <v>36915132.16371384</v>
+        <v>703.8599387970917</v>
       </c>
       <c r="G247">
-        <v>57.69138280990988</v>
-      </c>
-      <c r="H247">
         <v>0.06757644868917934</v>
       </c>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:7">
       <c r="A248">
         <v>5726.0428</v>
       </c>
@@ -6837,16 +6093,13 @@
         <v>1691739126.604408</v>
       </c>
       <c r="F248">
-        <v>23519326.46908582</v>
+        <v>449.2199320202233</v>
       </c>
       <c r="G248">
-        <v>172.7746623561969</v>
-      </c>
-      <c r="H248">
         <v>0.05850956438746335</v>
       </c>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:7">
       <c r="A249">
         <v>5733.3522</v>
       </c>
@@ -6863,16 +6116,13 @@
         <v>12750703148.693</v>
       </c>
       <c r="F249">
-        <v>-5982422.997667843</v>
+        <v>-114.4103883913527</v>
       </c>
       <c r="G249">
-        <v>292.8195767894628</v>
-      </c>
-      <c r="H249">
         <v>0.570149960651714</v>
       </c>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:7">
       <c r="A250">
         <v>5733.8861</v>
       </c>
@@ -6889,16 +6139,13 @@
         <v>3890180769.22627</v>
       </c>
       <c r="F250">
-        <v>15353945.1101766</v>
+        <v>293.6625322564381</v>
       </c>
       <c r="G250">
-        <v>135.9392874703295</v>
-      </c>
-      <c r="H250">
         <v>0.1488789939785273</v>
       </c>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:7">
       <c r="A251">
         <v>5743.4411</v>
       </c>
@@ -6915,16 +6162,13 @@
         <v>9298329284.585428</v>
       </c>
       <c r="F251">
-        <v>-54868.69214878235</v>
+        <v>-1.051178172548014</v>
       </c>
       <c r="G251">
-        <v>177.4710211691086</v>
-      </c>
-      <c r="H251">
         <v>0.3407291894690964</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:7">
       <c r="A252">
         <v>5744.5529</v>
       </c>
@@ -6941,16 +6185,13 @@
         <v>3652379040.419583</v>
       </c>
       <c r="F252">
-        <v>12278059.49792839</v>
+        <v>235.2694656762681</v>
       </c>
       <c r="G252">
-        <v>208.7490275865416</v>
-      </c>
-      <c r="H252">
         <v>0.1257828799788326</v>
       </c>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:7">
       <c r="A253">
         <v>5753.6274</v>
       </c>
@@ -6967,16 +6208,13 @@
         <v>12297377696.15588</v>
       </c>
       <c r="F253">
-        <v>-6471830.69757905</v>
+        <v>-124.2077448920831</v>
       </c>
       <c r="G253">
-        <v>343.892658511731</v>
-      </c>
-      <c r="H253">
         <v>0.5406763736894107</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:7">
       <c r="A254">
         <v>5754.7184</v>
       </c>
@@ -6993,16 +6231,13 @@
         <v>11728782322.6547</v>
       </c>
       <c r="F254">
-        <v>-13014050.44281741</v>
+        <v>-249.8138260556844</v>
       </c>
       <c r="G254">
-        <v>421.9700671478758</v>
-      </c>
-      <c r="H254">
         <v>0.6841031246416768</v>
       </c>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:7">
       <c r="A255">
         <v>5755.9986</v>
       </c>
@@ -7019,16 +6254,13 @@
         <v>4663863884.172993</v>
       </c>
       <c r="F255">
-        <v>3843561.521302867</v>
+        <v>73.7962184676544</v>
       </c>
       <c r="G255">
-        <v>203.1255855498597</v>
-      </c>
-      <c r="H255">
         <v>0.1537858319721854</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:7">
       <c r="A256">
         <v>5760.8595</v>
       </c>
@@ -7045,16 +6277,13 @@
         <v>2589328248.016824</v>
       </c>
       <c r="F256">
-        <v>25366999.64077644</v>
+        <v>487.4563458406394</v>
       </c>
       <c r="G256">
-        <v>31.22372191764283</v>
-      </c>
-      <c r="H256">
         <v>0.09564396247823714</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:7">
       <c r="A257">
         <v>5761.9422</v>
       </c>
@@ -7071,16 +6300,13 @@
         <v>7814001933.079844</v>
       </c>
       <c r="F257">
-        <v>2689953.093224318</v>
+        <v>51.700317533263</v>
       </c>
       <c r="G257">
-        <v>213.3220075740043</v>
-      </c>
-      <c r="H257">
         <v>0.2565716657221331</v>
       </c>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:7">
       <c r="A258">
         <v>5762.8537</v>
       </c>
@@ -7097,16 +6323,13 @@
         <v>1102718506.925474</v>
       </c>
       <c r="F258">
-        <v>-20957944.45015552</v>
+        <v>-402.8709155509284</v>
       </c>
       <c r="G258">
-        <v>234.0968782828236</v>
-      </c>
-      <c r="H258">
         <v>0.04151733430745241</v>
       </c>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:7">
       <c r="A259">
         <v>5764.0117</v>
       </c>
@@ -7123,16 +6346,13 @@
         <v>8893189822.746149</v>
       </c>
       <c r="F259">
-        <v>-1011347.244605607</v>
+        <v>-19.44485538565337</v>
       </c>
       <c r="G259">
-        <v>187.2398782436362</v>
-      </c>
-      <c r="H259">
         <v>0.312226736548865</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:7">
       <c r="A260">
         <v>5770.9229</v>
       </c>
@@ -7149,16 +6369,13 @@
         <v>2298181086.071551</v>
       </c>
       <c r="F260">
-        <v>77860202.31651072</v>
+        <v>1498.788762497404</v>
       </c>
       <c r="G260">
-        <v>228.574673124128</v>
-      </c>
-      <c r="H260">
         <v>0.08591485240877983</v>
       </c>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:7">
       <c r="A261">
         <v>5776.6821</v>
       </c>
@@ -7175,16 +6392,13 @@
         <v>12819149730.12114</v>
       </c>
       <c r="F261">
-        <v>-6538778.685229259</v>
+        <v>-125.9954348025336</v>
       </c>
       <c r="G261">
-        <v>280.243787914125</v>
-      </c>
-      <c r="H261">
         <v>0.5758663502578396</v>
       </c>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:7">
       <c r="A262">
         <v>5782.2031</v>
       </c>
@@ -7201,16 +6415,13 @@
         <v>11590855192.04243</v>
       </c>
       <c r="F262">
-        <v>-209442.1061749894</v>
+        <v>-4.039587213276233</v>
       </c>
       <c r="G262">
-        <v>243.6829921484749</v>
-      </c>
-      <c r="H262">
         <v>0.4068513993866343</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:7">
       <c r="A263">
         <v>5782.4074</v>
       </c>
@@ -7227,16 +6438,13 @@
         <v>7090627578.127073</v>
       </c>
       <c r="F263">
-        <v>809432.1742566603</v>
+        <v>15.6123649559789</v>
       </c>
       <c r="G263">
-        <v>171.0905238982596</v>
-      </c>
-      <c r="H263">
         <v>0.2621099459086483</v>
       </c>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:7">
       <c r="A264">
         <v>5786.2625</v>
       </c>
@@ -7253,16 +6461,13 @@
         <v>8406628971.141353</v>
       </c>
       <c r="F264">
-        <v>4020000.278322522</v>
+        <v>77.58965753050521</v>
       </c>
       <c r="G264">
-        <v>222.7876059399582</v>
-      </c>
-      <c r="H264">
         <v>0.2850912763441859</v>
       </c>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:7">
       <c r="A265">
         <v>5793.1299</v>
       </c>
@@ -7279,16 +6484,13 @@
         <v>2636949287.509439</v>
       </c>
       <c r="F265">
-        <v>34856387.18156535</v>
+        <v>673.5583429579615</v>
       </c>
       <c r="G265">
-        <v>196.6486787283332</v>
-      </c>
-      <c r="H265">
         <v>0.09635678491650046</v>
       </c>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:7">
       <c r="A266">
         <v>5795.5214</v>
       </c>
@@ -7305,16 +6507,13 @@
         <v>9601909371.648676</v>
       </c>
       <c r="F266">
-        <v>-1108894.318185029</v>
+        <v>-21.4369126771004</v>
       </c>
       <c r="G266">
-        <v>186.2218727446886</v>
-      </c>
-      <c r="H266">
         <v>0.3581318548226752</v>
       </c>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:7">
       <c r="A267">
         <v>5808.3349</v>
       </c>
@@ -7331,16 +6530,13 @@
         <v>11948453923.30882</v>
       </c>
       <c r="F267">
-        <v>-7272012.683518213</v>
+        <v>-140.8919037896548</v>
       </c>
       <c r="G267">
-        <v>320.0079319939016</v>
-      </c>
-      <c r="H267">
         <v>0.513701120096886</v>
       </c>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:7">
       <c r="A268">
         <v>5809.3941</v>
       </c>
@@ -7357,16 +6553,13 @@
         <v>2817778131.22779</v>
       </c>
       <c r="F268">
-        <v>17412012.16782926</v>
+        <v>337.411060727054</v>
       </c>
       <c r="G268">
-        <v>149.6538387839017</v>
-      </c>
-      <c r="H268">
         <v>0.0865426970784885</v>
       </c>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:7">
       <c r="A269">
         <v>5809.5858</v>
       </c>
@@ -7383,16 +6576,13 @@
         <v>1026382277.912191</v>
       </c>
       <c r="F269">
-        <v>45201568.92786155</v>
+        <v>875.9480198416351</v>
       </c>
       <c r="G269">
-        <v>247.6947321306367</v>
-      </c>
-      <c r="H269">
         <v>0.03781413557243707</v>
       </c>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:7">
       <c r="A270">
         <v>5813.5259</v>
       </c>
@@ -7409,16 +6599,13 @@
         <v>3677924007.161784</v>
       </c>
       <c r="F270">
-        <v>9646665.104001032</v>
+        <v>187.0666641411309</v>
       </c>
       <c r="G270">
-        <v>201.1155719441867</v>
-      </c>
-      <c r="H270">
         <v>0.1219908783055612</v>
       </c>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:7">
       <c r="A271">
         <v>5816.4197</v>
       </c>
@@ -7435,16 +6622,13 @@
         <v>6853346499.488369</v>
       </c>
       <c r="F271">
-        <v>3944747.521619114</v>
+        <v>76.53400885768581</v>
       </c>
       <c r="G271">
-        <v>149.4730732894459</v>
-      </c>
-      <c r="H271">
         <v>0.2417181014484968</v>
       </c>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:7">
       <c r="A272">
         <v>5818.6893</v>
       </c>
@@ -7461,16 +6645,13 @@
         <v>3144713581.889411</v>
       </c>
       <c r="F272">
-        <v>9945805.053879214</v>
+        <v>193.0387235599333</v>
       </c>
       <c r="G272">
-        <v>20.60893387877744</v>
-      </c>
-      <c r="H272">
         <v>0.1259895707218381</v>
       </c>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:7">
       <c r="A273">
         <v>5829.4928</v>
       </c>
@@ -7487,16 +6668,13 @@
         <v>4058394964.219866</v>
       </c>
       <c r="F273">
-        <v>4667681.502057527</v>
+        <v>90.76357366679218</v>
       </c>
       <c r="G273">
-        <v>210.8500893461524</v>
-      </c>
-      <c r="H273">
         <v>0.1255756009848736</v>
       </c>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:7">
       <c r="A274">
         <v>5836.7184</v>
       </c>
@@ -7513,16 +6691,13 @@
         <v>4444496096.342883</v>
       </c>
       <c r="F274">
-        <v>8492518.165005345</v>
+        <v>165.3425736574491</v>
       </c>
       <c r="G274">
-        <v>118.135329844852</v>
-      </c>
-      <c r="H274">
         <v>0.1528794762269441</v>
       </c>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:7">
       <c r="A275">
         <v>5839.3196</v>
       </c>
@@ -7539,16 +6714,13 @@
         <v>3075739332.563677</v>
       </c>
       <c r="F275">
-        <v>26177414.23509444</v>
+        <v>509.880793230748</v>
       </c>
       <c r="G275">
-        <v>251.5675018282688</v>
-      </c>
-      <c r="H275">
         <v>0.1070635693398051</v>
       </c>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:7">
       <c r="A276">
         <v>5839.9903</v>
       </c>
@@ -7565,16 +6737,13 @@
         <v>5501225333.187243</v>
       </c>
       <c r="F276">
-        <v>2732798.167033207</v>
+        <v>53.23524664934886</v>
       </c>
       <c r="G276">
-        <v>200.2042000006331</v>
-      </c>
-      <c r="H276">
         <v>0.1974303798161461</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:7">
       <c r="A277">
         <v>5846.5391</v>
       </c>
@@ -7591,16 +6760,13 @@
         <v>989760204.1558378</v>
       </c>
       <c r="F277">
-        <v>192639497.3788427</v>
+        <v>3756.849684469179</v>
       </c>
       <c r="G277">
-        <v>225.6184030490063</v>
-      </c>
-      <c r="H277">
         <v>0.04023402996429426</v>
       </c>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:7">
       <c r="A278">
         <v>5846.9073</v>
       </c>
@@ -7617,16 +6783,13 @@
         <v>1631355032.420958</v>
       </c>
       <c r="F278">
-        <v>34740371.84954984</v>
+        <v>677.5481343922837</v>
       </c>
       <c r="G278">
-        <v>128.1842017920085</v>
-      </c>
-      <c r="H278">
         <v>0.07042988772830405</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:7">
       <c r="A279">
         <v>5851.3056</v>
       </c>
@@ -7643,16 +6806,13 @@
         <v>2727072752.833871</v>
       </c>
       <c r="F279">
-        <v>17931099.33037942</v>
+        <v>349.9767447347311</v>
       </c>
       <c r="G279">
-        <v>133.2113624649405</v>
-      </c>
-      <c r="H279">
         <v>0.08884629654993814</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:7">
       <c r="A280">
         <v>5852.8271</v>
       </c>
@@ -7669,16 +6829,13 @@
         <v>1110320495.057286</v>
       </c>
       <c r="F280">
-        <v>6686754.498891828</v>
+        <v>130.5451655380258</v>
       </c>
       <c r="G280">
-        <v>291.9643757297873</v>
-      </c>
-      <c r="H280">
         <v>0.05827332964546672</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:7">
       <c r="A281">
         <v>5853.8409</v>
       </c>
@@ -7695,16 +6852,13 @@
         <v>10442866379.15743</v>
       </c>
       <c r="F281">
-        <v>-2066486.197056184</v>
+        <v>-40.35088683049963</v>
       </c>
       <c r="G281">
-        <v>250.9434522490381</v>
-      </c>
-      <c r="H281">
         <v>0.4102428024404212</v>
       </c>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:7">
       <c r="A282">
         <v>5854.7708</v>
       </c>
@@ -7721,16 +6875,13 @@
         <v>2910596616.173574</v>
       </c>
       <c r="F282">
-        <v>-4730770.867157295</v>
+        <v>-92.38927233476744</v>
       </c>
       <c r="G282">
-        <v>302.1084108215355</v>
-      </c>
-      <c r="H282">
         <v>0.08509883732321011</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:7">
       <c r="A283">
         <v>5856.6996</v>
       </c>
@@ -7747,16 +6898,13 @@
         <v>6557051766.791418</v>
       </c>
       <c r="F283">
-        <v>4187252.08519888</v>
+        <v>81.80158464833248</v>
       </c>
       <c r="G283">
-        <v>250.8209647597078</v>
-      </c>
-      <c r="H283">
         <v>0.2353750486133454</v>
       </c>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:7">
       <c r="A284">
         <v>5857.7113</v>
       </c>
@@ -7773,16 +6921,13 @@
         <v>9624811293.258402</v>
       </c>
       <c r="F284">
-        <v>397448.2986713732</v>
+        <v>7.765836651901634</v>
       </c>
       <c r="G284">
-        <v>240.5418226831307</v>
-      </c>
-      <c r="H284">
         <v>0.3572891361409473</v>
       </c>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" spans="1:7">
       <c r="A285">
         <v>5859.8892</v>
       </c>
@@ -7799,16 +6944,13 @@
         <v>1055859612.059226</v>
       </c>
       <c r="F285">
-        <v>-21834029.56178562</v>
+        <v>-426.7789185288083</v>
       </c>
       <c r="G285">
-        <v>250.6844402908375</v>
-      </c>
-      <c r="H285">
         <v>0.03572839752312751</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:7">
       <c r="A286">
         <v>5860.4019</v>
       </c>
@@ -7825,16 +6967,13 @@
         <v>3899666774.767416</v>
       </c>
       <c r="F286">
-        <v>16071181.90222057</v>
+        <v>314.1628856580853</v>
       </c>
       <c r="G286">
-        <v>250.6625090288727</v>
-      </c>
-      <c r="H286">
         <v>0.140016564584761</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:7">
       <c r="A287">
         <v>5862.7342</v>
       </c>
@@ -7851,16 +6990,13 @@
         <v>2796647006.734191</v>
       </c>
       <c r="F287">
-        <v>3109556.329087359</v>
+        <v>60.81042228498792</v>
       </c>
       <c r="G287">
-        <v>61.36231613344666</v>
-      </c>
-      <c r="H287">
         <v>0.09097379817495788</v>
       </c>
     </row>
-    <row r="288" spans="1:8">
+    <row r="288" spans="1:7">
       <c r="A288">
         <v>5863.9814</v>
       </c>
@@ -7877,16 +7013,13 @@
         <v>10996657712.37162</v>
       </c>
       <c r="F288">
-        <v>-14089576.36405749</v>
+        <v>-275.5945256778505</v>
       </c>
       <c r="G288">
-        <v>531.6936311114202</v>
-      </c>
-      <c r="H288">
         <v>0.6954016901626702</v>
       </c>
     </row>
-    <row r="289" spans="1:8">
+    <row r="289" spans="1:7">
       <c r="A289">
         <v>5874.8407</v>
       </c>
@@ -7903,16 +7036,13 @@
         <v>5058471582.44154</v>
       </c>
       <c r="F289">
-        <v>681508.082006223</v>
+        <v>13.35508355507638</v>
       </c>
       <c r="G289">
-        <v>142.883684043463</v>
-      </c>
-      <c r="H289">
         <v>0.1758552352553547</v>
       </c>
     </row>
-    <row r="290" spans="1:8">
+    <row r="290" spans="1:7">
       <c r="A290">
         <v>5882.9101</v>
       </c>
@@ -7929,16 +7059,13 @@
         <v>4334182649.244018</v>
       </c>
       <c r="F290">
-        <v>-1174579.329471263</v>
+        <v>-23.04910711499457</v>
       </c>
       <c r="G290">
-        <v>168.1676406513978</v>
-      </c>
-      <c r="H290">
         <v>0.1541122333719152</v>
       </c>
     </row>
-    <row r="291" spans="1:8">
+    <row r="291" spans="1:7">
       <c r="A291">
         <v>5904.1092</v>
       </c>
@@ -7955,16 +7082,13 @@
         <v>4940771358.595871</v>
       </c>
       <c r="F291">
-        <v>17880455.45545046</v>
+        <v>352.137632014258</v>
       </c>
       <c r="G291">
-        <v>126.9422904632902</v>
-      </c>
-      <c r="H291">
         <v>0.1588464291142485</v>
       </c>
     </row>
-    <row r="292" spans="1:8">
+    <row r="292" spans="1:7">
       <c r="A292">
         <v>5907.3085</v>
       </c>
@@ -7981,16 +7105,13 @@
         <v>12381135127.01262</v>
       </c>
       <c r="F292">
-        <v>-6550174.385248312</v>
+        <v>-129.0690803449723</v>
       </c>
       <c r="G292">
-        <v>279.1217893847889</v>
-      </c>
-      <c r="H292">
         <v>0.5537554165691374</v>
       </c>
     </row>
-    <row r="293" spans="1:8">
+    <row r="293" spans="1:7">
       <c r="A293">
         <v>5908.4799</v>
       </c>
@@ -8007,16 +7128,13 @@
         <v>4191046733.494698</v>
       </c>
       <c r="F293">
-        <v>2581349.139524592</v>
+        <v>50.87469466592872</v>
       </c>
       <c r="G293">
-        <v>5.07393544957745</v>
-      </c>
-      <c r="H293">
         <v>0.1581207767968238</v>
       </c>
     </row>
-    <row r="294" spans="1:8">
+    <row r="294" spans="1:7">
       <c r="A294">
         <v>5917.8867</v>
       </c>
@@ -8033,16 +7151,13 @@
         <v>13955890224.08709</v>
       </c>
       <c r="F294">
-        <v>-1159099.325523965</v>
+        <v>-22.88058735444233</v>
       </c>
       <c r="G294">
-        <v>395.1378745460425</v>
-      </c>
-      <c r="H294">
         <v>0.5650563788751721</v>
       </c>
     </row>
-    <row r="295" spans="1:8">
+    <row r="295" spans="1:7">
       <c r="A295">
         <v>5929.4316</v>
       </c>
@@ -8059,16 +7174,13 @@
         <v>10766575342.90373</v>
       </c>
       <c r="F295">
-        <v>-2033420.228375565</v>
+        <v>-40.21793937830243</v>
       </c>
       <c r="G295">
-        <v>217.4082874196293</v>
-      </c>
-      <c r="H295">
         <v>0.4291980716710346</v>
       </c>
     </row>
-    <row r="296" spans="1:8">
+    <row r="296" spans="1:7">
       <c r="A296">
         <v>5931.3202</v>
       </c>
@@ -8085,16 +7197,13 @@
         <v>10489331473.43997</v>
       </c>
       <c r="F296">
-        <v>-2477687.205762073</v>
+        <v>-49.02046547080995</v>
       </c>
       <c r="G296">
-        <v>197.1214749586593</v>
-      </c>
-      <c r="H296">
         <v>0.4081746479187643</v>
       </c>
     </row>
-    <row r="297" spans="1:8">
+    <row r="297" spans="1:7">
       <c r="A297">
         <v>5931.8229</v>
       </c>
@@ -8111,16 +7220,13 @@
         <v>10669998090.33092</v>
       </c>
       <c r="F297">
-        <v>-16573513.59625077</v>
+        <v>-327.9312755858115</v>
       </c>
       <c r="G297">
-        <v>535.7206558771211</v>
-      </c>
-      <c r="H297">
         <v>0.6969114551418815</v>
       </c>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" spans="1:7">
       <c r="A298">
         <v>5936.2992</v>
       </c>
@@ -8137,16 +7243,13 @@
         <v>11437481615.95392</v>
       </c>
       <c r="F298">
-        <v>-9698805.968017658</v>
+        <v>-192.0498433919508</v>
       </c>
       <c r="G298">
-        <v>419.1630707102194</v>
-      </c>
-      <c r="H298">
         <v>0.648338550543504</v>
       </c>
     </row>
-    <row r="299" spans="1:8">
+    <row r="299" spans="1:7">
       <c r="A299">
         <v>5954.3675</v>
       </c>
@@ -8163,16 +7266,13 @@
         <v>11925408810.53115</v>
       </c>
       <c r="F299">
-        <v>-4383808.066051207</v>
+        <v>-87.06967502405939</v>
       </c>
       <c r="G299">
-        <v>317.1944770638686</v>
-      </c>
-      <c r="H299">
         <v>0.5497363852027355</v>
       </c>
     </row>
-    <row r="300" spans="1:8">
+    <row r="300" spans="1:7">
       <c r="A300">
         <v>5964.8905</v>
       </c>
@@ -8189,16 +7289,13 @@
         <v>1339451500.753004</v>
       </c>
       <c r="F300">
-        <v>28734940.94975821</v>
+        <v>571.7320236885993</v>
       </c>
       <c r="G300">
-        <v>301.5570441444258</v>
-      </c>
-      <c r="H300">
         <v>0.03902640370934984</v>
       </c>
     </row>
-    <row r="301" spans="1:8">
+    <row r="301" spans="1:7">
       <c r="A301">
         <v>5971.2159</v>
       </c>
@@ -8215,16 +7312,13 @@
         <v>1351231417.432497</v>
       </c>
       <c r="F301">
-        <v>29172534.43585939</v>
+        <v>581.053969463317</v>
       </c>
       <c r="G301">
-        <v>165.6806800781056</v>
-      </c>
-      <c r="H301">
         <v>0.04747334885483201</v>
       </c>
     </row>
-    <row r="302" spans="1:8">
+    <row r="302" spans="1:7">
       <c r="A302">
         <v>5977.8158</v>
       </c>
@@ -8241,16 +7335,13 @@
         <v>510351796.5584667</v>
       </c>
       <c r="F302">
-        <v>99787320.79657586</v>
+        <v>1989.745825043965</v>
       </c>
       <c r="G302">
-        <v>285.8597634298384</v>
-      </c>
-      <c r="H302">
         <v>0.02205679465607424</v>
       </c>
     </row>
-    <row r="303" spans="1:8">
+    <row r="303" spans="1:7">
       <c r="A303">
         <v>5985.3384</v>
       </c>
@@ -8267,16 +7358,13 @@
         <v>12534023019.66874</v>
       </c>
       <c r="F303">
-        <v>-8882016.931023909</v>
+        <v>-177.3291473437583</v>
       </c>
       <c r="G303">
-        <v>360.6321903990441</v>
-      </c>
-      <c r="H303">
         <v>0.6190323071362765</v>
       </c>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" spans="1:7">
       <c r="A304">
         <v>5986.4728</v>
       </c>
@@ -8293,16 +7381,13 @@
         <v>10951515210.86382</v>
       </c>
       <c r="F304">
-        <v>-14447133.5133646</v>
+        <v>-288.4912770670634</v>
       </c>
       <c r="G304">
-        <v>475.7439724646751</v>
-      </c>
-      <c r="H304">
         <v>0.6603062211814863</v>
       </c>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" spans="1:7">
       <c r="A305">
         <v>6004.6749</v>
       </c>
@@ -8319,16 +7404,13 @@
         <v>10500226477.82729</v>
       </c>
       <c r="F305">
-        <v>-12709223.6496095</v>
+        <v>-254.5590077196318</v>
       </c>
       <c r="G305">
-        <v>449.3385848136188</v>
-      </c>
-      <c r="H305">
         <v>0.6714223540492699</v>
       </c>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" spans="1:7">
       <c r="A306">
         <v>6007.2046</v>
       </c>
@@ -8345,16 +7427,13 @@
         <v>7979249424.670936</v>
       </c>
       <c r="F306">
-        <v>4345107.934872659</v>
+        <v>87.0668267778783</v>
       </c>
       <c r="G306">
-        <v>294.4423604351983</v>
-      </c>
-      <c r="H306">
         <v>0.2447084945482755</v>
       </c>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" spans="1:7">
       <c r="A307">
         <v>6009.6241</v>
       </c>
@@ -8371,16 +7450,13 @@
         <v>12415363555.23792</v>
       </c>
       <c r="F307">
-        <v>-7288189.337732968</v>
+        <v>-146.0988462291609</v>
       </c>
       <c r="G307">
-        <v>369.1519057380905</v>
-      </c>
-      <c r="H307">
         <v>0.5676056243134864</v>
       </c>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" spans="1:7">
       <c r="A308">
         <v>6010.2207</v>
       </c>
@@ -8397,16 +7473,13 @@
         <v>10177483256.48672</v>
       </c>
       <c r="F308">
-        <v>-14013199.2687417</v>
+        <v>-280.9361983469555</v>
       </c>
       <c r="G308">
-        <v>473.8641878588085</v>
-      </c>
-      <c r="H308">
         <v>0.684145828137061</v>
       </c>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" spans="1:7">
       <c r="A309">
         <v>6016.9102</v>
       </c>
@@ -8423,16 +7496,13 @@
         <v>1823829065.699931</v>
       </c>
       <c r="F309">
-        <v>-27596048.03371594</v>
+        <v>-553.8602292271901</v>
       </c>
       <c r="G309">
-        <v>318.879901335732</v>
-      </c>
-      <c r="H309">
         <v>0.05621120943293445</v>
       </c>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" spans="1:7">
       <c r="A310">
         <v>6019.9662</v>
       </c>
@@ -8449,16 +7519,13 @@
         <v>2615749583.655995</v>
       </c>
       <c r="F310">
-        <v>24015373.93021127</v>
+        <v>482.2394943491439</v>
       </c>
       <c r="G310">
-        <v>49.79969125091323</v>
-      </c>
-      <c r="H310">
         <v>0.09158216942311315</v>
       </c>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" spans="1:7">
       <c r="A311">
         <v>6021.0329</v>
       </c>
@@ -8475,16 +7542,13 @@
         <v>1676683416.738425</v>
       </c>
       <c r="F311">
-        <v>2753664.521215137</v>
+        <v>55.30464392711396</v>
       </c>
       <c r="G311">
-        <v>189.2053006797367</v>
-      </c>
-      <c r="H311">
         <v>0.05556808939885982</v>
       </c>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" spans="1:7">
       <c r="A312">
         <v>6025.7262</v>
       </c>
@@ -8501,16 +7565,13 @@
         <v>8042412587.169543</v>
       </c>
       <c r="F312">
-        <v>-30517707.14593407</v>
+        <v>-613.3967106741774</v>
       </c>
       <c r="G312">
-        <v>587.0746341558789</v>
-      </c>
-      <c r="H312">
         <v>0.7397161411098176</v>
       </c>
     </row>
-    <row r="313" spans="1:8">
+    <row r="313" spans="1:7">
       <c r="A313">
         <v>6028.72</v>
       </c>
@@ -8527,16 +7588,13 @@
         <v>13445119218.55251</v>
       </c>
       <c r="F313">
-        <v>-8370326.540323065</v>
+        <v>-168.3245073417608</v>
       </c>
       <c r="G313">
-        <v>372.9553595075291</v>
-      </c>
-      <c r="H313">
         <v>0.6160553739397592</v>
       </c>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" spans="1:7">
       <c r="A314">
         <v>6035.7064</v>
       </c>
@@ -8553,16 +7611,13 @@
         <v>2689074173.20319</v>
       </c>
       <c r="F314">
-        <v>21197381.49815887</v>
+        <v>426.7659372770672</v>
       </c>
       <c r="G314">
-        <v>89.40567822075303</v>
-      </c>
-      <c r="H314">
         <v>0.08902899983976753</v>
       </c>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" spans="1:7">
       <c r="A315">
         <v>6055.7504</v>
       </c>
@@ -8579,16 +7634,13 @@
         <v>2746962579.036287</v>
       </c>
       <c r="F315">
-        <v>8672385.212878132</v>
+        <v>175.1805974478646</v>
       </c>
       <c r="G315">
-        <v>123.7635463544082</v>
-      </c>
-      <c r="H315">
         <v>0.09910040086236804</v>
       </c>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" spans="1:7">
       <c r="A316">
         <v>6057.6815</v>
       </c>
@@ -8605,16 +7657,13 @@
         <v>11905487746.36022</v>
       </c>
       <c r="F316">
-        <v>-12450086.89931176</v>
+        <v>-251.5699066854056</v>
       </c>
       <c r="G316">
-        <v>395.917095359063</v>
-      </c>
-      <c r="H316">
         <v>0.6249361462439429</v>
       </c>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" spans="1:7">
       <c r="A317">
         <v>6064.5271</v>
       </c>
@@ -8631,16 +7680,13 @@
         <v>7627159891.589754</v>
       </c>
       <c r="F317">
-        <v>4366548.069340677</v>
+        <v>88.3313446554735</v>
       </c>
       <c r="G317">
-        <v>247.1688666531107</v>
-      </c>
-      <c r="H317">
         <v>0.2196021545531024</v>
       </c>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" spans="1:7">
       <c r="A318">
         <v>6080.1739</v>
       </c>
@@ -8657,16 +7703,13 @@
         <v>11363615989.23699</v>
       </c>
       <c r="F318">
-        <v>-12808675.20513519</v>
+        <v>-259.7766494469714</v>
       </c>
       <c r="G318">
-        <v>414.1751023327312</v>
-      </c>
-      <c r="H318">
         <v>0.6315564635573452</v>
       </c>
     </row>
-    <row r="319" spans="1:8">
+    <row r="319" spans="1:7">
       <c r="A319">
         <v>6080.6922</v>
       </c>
@@ -8683,16 +7726,13 @@
         <v>11316270148.15133</v>
       </c>
       <c r="F319">
-        <v>-3472077.322784561</v>
+        <v>-70.42421468916822</v>
       </c>
       <c r="G319">
-        <v>212.000135340784</v>
-      </c>
-      <c r="H319">
         <v>0.4529953476645689</v>
       </c>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" spans="1:7">
       <c r="A320">
         <v>6084.3946</v>
       </c>
@@ -8709,16 +7749,13 @@
         <v>12421367242.34694</v>
       </c>
       <c r="F320">
-        <v>254882.8827256591</v>
+        <v>5.172943127178788</v>
       </c>
       <c r="G320">
-        <v>251.2890166721456</v>
-      </c>
-      <c r="H320">
         <v>0.3799572678981898</v>
       </c>
     </row>
-    <row r="321" spans="1:8">
+    <row r="321" spans="1:7">
       <c r="A321">
         <v>6095.3313</v>
       </c>
@@ -8735,16 +7772,13 @@
         <v>8558354679.616647</v>
       </c>
       <c r="F321">
-        <v>1633582.998557557</v>
+        <v>33.21375693037457</v>
       </c>
       <c r="G321">
-        <v>127.8782649479058</v>
-      </c>
-      <c r="H321">
         <v>0.3118276962518409</v>
       </c>
     </row>
-    <row r="322" spans="1:8">
+    <row r="322" spans="1:7">
       <c r="A322">
         <v>6096.0607</v>
       </c>
@@ -8761,16 +7795,13 @@
         <v>5460009466.793177</v>
       </c>
       <c r="F322">
-        <v>3540763.158393706</v>
+        <v>71.99888030853792</v>
       </c>
       <c r="G322">
-        <v>196.7122525614102</v>
-      </c>
-      <c r="H322">
         <v>0.194616287956635</v>
       </c>
     </row>
-    <row r="323" spans="1:8">
+    <row r="323" spans="1:7">
       <c r="A323">
         <v>6098.353</v>
       </c>
@@ -8787,16 +7818,13 @@
         <v>9667578175.065166</v>
       </c>
       <c r="F323">
-        <v>-498305.7785261101</v>
+        <v>-10.13650127341199</v>
       </c>
       <c r="G323">
-        <v>206.4702262821356</v>
-      </c>
-      <c r="H323">
         <v>0.3684058513122634</v>
       </c>
     </row>
-    <row r="324" spans="1:8">
+    <row r="324" spans="1:7">
       <c r="A324">
         <v>6099.9329</v>
       </c>
@@ -8813,16 +7841,13 @@
         <v>4557888930.522683</v>
       </c>
       <c r="F324">
-        <v>16583372.46383609</v>
+        <v>337.4251297383379</v>
       </c>
       <c r="G324">
-        <v>147.4405356400202</v>
-      </c>
-      <c r="H324">
         <v>0.1608942236396645</v>
       </c>
     </row>
-    <row r="325" spans="1:8">
+    <row r="325" spans="1:7">
       <c r="A325">
         <v>6101.9603</v>
       </c>
@@ -8839,16 +7864,13 @@
         <v>2401448478.774716</v>
       </c>
       <c r="F325">
-        <v>22421123.90685183</v>
+        <v>456.3586891877768</v>
       </c>
       <c r="G325">
-        <v>186.6959607134303</v>
-      </c>
-      <c r="H325">
         <v>0.08406288797050054</v>
       </c>
     </row>
-    <row r="326" spans="1:8">
+    <row r="326" spans="1:7">
       <c r="A326">
         <v>6106.8214</v>
       </c>
@@ -8865,16 +7887,13 @@
         <v>3512015559.437302</v>
       </c>
       <c r="F326">
-        <v>21658919.88904367</v>
+        <v>441.1957259695757</v>
       </c>
       <c r="G326">
-        <v>-9.818281462614754</v>
-      </c>
-      <c r="H326">
         <v>0.1174202872054156</v>
       </c>
     </row>
-    <row r="327" spans="1:8">
+    <row r="327" spans="1:7">
       <c r="A327">
         <v>6121.9435</v>
       </c>
@@ -8891,16 +7910,13 @@
         <v>2049494032.412061</v>
       </c>
       <c r="F327">
-        <v>38225340.4178875</v>
+        <v>780.5849644158189</v>
       </c>
       <c r="G327">
-        <v>142.01341913711</v>
-      </c>
-      <c r="H327">
         <v>0.05783687841960117</v>
       </c>
     </row>
-    <row r="328" spans="1:8">
+    <row r="328" spans="1:7">
       <c r="A328">
         <v>6129.6027</v>
       </c>
@@ -8917,16 +7933,13 @@
         <v>12689612245.63659</v>
       </c>
       <c r="F328">
-        <v>-3540413.588581478</v>
+        <v>-72.38790682987033</v>
       </c>
       <c r="G328">
-        <v>273.8901437581127</v>
-      </c>
-      <c r="H328">
         <v>0.4911134632748123</v>
       </c>
     </row>
-    <row r="329" spans="1:8">
+    <row r="329" spans="1:7">
       <c r="A329">
         <v>6138.3138</v>
       </c>
@@ -8943,16 +7956,13 @@
         <v>2799485789.374488</v>
       </c>
       <c r="F329">
-        <v>-86964651.28316088</v>
+        <v>-1780.623606922983</v>
       </c>
       <c r="G329">
-        <v>678.8696866891216</v>
-      </c>
-      <c r="H329">
         <v>0.7815014133277446</v>
       </c>
     </row>
-    <row r="330" spans="1:8">
+    <row r="330" spans="1:7">
       <c r="A330">
         <v>6138.6932</v>
       </c>
@@ -8969,16 +7979,13 @@
         <v>14012350167.0482</v>
       </c>
       <c r="F330">
-        <v>-7724419.872112893</v>
+        <v>-158.1691024173773</v>
       </c>
       <c r="G330">
-        <v>380.9249129044233</v>
-      </c>
-      <c r="H330">
         <v>0.636353656290517</v>
       </c>
     </row>
-    <row r="331" spans="1:8">
+    <row r="331" spans="1:7">
       <c r="A331">
         <v>6139.3904</v>
       </c>
@@ -8995,16 +8002,13 @@
         <v>3345069457.0417</v>
       </c>
       <c r="F331">
-        <v>-77785583.60000248</v>
+        <v>-1592.959070763653</v>
       </c>
       <c r="G331">
-        <v>659.2182479698313</v>
-      </c>
-      <c r="H331">
         <v>0.7750025739682369</v>
       </c>
     </row>
-    <row r="332" spans="1:8">
+    <row r="332" spans="1:7">
       <c r="A332">
         <v>6153.3206</v>
       </c>
@@ -9021,16 +8025,13 @@
         <v>15033746421.19675</v>
       </c>
       <c r="F332">
-        <v>-2179549.673213859</v>
+        <v>-44.73588809238161</v>
       </c>
       <c r="G332">
-        <v>311.810785737741</v>
-      </c>
-      <c r="H332">
         <v>0.5256068458744143</v>
       </c>
     </row>
-    <row r="333" spans="1:8">
+    <row r="333" spans="1:7">
       <c r="A333">
         <v>6159.4325</v>
       </c>
@@ -9047,16 +8048,13 @@
         <v>13201911266.28087</v>
       </c>
       <c r="F333">
-        <v>-7634507.67255867</v>
+        <v>-156.8561310091659</v>
       </c>
       <c r="G333">
-        <v>321.2357993535135</v>
-      </c>
-      <c r="H333">
         <v>0.5873987979124176</v>
       </c>
     </row>
-    <row r="334" spans="1:8">
+    <row r="334" spans="1:7">
       <c r="A334">
         <v>6167.0664</v>
       </c>
@@ -9073,16 +8071,13 @@
         <v>12317003272.46349</v>
       </c>
       <c r="F334">
-        <v>-3337415.493938887</v>
+        <v>-68.65443218572756</v>
       </c>
       <c r="G334">
-        <v>262.5039473108753</v>
-      </c>
-      <c r="H334">
         <v>0.456787619183467</v>
       </c>
     </row>
-    <row r="335" spans="1:8">
+    <row r="335" spans="1:7">
       <c r="A335">
         <v>6175.0438</v>
       </c>
@@ -9099,16 +8094,13 @@
         <v>13830118339.5256</v>
       </c>
       <c r="F335">
-        <v>-8428371.137269182</v>
+        <v>-173.6055349595764</v>
       </c>
       <c r="G335">
-        <v>398.1021406184202</v>
-      </c>
-      <c r="H335">
         <v>0.644658734980281</v>
       </c>
     </row>
-    <row r="336" spans="1:8">
+    <row r="336" spans="1:7">
       <c r="A336">
         <v>6181.9143</v>
       </c>
@@ -9125,16 +8117,13 @@
         <v>14227905075.67407</v>
       </c>
       <c r="F336">
-        <v>-3195038.095257245</v>
+        <v>-65.88382145813338</v>
       </c>
       <c r="G336">
-        <v>320.0675594512902</v>
-      </c>
-      <c r="H336">
         <v>0.5430179005926099</v>
       </c>
     </row>
-    <row r="337" spans="1:8">
+    <row r="337" spans="1:7">
       <c r="A337">
         <v>6189.7026</v>
       </c>
@@ -9151,16 +8140,13 @@
         <v>11022363957.31765</v>
       </c>
       <c r="F337">
-        <v>-2220739.152609609</v>
+        <v>-45.850809558461</v>
       </c>
       <c r="G337">
-        <v>261.5439509517371</v>
-      </c>
-      <c r="H337">
         <v>0.4475896790619687</v>
       </c>
     </row>
-    <row r="338" spans="1:8">
+    <row r="338" spans="1:7">
       <c r="A338">
         <v>6202.0285</v>
       </c>
@@ -9177,16 +8163,13 @@
         <v>11888421197.71374</v>
       </c>
       <c r="F338">
-        <v>-7622464.384466942</v>
+        <v>-157.6918098806991</v>
       </c>
       <c r="G338">
-        <v>468.8767299859279</v>
-      </c>
-      <c r="H338">
         <v>0.6507609176834865</v>
       </c>
     </row>
-    <row r="339" spans="1:8">
+    <row r="339" spans="1:7">
       <c r="A339">
         <v>6215.1493</v>
       </c>
@@ -9203,16 +8186,13 @@
         <v>10517890543.49904</v>
       </c>
       <c r="F339">
-        <v>-18951699.24991865</v>
+        <v>-392.8978835860348</v>
       </c>
       <c r="G339">
-        <v>463.0633083425498</v>
-      </c>
-      <c r="H339">
         <v>0.6999906849557218</v>
       </c>
     </row>
-    <row r="340" spans="1:8">
+    <row r="340" spans="1:7">
       <c r="A340">
         <v>6216.8633</v>
       </c>
@@ -9229,16 +8209,13 @@
         <v>11299741730.86432</v>
       </c>
       <c r="F340">
-        <v>-2291136.379248552</v>
+        <v>-47.51185221622956</v>
       </c>
       <c r="G340">
-        <v>279.6902830954069</v>
-      </c>
-      <c r="H340">
         <v>0.5033954754414275</v>
       </c>
     </row>
-    <row r="341" spans="1:8">
+    <row r="341" spans="1:7">
       <c r="A341">
         <v>6221.0016</v>
       </c>
@@ -9255,16 +8232,13 @@
         <v>9112147055.012003</v>
       </c>
       <c r="F341">
-        <v>-25895176.46467625</v>
+        <v>-537.3523965046365</v>
       </c>
       <c r="G341">
-        <v>486.7228816925806</v>
-      </c>
-      <c r="H341">
         <v>0.7167836707229329</v>
       </c>
     </row>
-    <row r="342" spans="1:8">
+    <row r="342" spans="1:7">
       <c r="A342">
         <v>6234.3654</v>
       </c>
@@ -9281,16 +8255,13 @@
         <v>11246854609.25177</v>
       </c>
       <c r="F342">
-        <v>-11764468.7818448</v>
+        <v>-244.6495896393948</v>
       </c>
       <c r="G342">
-        <v>427.975055229197</v>
-      </c>
-      <c r="H342">
         <v>0.6630203688188003</v>
       </c>
     </row>
-    <row r="343" spans="1:8">
+    <row r="343" spans="1:7">
       <c r="A343">
         <v>6242.3726</v>
       </c>
@@ -9307,16 +8278,13 @@
         <v>14846790996.89622</v>
       </c>
       <c r="F343">
-        <v>-2466836.580840665</v>
+        <v>-51.36530268808002</v>
       </c>
       <c r="G343">
-        <v>336.1778190223142</v>
-      </c>
-      <c r="H343">
         <v>0.5079423245743135</v>
       </c>
     </row>
-    <row r="344" spans="1:8">
+    <row r="344" spans="1:7">
       <c r="A344">
         <v>6248.0467</v>
       </c>
@@ -9333,16 +8301,13 @@
         <v>6781847388.380048</v>
       </c>
       <c r="F344">
-        <v>-36460525.76559008</v>
+        <v>-759.8839097869864</v>
       </c>
       <c r="G344">
-        <v>523.001499348122</v>
-      </c>
-      <c r="H344">
         <v>0.7336325604439211</v>
       </c>
     </row>
-    <row r="345" spans="1:8">
+    <row r="345" spans="1:7">
       <c r="A345">
         <v>6254.285</v>
       </c>
@@ -9359,16 +8324,13 @@
         <v>3480849164.915765</v>
       </c>
       <c r="F345">
-        <v>-83271495.83645821</v>
+        <v>-1737.217846077422</v>
       </c>
       <c r="G345">
-        <v>656.694838006605</v>
-      </c>
-      <c r="H345">
         <v>0.7562403972721112</v>
       </c>
     </row>
-    <row r="346" spans="1:8">
+    <row r="346" spans="1:7">
       <c r="A346">
         <v>6266.8669</v>
       </c>
@@ -9385,16 +8347,13 @@
         <v>10023096943.77432</v>
       </c>
       <c r="F346">
-        <v>-21531194.70478527</v>
+        <v>-450.089168395101</v>
       </c>
       <c r="G346">
-        <v>459.2418576381539</v>
-      </c>
-      <c r="H346">
         <v>0.7055188649089266</v>
       </c>
     </row>
-    <row r="347" spans="1:8">
+    <row r="347" spans="1:7">
       <c r="A347">
         <v>6282.3553</v>
       </c>
@@ -9411,16 +8370,13 @@
         <v>14953298542.03981</v>
       </c>
       <c r="F347">
-        <v>-6926871.793785607</v>
+        <v>-145.157504733104</v>
       </c>
       <c r="G347">
-        <v>381.758042844241</v>
-      </c>
-      <c r="H347">
         <v>0.6313794101165418</v>
       </c>
     </row>
-    <row r="348" spans="1:8">
+    <row r="348" spans="1:7">
       <c r="A348">
         <v>6299.5348</v>
       </c>
@@ -9437,16 +8393,13 @@
         <v>12632071631.39491</v>
       </c>
       <c r="F348">
-        <v>-11769442.80861209</v>
+        <v>-247.3115011730396</v>
       </c>
       <c r="G348">
-        <v>437.8244903536454</v>
-      </c>
-      <c r="H348">
         <v>0.6654854464290649</v>
       </c>
     </row>
-    <row r="349" spans="1:8">
+    <row r="349" spans="1:7">
       <c r="A349">
         <v>6303.2439</v>
       </c>
@@ -9463,16 +8416,13 @@
         <v>6884493956.112151</v>
       </c>
       <c r="F349">
-        <v>-35292504.53356972</v>
+        <v>-742.0388427691704</v>
       </c>
       <c r="G349">
-        <v>518.4216006885525</v>
-      </c>
-      <c r="H349">
         <v>0.732145323298764</v>
       </c>
     </row>
-    <row r="350" spans="1:8">
+    <row r="350" spans="1:7">
       <c r="A350">
         <v>6304.2365</v>
       </c>
@@ -9489,16 +8439,13 @@
         <v>11023058042.25396</v>
       </c>
       <c r="F350">
-        <v>-14763348.81025014</v>
+        <v>-310.4540399443753</v>
       </c>
       <c r="G350">
-        <v>442.2533734426983</v>
-      </c>
-      <c r="H350">
         <v>0.6651886282036505</v>
       </c>
     </row>
-    <row r="351" spans="1:8">
+    <row r="351" spans="1:7">
       <c r="A351">
         <v>6313.2457</v>
       </c>
@@ -9515,16 +8462,13 @@
         <v>9562939862.65</v>
       </c>
       <c r="F351">
-        <v>754925.4863659821</v>
+        <v>15.89777820972726</v>
       </c>
       <c r="G351">
-        <v>246.928577745953</v>
-      </c>
-      <c r="H351">
         <v>0.2912627011339803</v>
       </c>
     </row>
-    <row r="352" spans="1:8">
+    <row r="352" spans="1:7">
       <c r="A352">
         <v>6317.558</v>
       </c>
@@ -9541,16 +8485,13 @@
         <v>11380291370.07478</v>
       </c>
       <c r="F352">
-        <v>-2702758.691107813</v>
+        <v>-56.95556235305719</v>
       </c>
       <c r="G352">
-        <v>232.5238714657339</v>
-      </c>
-      <c r="H352">
         <v>0.413430722805997</v>
       </c>
     </row>
-    <row r="353" spans="1:8">
+    <row r="353" spans="1:7">
       <c r="A353">
         <v>6338.5765</v>
       </c>
@@ -9567,16 +8508,13 @@
         <v>8088641038.087713</v>
       </c>
       <c r="F353">
-        <v>-27381835.327106</v>
+        <v>-578.9410091788178</v>
       </c>
       <c r="G353">
-        <v>501.3428574279085</v>
-      </c>
-      <c r="H353">
         <v>0.7111820552698167</v>
       </c>
     </row>
-    <row r="354" spans="1:8">
+    <row r="354" spans="1:7">
       <c r="A354">
         <v>6340.6302</v>
       </c>
@@ -9593,16 +8531,13 @@
         <v>10430600514.49866</v>
       </c>
       <c r="F354">
-        <v>-3233199.247247541</v>
+        <v>-68.38241874381006</v>
       </c>
       <c r="G354">
-        <v>184.3965898477051</v>
-      </c>
-      <c r="H354">
         <v>0.4095668089177944</v>
       </c>
     </row>
-    <row r="355" spans="1:8">
+    <row r="355" spans="1:7">
       <c r="A355">
         <v>6345.9033</v>
       </c>
@@ -9619,16 +8554,13 @@
         <v>12973216277.58961</v>
       </c>
       <c r="F355">
-        <v>-3922429.49292617</v>
+        <v>-83.02873733524845</v>
       </c>
       <c r="G355">
-        <v>373.2109214823816</v>
-      </c>
-      <c r="H355">
         <v>0.5650854921639806</v>
       </c>
     </row>
-    <row r="356" spans="1:8">
+    <row r="356" spans="1:7">
       <c r="A356">
         <v>6366.1253</v>
       </c>
@@ -9645,16 +8577,13 @@
         <v>7395561542.717018</v>
       </c>
       <c r="F356">
-        <v>427209.6195042419</v>
+        <v>9.071845938273785</v>
       </c>
       <c r="G356">
-        <v>113.0203798200507</v>
-      </c>
-      <c r="H356">
         <v>0.2727056654817125</v>
       </c>
     </row>
-    <row r="357" spans="1:8">
+    <row r="357" spans="1:7">
       <c r="A357">
         <v>6366.4548</v>
       </c>
@@ -9671,16 +8600,13 @@
         <v>3704710244.979796</v>
       </c>
       <c r="F357">
-        <v>-2409918.728945904</v>
+        <v>-51.17755150908018</v>
       </c>
       <c r="G357">
-        <v>103.5966528170118</v>
-      </c>
-      <c r="H357">
         <v>0.1257503446841526</v>
       </c>
     </row>
-    <row r="358" spans="1:8">
+    <row r="358" spans="1:7">
       <c r="A358">
         <v>6382.5072</v>
       </c>
@@ -9697,16 +8623,13 @@
         <v>12506265000.31371</v>
       </c>
       <c r="F358">
-        <v>-6073885.954013045</v>
+        <v>-129.311647557839</v>
       </c>
       <c r="G358">
-        <v>277.1286340804427</v>
-      </c>
-      <c r="H358">
         <v>0.4952371058970548</v>
       </c>
     </row>
-    <row r="359" spans="1:8">
+    <row r="359" spans="1:7">
       <c r="A359">
         <v>6387.4838</v>
       </c>
@@ -9723,16 +8646,13 @@
         <v>3205790552.841436</v>
       </c>
       <c r="F359">
-        <v>16696418.08448537</v>
+        <v>355.7399147224857</v>
       </c>
       <c r="G359">
-        <v>122.0293335120035</v>
-      </c>
-      <c r="H359">
         <v>0.1070531645952315</v>
       </c>
     </row>
-    <row r="360" spans="1:8">
+    <row r="360" spans="1:7">
       <c r="A360">
         <v>6394.3059</v>
       </c>
@@ -9749,16 +8669,13 @@
         <v>6630910522.559899</v>
       </c>
       <c r="F360">
-        <v>4808875.471577702</v>
+        <v>102.5691058704499</v>
       </c>
       <c r="G360">
-        <v>229.7329948318014</v>
-      </c>
-      <c r="H360">
         <v>0.1895513576937424</v>
       </c>
     </row>
-    <row r="361" spans="1:8">
+    <row r="361" spans="1:7">
       <c r="A361">
         <v>6395.3687</v>
       </c>
@@ -9775,16 +8692,13 @@
         <v>2954065593.074745</v>
       </c>
       <c r="F361">
-        <v>-49566298.6596772</v>
+        <v>-1057.382984579628</v>
       </c>
       <c r="G361">
-        <v>651.5832568196157</v>
-      </c>
-      <c r="H361">
         <v>0.7548010022744016</v>
       </c>
     </row>
-    <row r="362" spans="1:8">
+    <row r="362" spans="1:7">
       <c r="A362">
         <v>6401.7704</v>
       </c>
@@ -9801,16 +8715,13 @@
         <v>4536393233.336523</v>
       </c>
       <c r="F362">
-        <v>-50421833.47258341</v>
+        <v>-1076.710346715256</v>
       </c>
       <c r="G362">
-        <v>594.7361399262213</v>
-      </c>
-      <c r="H362">
         <v>0.7659491932657994</v>
       </c>
     </row>
-    <row r="363" spans="1:8">
+    <row r="363" spans="1:7">
       <c r="A363">
         <v>6409.7896</v>
       </c>
@@ -9827,16 +8738,13 @@
         <v>9307800823.4429</v>
       </c>
       <c r="F363">
-        <v>-20422152.50991127</v>
+        <v>-436.6417617863605</v>
       </c>
       <c r="G363">
-        <v>472.3873972143959</v>
-      </c>
-      <c r="H363">
         <v>0.6844420822360129</v>
       </c>
     </row>
-    <row r="364" spans="1:8">
+    <row r="364" spans="1:7">
       <c r="A364">
         <v>6413.4216</v>
       </c>
@@ -9853,16 +8761,13 @@
         <v>6053397654.657803</v>
       </c>
       <c r="F364">
-        <v>-42010462.2615065</v>
+        <v>-898.7260560613998</v>
       </c>
       <c r="G364">
-        <v>542.2366920214278</v>
-      </c>
-      <c r="H364">
         <v>0.736909043582247</v>
       </c>
     </row>
-    <row r="365" spans="1:8">
+    <row r="365" spans="1:7">
       <c r="A365">
         <v>6421.4198</v>
       </c>
@@ -9879,16 +8784,13 @@
         <v>3166040119.89288</v>
       </c>
       <c r="F365">
-        <v>20062529.20130051</v>
+        <v>429.7306991090326</v>
       </c>
       <c r="G365">
-        <v>233.4315987165931</v>
-      </c>
-      <c r="H365">
         <v>0.1071799743930507</v>
       </c>
     </row>
-    <row r="366" spans="1:8">
+    <row r="366" spans="1:7">
       <c r="A366">
         <v>6421.7241</v>
       </c>
@@ -9905,16 +8807,13 @@
         <v>10974887381.89085</v>
       </c>
       <c r="F366">
-        <v>-12579516.83244504</v>
+        <v>-269.4607132555216</v>
       </c>
       <c r="G366">
-        <v>382.8096812041815</v>
-      </c>
-      <c r="H366">
         <v>0.6466716822774413</v>
       </c>
     </row>
-    <row r="367" spans="1:8">
+    <row r="367" spans="1:7">
       <c r="A367">
         <v>6423.1257</v>
       </c>
@@ -9931,16 +8830,13 @@
         <v>5708228788.672423</v>
       </c>
       <c r="F367">
-        <v>-64932027.94484177</v>
+        <v>-1391.186954509599</v>
       </c>
       <c r="G367">
-        <v>560.0870455224909</v>
-      </c>
-      <c r="H367">
         <v>0.735806372255108</v>
       </c>
     </row>
-    <row r="368" spans="1:8">
+    <row r="368" spans="1:7">
       <c r="A368">
         <v>6432.6238</v>
       </c>
@@ -9957,16 +8853,13 @@
         <v>4891833407.858776</v>
       </c>
       <c r="F368">
-        <v>-90150894.77902985</v>
+        <v>-1934.364510223267</v>
       </c>
       <c r="G368">
-        <v>568.5810489098885</v>
-      </c>
-      <c r="H368">
         <v>0.742007667078084</v>
       </c>
     </row>
-    <row r="369" spans="1:8">
+    <row r="369" spans="1:7">
       <c r="A369">
         <v>6438.1862</v>
       </c>
@@ -9983,16 +8876,13 @@
         <v>3163299084.607537</v>
       </c>
       <c r="F369">
-        <v>13251098.36659904</v>
+        <v>284.5738201243367</v>
       </c>
       <c r="G369">
-        <v>162.9765853665559</v>
-      </c>
-      <c r="H369">
         <v>0.1011722032202695</v>
       </c>
     </row>
-    <row r="370" spans="1:8">
+    <row r="370" spans="1:7">
       <c r="A370">
         <v>6483.6614</v>
       </c>
@@ -10009,16 +8899,13 @@
         <v>13869775358.03662</v>
       </c>
       <c r="F370">
-        <v>-5665370.027981409</v>
+        <v>-122.526067091375</v>
       </c>
       <c r="G370">
-        <v>406.895651647155</v>
-      </c>
-      <c r="H370">
         <v>0.5949746148457946</v>
       </c>
     </row>
-    <row r="371" spans="1:8">
+    <row r="371" spans="1:7">
       <c r="A371">
         <v>6496.7751</v>
       </c>
@@ -10035,16 +8922,13 @@
         <v>2508076262.359835</v>
       </c>
       <c r="F371">
-        <v>14270431.72750136</v>
+        <v>309.2539282253299</v>
       </c>
       <c r="G371">
-        <v>678.3287192218567</v>
-      </c>
-      <c r="H371">
         <v>0.7696031101827028</v>
       </c>
     </row>
-    <row r="372" spans="1:8">
+    <row r="372" spans="1:7">
       <c r="A372">
         <v>6498.2616</v>
       </c>
@@ -10061,16 +8945,13 @@
         <v>11899147860.60353</v>
       </c>
       <c r="F372">
-        <v>-9023166.110623879</v>
+        <v>-195.5851939157768</v>
       </c>
       <c r="G372">
-        <v>369.0740403721263</v>
-      </c>
-      <c r="H372">
         <v>0.5432576184678575</v>
       </c>
     </row>
-    <row r="373" spans="1:8">
+    <row r="373" spans="1:7">
       <c r="A373">
         <v>6500.735</v>
       </c>
@@ -10087,16 +8968,13 @@
         <v>14846282057.65637</v>
       </c>
       <c r="F373">
-        <v>-986240.9067970578</v>
+        <v>-21.38578678423467</v>
       </c>
       <c r="G373">
-        <v>318.2052429697663</v>
-      </c>
-      <c r="H373">
         <v>0.4734266402612695</v>
       </c>
     </row>
-    <row r="374" spans="1:8">
+    <row r="374" spans="1:7">
       <c r="A374">
         <v>6511.4154</v>
       </c>
@@ -10113,16 +8991,13 @@
         <v>1343684328.225561</v>
       </c>
       <c r="F374">
-        <v>17808104.12537283</v>
+        <v>386.7876444439406</v>
       </c>
       <c r="G374">
-        <v>142.7272816474987</v>
-      </c>
-      <c r="H374">
         <v>0.03762321127457968</v>
       </c>
     </row>
-    <row r="375" spans="1:8">
+    <row r="375" spans="1:7">
       <c r="A375">
         <v>6520.1681</v>
       </c>
@@ -10139,16 +9014,13 @@
         <v>13888958087.78277</v>
       </c>
       <c r="F375">
-        <v>-4102308.351346817</v>
+        <v>-89.22096244525741</v>
       </c>
       <c r="G375">
-        <v>354.0402472986774</v>
-      </c>
-      <c r="H375">
         <v>0.5410218411436283</v>
       </c>
     </row>
-    <row r="376" spans="1:8">
+    <row r="376" spans="1:7">
       <c r="A376">
         <v>6553.4879</v>
       </c>
@@ -10165,16 +9037,13 @@
         <v>2098704886.396751</v>
       </c>
       <c r="F376">
-        <v>31856808.35245714</v>
+        <v>696.3930044570013</v>
       </c>
       <c r="G376">
-        <v>233.3019545104987</v>
-      </c>
-      <c r="H376">
         <v>0.08993388414018733</v>
       </c>
     </row>
-    <row r="377" spans="1:8">
+    <row r="377" spans="1:7">
       <c r="A377">
         <v>6558.5993</v>
       </c>
@@ -10191,16 +9060,13 @@
         <v>3469584948.927464</v>
       </c>
       <c r="F377">
-        <v>20031807.26950025</v>
+        <v>438.2389878789824</v>
       </c>
       <c r="G377">
-        <v>333.6817578340248</v>
-      </c>
-      <c r="H377">
         <v>0.1949866208909089</v>
       </c>
     </row>
-    <row r="378" spans="1:8">
+    <row r="378" spans="1:7">
       <c r="A378">
         <v>6571.0301</v>
       </c>
@@ -10217,16 +9083,13 @@
         <v>10741197770.21745</v>
       </c>
       <c r="F378">
-        <v>-10289526.79977641</v>
+        <v>-225.5323217488839</v>
       </c>
       <c r="G378">
-        <v>437.9842358258773</v>
-      </c>
-      <c r="H378">
         <v>0.6181121305685302</v>
       </c>
     </row>
-    <row r="379" spans="1:8">
+    <row r="379" spans="1:7">
       <c r="A379">
         <v>6583.028</v>
       </c>
@@ -10243,16 +9106,13 @@
         <v>6781429250.844815</v>
       </c>
       <c r="F379">
-        <v>369953.7463990645</v>
+        <v>8.123679455621252</v>
       </c>
       <c r="G379">
-        <v>241.3630972534624</v>
-      </c>
-      <c r="H379">
         <v>0.191318307504056</v>
       </c>
     </row>
-    <row r="380" spans="1:8">
+    <row r="380" spans="1:7">
       <c r="A380">
         <v>6593.1334</v>
       </c>
@@ -10269,16 +9129,13 @@
         <v>3204548479.936498</v>
       </c>
       <c r="F380">
-        <v>3719109.553093203</v>
+        <v>81.79190856732106</v>
       </c>
       <c r="G380">
-        <v>145.5053018729194</v>
-      </c>
-      <c r="H380">
         <v>0.09913024090132272</v>
       </c>
     </row>
-    <row r="381" spans="1:8">
+    <row r="381" spans="1:7">
       <c r="A381">
         <v>6594.7348</v>
       </c>
@@ -10295,16 +9152,13 @@
         <v>5581282764.728048</v>
       </c>
       <c r="F381">
-        <v>-62014925.11118027</v>
+        <v>-1364.186369033434</v>
       </c>
       <c r="G381">
-        <v>586.4258116898707</v>
-      </c>
-      <c r="H381">
         <v>0.7240466599809766</v>
       </c>
     </row>
-    <row r="382" spans="1:8">
+    <row r="382" spans="1:7">
       <c r="A382">
         <v>6595.6917</v>
       </c>
@@ -10321,16 +9175,13 @@
         <v>9102090185.950563</v>
       </c>
       <c r="F382">
-        <v>-14514621.34765114</v>
+        <v>-319.334738171392</v>
       </c>
       <c r="G382">
-        <v>559.0690713101734</v>
-      </c>
-      <c r="H382">
         <v>0.6616851736999052</v>
       </c>
     </row>
-    <row r="383" spans="1:8">
+    <row r="383" spans="1:7">
       <c r="A383">
         <v>6609.851</v>
       </c>
@@ -10347,16 +9198,13 @@
         <v>6399037030.390108</v>
       </c>
       <c r="F383">
-        <v>3539894.703825359</v>
+        <v>78.04798556124285</v>
       </c>
       <c r="G383">
-        <v>267.5968796027918</v>
-      </c>
-      <c r="H383">
         <v>0.1799982202413752</v>
       </c>
     </row>
-    <row r="384" spans="1:8">
+    <row r="384" spans="1:7">
       <c r="A384">
         <v>6610.9356</v>
       </c>
@@ -10373,16 +9221,13 @@
         <v>12563549280.80945</v>
       </c>
       <c r="F384">
-        <v>-4753925.450748739</v>
+        <v>-104.8323258345118</v>
       </c>
       <c r="G384">
-        <v>435.34043757306</v>
-      </c>
-      <c r="H384">
         <v>0.5805276924162144</v>
       </c>
     </row>
-    <row r="385" spans="1:8">
+    <row r="385" spans="1:7">
       <c r="A385">
         <v>6626.8517</v>
       </c>
@@ -10399,16 +9244,13 @@
         <v>6283692500.929295</v>
       </c>
       <c r="F385">
-        <v>2129965.376865087</v>
+        <v>47.08249187321464</v>
       </c>
       <c r="G385">
-        <v>239.7669510445183</v>
-      </c>
-      <c r="H385">
         <v>0.1557229932865727</v>
       </c>
     </row>
-    <row r="386" spans="1:8">
+    <row r="386" spans="1:7">
       <c r="A386">
         <v>6629.3751</v>
       </c>
@@ -10425,16 +9267,13 @@
         <v>7415337182.884626</v>
       </c>
       <c r="F386">
-        <v>945234.3396702323</v>
+        <v>20.90218285615491</v>
       </c>
       <c r="G386">
-        <v>180.8873104808309</v>
-      </c>
-      <c r="H386">
         <v>0.2606401474733556</v>
       </c>
     </row>
-    <row r="387" spans="1:8">
+    <row r="387" spans="1:7">
       <c r="A387">
         <v>6635.2444</v>
       </c>
@@ -10451,16 +9290,13 @@
         <v>6682589851.132745</v>
       </c>
       <c r="F387">
-        <v>1400603.725012753</v>
+        <v>30.99929327016884</v>
       </c>
       <c r="G387">
-        <v>203.3182170645693</v>
-      </c>
-      <c r="H387">
         <v>0.2482344926376828</v>
       </c>
     </row>
-    <row r="388" spans="1:8">
+    <row r="388" spans="1:7">
       <c r="A388">
         <v>6635.5816</v>
       </c>
@@ -10477,16 +9313,13 @@
         <v>11520420245.40657</v>
       </c>
       <c r="F388">
-        <v>-9016174.033531202</v>
+        <v>-199.5634768069625</v>
       </c>
       <c r="G388">
-        <v>334.328522039182</v>
-      </c>
-      <c r="H388">
         <v>0.5502823150002766</v>
       </c>
     </row>
-    <row r="389" spans="1:8">
+    <row r="389" spans="1:7">
       <c r="A389">
         <v>6635.9392</v>
       </c>
@@ -10503,16 +9336,13 @@
         <v>7098847314.927449</v>
       </c>
       <c r="F389">
-        <v>6347115.569358299</v>
+        <v>140.494178904726</v>
       </c>
       <c r="G389">
-        <v>158.1198337144403</v>
-      </c>
-      <c r="H389">
         <v>0.2795884990021381</v>
       </c>
     </row>
-    <row r="390" spans="1:8">
+    <row r="390" spans="1:7">
       <c r="A390">
         <v>6648.7673</v>
       </c>
@@ -10529,16 +9359,13 @@
         <v>3341946036.579381</v>
       </c>
       <c r="F390">
-        <v>11249100.11776005</v>
+        <v>249.481610584379</v>
       </c>
       <c r="G390">
-        <v>225.449654349734</v>
-      </c>
-      <c r="H390">
         <v>0.09448733767914785</v>
       </c>
     </row>
-    <row r="391" spans="1:8">
+    <row r="391" spans="1:7">
       <c r="A391">
         <v>6655.6901</v>
       </c>
@@ -10555,16 +9382,13 @@
         <v>3003120981.404699</v>
       </c>
       <c r="F391">
-        <v>5602085.67968562</v>
+        <v>124.3719404255167</v>
       </c>
       <c r="G391">
-        <v>189.1807318217273</v>
-      </c>
-      <c r="H391">
         <v>0.09715224720557192</v>
       </c>
     </row>
-    <row r="392" spans="1:8">
+    <row r="392" spans="1:7">
       <c r="A392">
         <v>6669.2601</v>
       </c>
@@ -10581,16 +9405,13 @@
         <v>2075463188.252383</v>
       </c>
       <c r="F392">
-        <v>2184599.835463396</v>
+        <v>48.59920022551702</v>
       </c>
       <c r="G392">
-        <v>188.7958040917876</v>
-      </c>
-      <c r="H392">
         <v>0.05896159583261051</v>
       </c>
     </row>
-    <row r="393" spans="1:8">
+    <row r="393" spans="1:7">
       <c r="A393">
         <v>6689.3386</v>
       </c>
@@ -10607,16 +9428,13 @@
         <v>1189833101.197466</v>
       </c>
       <c r="F393">
-        <v>-22726227.2518142</v>
+        <v>-507.0958186408407</v>
       </c>
       <c r="G393">
-        <v>143.4126634726172</v>
-      </c>
-      <c r="H393">
         <v>0.03871060475871968</v>
       </c>
     </row>
-    <row r="394" spans="1:8">
+    <row r="394" spans="1:7">
       <c r="A394">
         <v>6694.1201</v>
       </c>
@@ -10633,16 +9451,13 @@
         <v>921055694.790382</v>
       </c>
       <c r="F394">
-        <v>54643399.9457631</v>
+        <v>1220.143195879102</v>
       </c>
       <c r="G394">
-        <v>201.5300055623515</v>
-      </c>
-      <c r="H394">
         <v>0.02972880723582605</v>
       </c>
     </row>
-    <row r="395" spans="1:8">
+    <row r="395" spans="1:7">
       <c r="A395">
         <v>6700.9914</v>
       </c>
@@ -10659,16 +9474,13 @@
         <v>2269971915.899831</v>
       </c>
       <c r="F395">
-        <v>27727450.96783087</v>
+        <v>619.7671266906249</v>
       </c>
       <c r="G395">
-        <v>161.0586828614334</v>
-      </c>
-      <c r="H395">
         <v>0.07781847090745908</v>
       </c>
     </row>
-    <row r="396" spans="1:8">
+    <row r="396" spans="1:7">
       <c r="A396">
         <v>6705.4182</v>
       </c>
@@ -10685,16 +9497,13 @@
         <v>11617561877.23574</v>
       </c>
       <c r="F396">
-        <v>-120159.9502042219</v>
+        <v>-2.687604215907824</v>
       </c>
       <c r="G396">
-        <v>281.6666207710454</v>
-      </c>
-      <c r="H396">
         <v>0.3654217584600302</v>
       </c>
     </row>
-    <row r="397" spans="1:8">
+    <row r="397" spans="1:7">
       <c r="A397">
         <v>6706.3319</v>
       </c>
@@ -10711,16 +9520,13 @@
         <v>1849652005.153118</v>
       </c>
       <c r="F397">
-        <v>29654335.74323343</v>
+        <v>663.3654444486879</v>
       </c>
       <c r="G397">
-        <v>210.1036115224865</v>
-      </c>
-      <c r="H397">
         <v>0.06088215699410571</v>
       </c>
     </row>
-    <row r="398" spans="1:8">
+    <row r="398" spans="1:7">
       <c r="A398">
         <v>6706.9535</v>
       </c>
@@ -10737,16 +9543,13 @@
         <v>10147540515.60598</v>
       </c>
       <c r="F398">
-        <v>-2002497.87381213</v>
+        <v>-44.79989532206829</v>
       </c>
       <c r="G398">
-        <v>236.9033910424936</v>
-      </c>
-      <c r="H398">
         <v>0.4098251514038731</v>
       </c>
     </row>
-    <row r="399" spans="1:8">
+    <row r="399" spans="1:7">
       <c r="A399">
         <v>6709.2849</v>
       </c>
@@ -10763,16 +9566,13 @@
         <v>1749073654.666918</v>
       </c>
       <c r="F399">
-        <v>63548672.92859666</v>
+        <v>1422.204798885738</v>
       </c>
       <c r="G399">
-        <v>84.89811937545133</v>
-      </c>
-      <c r="H399">
         <v>0.05989318483075701</v>
       </c>
     </row>
-    <row r="400" spans="1:8">
+    <row r="400" spans="1:7">
       <c r="A400">
         <v>6712.1721</v>
       </c>
@@ -10789,16 +9589,13 @@
         <v>5925674612.860806</v>
       </c>
       <c r="F400">
-        <v>1782974.531947648</v>
+        <v>39.91975580222731</v>
       </c>
       <c r="G400">
-        <v>245.6520027616339</v>
-      </c>
-      <c r="H400">
         <v>0.1579565675627709</v>
       </c>
     </row>
-    <row r="401" spans="1:8">
+    <row r="401" spans="1:7">
       <c r="A401">
         <v>6717.2372</v>
       </c>
@@ -10815,16 +9612,13 @@
         <v>6466847073.592945</v>
       </c>
       <c r="F401">
-        <v>6504217.715117049</v>
+        <v>145.7354848124769</v>
       </c>
       <c r="G401">
-        <v>178.5212873107702</v>
-      </c>
-      <c r="H401">
         <v>0.2345089565646257</v>
       </c>
     </row>
-    <row r="402" spans="1:8">
+    <row r="402" spans="1:7">
       <c r="A402">
         <v>6718.0914</v>
       </c>
@@ -10841,16 +9635,13 @@
         <v>4296664902.39156</v>
       </c>
       <c r="F402">
-        <v>2748436.596176813</v>
+        <v>61.59013381485784</v>
       </c>
       <c r="G402">
-        <v>151.7238001688008</v>
-      </c>
-      <c r="H402">
         <v>0.1414342387134878</v>
       </c>
     </row>
-    <row r="403" spans="1:8">
+    <row r="403" spans="1:7">
       <c r="A403">
         <v>6727.2138</v>
       </c>
@@ -10867,16 +9658,13 @@
         <v>4843420705.339406</v>
       </c>
       <c r="F403">
-        <v>5182053.485208192</v>
+        <v>116.2831306299129</v>
       </c>
       <c r="G403">
-        <v>204.9950168773173</v>
-      </c>
-      <c r="H403">
         <v>0.1609271428297842</v>
       </c>
     </row>
-    <row r="404" spans="1:8">
+    <row r="404" spans="1:7">
       <c r="A404">
         <v>6728.5238</v>
       </c>
@@ -10893,16 +9681,13 @@
         <v>10675475455.60962</v>
       </c>
       <c r="F404">
-        <v>-4997624.731516102</v>
+        <v>-112.1665006439984</v>
       </c>
       <c r="G404">
-        <v>302.9771127943011</v>
-      </c>
-      <c r="H404">
         <v>0.4193147608492456</v>
       </c>
     </row>
-    <row r="405" spans="1:8">
+    <row r="405" spans="1:7">
       <c r="A405">
         <v>6733.9233</v>
       </c>
@@ -10919,16 +9704,13 @@
         <v>2357809041.239516</v>
       </c>
       <c r="F405">
-        <v>22449607.34670368</v>
+        <v>504.2622121985581</v>
       </c>
       <c r="G405">
-        <v>146.9151142995059</v>
-      </c>
-      <c r="H405">
         <v>0.07291182916377414</v>
       </c>
     </row>
-    <row r="406" spans="1:8">
+    <row r="406" spans="1:7">
       <c r="A406">
         <v>6735.01</v>
       </c>
@@ -10945,16 +9727,13 @@
         <v>7035922992.018658</v>
       </c>
       <c r="F406">
-        <v>186800.6687725699</v>
+        <v>4.196587394313599</v>
       </c>
       <c r="G406">
-        <v>209.2089770606141</v>
-      </c>
-      <c r="H406">
         <v>0.2479766591546467</v>
       </c>
     </row>
-    <row r="407" spans="1:8">
+    <row r="407" spans="1:7">
       <c r="A407">
         <v>6739.847</v>
       </c>
@@ -10971,16 +9750,13 @@
         <v>5893112517.811577</v>
       </c>
       <c r="F407">
-        <v>2612029.405499047</v>
+        <v>58.72290850838566</v>
       </c>
       <c r="G407">
-        <v>111.2015072872874</v>
-      </c>
-      <c r="H407">
         <v>0.201050616303423</v>
       </c>
     </row>
-    <row r="408" spans="1:8">
+    <row r="408" spans="1:7">
       <c r="A408">
         <v>6741.3823</v>
       </c>
@@ -10997,16 +9773,13 @@
         <v>4570776091.417056</v>
       </c>
       <c r="F408">
-        <v>1496550.362886542</v>
+        <v>33.6527003618909</v>
       </c>
       <c r="G408">
-        <v>226.7994110915046</v>
-      </c>
-      <c r="H408">
         <v>0.1176259859301999</v>
       </c>
     </row>
-    <row r="409" spans="1:8">
+    <row r="409" spans="1:7">
       <c r="A409">
         <v>6746.9632</v>
       </c>
@@ -11023,16 +9796,13 @@
         <v>2572297064.373842</v>
       </c>
       <c r="F409">
-        <v>26641952.6582154</v>
+        <v>599.5894112623987</v>
       </c>
       <c r="G409">
-        <v>182.1781209483723</v>
-      </c>
-      <c r="H409">
         <v>0.08296620389872322</v>
       </c>
     </row>
-    <row r="410" spans="1:8">
+    <row r="410" spans="1:7">
       <c r="A410">
         <v>6748.8173</v>
       </c>
@@ -11049,16 +9819,13 @@
         <v>1472772815.01032</v>
       </c>
       <c r="F410">
-        <v>43203877.10277835</v>
+        <v>972.5904897783572</v>
       </c>
       <c r="G410">
-        <v>226.5495520036302</v>
-      </c>
-      <c r="H410">
         <v>0.04367003290121174</v>
       </c>
     </row>
-    <row r="411" spans="1:8">
+    <row r="411" spans="1:7">
       <c r="A411">
         <v>6752.0157</v>
       </c>
@@ -11075,16 +9842,13 @@
         <v>12326018475.64012</v>
       </c>
       <c r="F411">
-        <v>-11844508.54755271</v>
+        <v>-266.765974817807</v>
       </c>
       <c r="G411">
-        <v>448.4444291037528</v>
-      </c>
-      <c r="H411">
         <v>0.6303651204672323</v>
       </c>
     </row>
-    <row r="412" spans="1:8">
+    <row r="412" spans="1:7">
       <c r="A412">
         <v>6754.5711</v>
       </c>
@@ -11101,16 +9865,13 @@
         <v>8869183995.713091</v>
       </c>
       <c r="F412">
-        <v>-1729172.915443693</v>
+        <v>-38.95972172552939</v>
       </c>
       <c r="G412">
-        <v>239.6716607563876</v>
-      </c>
-      <c r="H412">
         <v>0.3247967931021069</v>
       </c>
     </row>
-    <row r="413" spans="1:8">
+    <row r="413" spans="1:7">
       <c r="A413">
         <v>6755.3281</v>
       </c>
@@ -11127,16 +9888,13 @@
         <v>1586076246.070092</v>
       </c>
       <c r="F413">
-        <v>-15747787.06813077</v>
+        <v>-354.850561439529</v>
       </c>
       <c r="G413">
-        <v>150.887468741358</v>
-      </c>
-      <c r="H413">
         <v>0.05827670071570912</v>
       </c>
     </row>
-    <row r="414" spans="1:8">
+    <row r="414" spans="1:7">
       <c r="A414">
         <v>6785.5762</v>
       </c>
@@ -11153,16 +9911,13 @@
         <v>3211753353.620571</v>
       </c>
       <c r="F414">
-        <v>-247274.2370536211</v>
+        <v>-5.596869834332347</v>
       </c>
       <c r="G414">
-        <v>212.0680331192632</v>
-      </c>
-      <c r="H414">
         <v>0.1108983669893502</v>
       </c>
     </row>
-    <row r="415" spans="1:8">
+    <row r="415" spans="1:7">
       <c r="A415">
         <v>6788.7335</v>
       </c>
@@ -11179,16 +9934,13 @@
         <v>6707027149.956857</v>
       </c>
       <c r="F415">
-        <v>740634.2348484639</v>
+        <v>16.77150904958236</v>
       </c>
       <c r="G415">
-        <v>207.5533754041792</v>
-      </c>
-      <c r="H415">
         <v>0.2329727416146766</v>
       </c>
     </row>
-    <row r="416" spans="1:8">
+    <row r="416" spans="1:7">
       <c r="A416">
         <v>6795.1341</v>
       </c>
@@ -11205,16 +9957,13 @@
         <v>3807395514.217355</v>
       </c>
       <c r="F416">
-        <v>4885683.158617209</v>
+        <v>110.739571559435</v>
       </c>
       <c r="G416">
-        <v>145.5916979046763</v>
-      </c>
-      <c r="H416">
         <v>0.1215238935587594</v>
       </c>
     </row>
-    <row r="417" spans="1:8">
+    <row r="417" spans="1:7">
       <c r="A417">
         <v>6805.8786</v>
       </c>
@@ -11231,16 +9980,13 @@
         <v>5635938770.166121</v>
       </c>
       <c r="F417">
-        <v>150705.3712828445</v>
+        <v>3.421310130881373</v>
       </c>
       <c r="G417">
-        <v>149.7667556265442</v>
-      </c>
-      <c r="H417">
         <v>0.1960633960544875</v>
       </c>
     </row>
-    <row r="418" spans="1:8">
+    <row r="418" spans="1:7">
       <c r="A418">
         <v>6806.1492</v>
       </c>
@@ -11257,16 +10003,13 @@
         <v>4313395597.11251</v>
       </c>
       <c r="F418">
-        <v>12668182.9316761</v>
+        <v>287.6042834454194</v>
       </c>
       <c r="G418">
-        <v>180.5939073269799</v>
-      </c>
-      <c r="H418">
         <v>0.1405716974125787</v>
       </c>
     </row>
-    <row r="419" spans="1:8">
+    <row r="419" spans="1:7">
       <c r="A419">
         <v>6808.7234</v>
       </c>
@@ -11283,16 +10026,13 @@
         <v>11022729315.73971</v>
       </c>
       <c r="F419">
-        <v>1193487.487687052</v>
+        <v>27.10586436431705</v>
       </c>
       <c r="G419">
-        <v>277.3930404527628</v>
-      </c>
-      <c r="H419">
         <v>0.3378049047013986</v>
       </c>
     </row>
-    <row r="420" spans="1:8">
+    <row r="420" spans="1:7">
       <c r="A420">
         <v>6812.1422</v>
       </c>
@@ -11309,16 +10049,13 @@
         <v>10925497589.57991</v>
       </c>
       <c r="F420">
-        <v>-5119502.304992794</v>
+        <v>-116.3298374234027</v>
       </c>
       <c r="G420">
-        <v>259.6504080836066</v>
-      </c>
-      <c r="H420">
         <v>0.4371920277846642</v>
       </c>
     </row>
-    <row r="421" spans="1:8">
+    <row r="421" spans="1:7">
       <c r="A421">
         <v>6830.4756</v>
       </c>
@@ -11335,16 +10072,13 @@
         <v>11500540566.43847</v>
       </c>
       <c r="F421">
-        <v>-7269538.578155664</v>
+        <v>-165.629463692711</v>
       </c>
       <c r="G421">
-        <v>351.1233776749401</v>
-      </c>
-      <c r="H421">
         <v>0.4822456929342895</v>
       </c>
     </row>
-    <row r="422" spans="1:8">
+    <row r="422" spans="1:7">
       <c r="A422">
         <v>6838.8928</v>
       </c>
@@ -11361,16 +10095,13 @@
         <v>5008989771.091767</v>
       </c>
       <c r="F422">
-        <v>7329714.429775923</v>
+        <v>167.2061948966032</v>
       </c>
       <c r="G422">
-        <v>149.0437688032002</v>
-      </c>
-      <c r="H422">
         <v>0.1666512599697192</v>
       </c>
     </row>
-    <row r="423" spans="1:8">
+    <row r="423" spans="1:7">
       <c r="A423">
         <v>6841.7179</v>
       </c>
@@ -11387,16 +10118,13 @@
         <v>9283108393.589682</v>
       </c>
       <c r="F423">
-        <v>2389180.875809909</v>
+        <v>54.52477917866165</v>
       </c>
       <c r="G423">
-        <v>293.5826203511812</v>
-      </c>
-      <c r="H423">
         <v>0.2916092124074483</v>
       </c>
     </row>
-    <row r="424" spans="1:8">
+    <row r="424" spans="1:7">
       <c r="A424">
         <v>6844.574</v>
       </c>
@@ -11413,16 +10141,13 @@
         <v>9081272908.763472</v>
       </c>
       <c r="F424">
-        <v>-4481801.999388166</v>
+        <v>-102.3243008785526</v>
       </c>
       <c r="G424">
-        <v>275.9401075279162</v>
-      </c>
-      <c r="H424">
         <v>0.3504549068744095</v>
       </c>
     </row>
-    <row r="425" spans="1:8">
+    <row r="425" spans="1:7">
       <c r="A425">
         <v>6845.5444</v>
       </c>
@@ -11439,16 +10164,13 @@
         <v>11555138054.32149</v>
       </c>
       <c r="F425">
-        <v>-9118477.395269874</v>
+        <v>-208.2140628736499</v>
       </c>
       <c r="G425">
-        <v>306.5566569396331</v>
-      </c>
-      <c r="H425">
         <v>0.5089782589158635</v>
       </c>
     </row>
-    <row r="426" spans="1:8">
+    <row r="426" spans="1:7">
       <c r="A426">
         <v>6857.0537</v>
       </c>
@@ -11465,16 +10187,13 @@
         <v>11697158721.71951</v>
       </c>
       <c r="F426">
-        <v>-11068378.07657321</v>
+        <v>-253.1636744667282</v>
       </c>
       <c r="G426">
-        <v>384.7386568464726</v>
-      </c>
-      <c r="H426">
         <v>0.5772602861787268</v>
       </c>
     </row>
-    <row r="427" spans="1:8">
+    <row r="427" spans="1:7">
       <c r="A427">
         <v>6859.1424</v>
       </c>
@@ -11491,16 +10210,13 @@
         <v>6445370256.299841</v>
       </c>
       <c r="F427">
-        <v>-344849.0434468603</v>
+        <v>-7.890024943346847</v>
       </c>
       <c r="G427">
-        <v>161.7158574597413</v>
-      </c>
-      <c r="H427">
         <v>0.2098797067791576</v>
       </c>
     </row>
-    <row r="428" spans="1:8">
+    <row r="428" spans="1:7">
       <c r="A428">
         <v>6860.0421</v>
       </c>
@@ -11517,16 +10233,13 @@
         <v>10984208057.37715</v>
       </c>
       <c r="F428">
-        <v>-5374098.654890883</v>
+        <v>-122.9736618041155</v>
       </c>
       <c r="G428">
-        <v>270.9477890440778</v>
-      </c>
-      <c r="H428">
         <v>0.4488791099090512</v>
       </c>
     </row>
-    <row r="429" spans="1:8">
+    <row r="429" spans="1:7">
       <c r="A429">
         <v>6918.5896</v>
       </c>
@@ -11543,16 +10256,13 @@
         <v>11398016353.14199</v>
       </c>
       <c r="F429">
-        <v>-5708945.619972014</v>
+        <v>-131.750792875188</v>
       </c>
       <c r="G429">
-        <v>320.6526643654252</v>
-      </c>
-      <c r="H429">
         <v>0.4839161704606616</v>
       </c>
     </row>
-    <row r="430" spans="1:8">
+    <row r="430" spans="1:7">
       <c r="A430">
         <v>6947.121</v>
       </c>
@@ -11569,16 +10279,13 @@
         <v>10466949285.08228</v>
       </c>
       <c r="F430">
-        <v>-16426917.3157606</v>
+        <v>-380.6632327990653</v>
       </c>
       <c r="G430">
-        <v>483.3189935356198</v>
-      </c>
-      <c r="H430">
         <v>0.6405441633589763</v>
       </c>
     </row>
-    <row r="431" spans="1:8">
+    <row r="431" spans="1:7">
       <c r="A431">
         <v>6980.7765</v>
       </c>
@@ -11595,16 +10302,13 @@
         <v>11123712111.03624</v>
       </c>
       <c r="F431">
-        <v>-12031421.49191038</v>
+        <v>-280.1564780000023</v>
       </c>
       <c r="G431">
-        <v>480.9888311674453</v>
-      </c>
-      <c r="H431">
         <v>0.6326146648792834</v>
       </c>
     </row>
-    <row r="432" spans="1:8">
+    <row r="432" spans="1:7">
       <c r="A432">
         <v>7001.8146</v>
       </c>
@@ -11621,16 +10325,13 @@
         <v>11267464611.97781</v>
       </c>
       <c r="F432">
-        <v>-5142448.261422534</v>
+        <v>-120.1047993921953</v>
       </c>
       <c r="G432">
-        <v>363.9393555399216</v>
-      </c>
-      <c r="H432">
         <v>0.4551932790065255</v>
       </c>
     </row>
-    <row r="433" spans="1:8">
+    <row r="433" spans="1:7">
       <c r="A433">
         <v>7024.8907</v>
       </c>
@@ -11647,16 +10348,13 @@
         <v>11335290326.72852</v>
       </c>
       <c r="F433">
-        <v>-7696068.337145343</v>
+        <v>-180.3384454854142</v>
       </c>
       <c r="G433">
-        <v>371.2789986395435</v>
-      </c>
-      <c r="H433">
         <v>0.5253879715744005</v>
       </c>
     </row>
-    <row r="434" spans="1:8">
+    <row r="434" spans="1:7">
       <c r="A434">
         <v>7134.9526</v>
       </c>
@@ -11673,16 +10371,13 @@
         <v>10819819332.62493</v>
       </c>
       <c r="F434">
-        <v>-2536512.074496774</v>
+        <v>-60.36813451156894</v>
       </c>
       <c r="G434">
-        <v>298.3238391989815</v>
-      </c>
-      <c r="H434">
         <v>0.389598141218077</v>
       </c>
     </row>
-    <row r="435" spans="1:8">
+    <row r="435" spans="1:7">
       <c r="A435">
         <v>7209.0979</v>
       </c>
@@ -11699,16 +10394,13 @@
         <v>11460216963.4004</v>
       </c>
       <c r="F435">
-        <v>-6685394.032770485</v>
+        <v>-160.7636248690511</v>
       </c>
       <c r="G435">
-        <v>386.7432372292913</v>
-      </c>
-      <c r="H435">
         <v>0.5342976568372431</v>
       </c>
     </row>
-    <row r="436" spans="1:8">
+    <row r="436" spans="1:7">
       <c r="A436">
         <v>7209.3744</v>
       </c>
@@ -11725,16 +10417,13 @@
         <v>6409794568.045595</v>
       </c>
       <c r="F436">
-        <v>-31341712.43832516</v>
+        <v>-753.7033125979553</v>
       </c>
       <c r="G436">
-        <v>569.6966819413633</v>
-      </c>
-      <c r="H436">
         <v>0.6721015119644458</v>
       </c>
     </row>
-    <row r="437" spans="1:8">
+    <row r="437" spans="1:7">
       <c r="A437">
         <v>7290.7468</v>
       </c>
@@ -11751,16 +10440,13 @@
         <v>11017776580.05437</v>
       </c>
       <c r="F437">
-        <v>-6281192.555164498</v>
+        <v>-152.75445074343</v>
       </c>
       <c r="G437">
-        <v>312.5088202088724</v>
-      </c>
-      <c r="H437">
         <v>0.4954870406324505</v>
       </c>
     </row>
-    <row r="438" spans="1:8">
+    <row r="438" spans="1:7">
       <c r="A438">
         <v>7403.7236</v>
       </c>
@@ -11777,16 +10463,13 @@
         <v>10748158308.72359</v>
       </c>
       <c r="F438">
-        <v>-3740366.220730961</v>
+        <v>-92.37277485271434</v>
       </c>
       <c r="G438">
-        <v>255.1003504786072</v>
-      </c>
-      <c r="H438">
         <v>0.3643349965352209</v>
       </c>
     </row>
-    <row r="439" spans="1:8">
+    <row r="439" spans="1:7">
       <c r="A439">
         <v>7420.7108</v>
       </c>
@@ -11803,16 +10486,13 @@
         <v>11466576984.6684</v>
       </c>
       <c r="F439">
-        <v>-4791894.335482059</v>
+        <v>-118.6130617779053</v>
       </c>
       <c r="G439">
-        <v>331.2752944979538</v>
-      </c>
-      <c r="H439">
         <v>0.422099767756754</v>
       </c>
     </row>
-    <row r="440" spans="1:8">
+    <row r="440" spans="1:7">
       <c r="A440">
         <v>7445.0723</v>
       </c>
@@ -11829,16 +10509,13 @@
         <v>8916908999.446501</v>
       </c>
       <c r="F440">
-        <v>-3898809.766295747</v>
+        <v>-96.82347087651684</v>
       </c>
       <c r="G440">
-        <v>265.7637351744941</v>
-      </c>
-      <c r="H440">
         <v>0.3101320876306226</v>
       </c>
     </row>
-    <row r="441" spans="1:8">
+    <row r="441" spans="1:7">
       <c r="A441">
         <v>7449.4449</v>
       </c>
@@ -11855,16 +10532,13 @@
         <v>7265738821.196564</v>
       </c>
       <c r="F441">
-        <v>-723038.6445987809</v>
+        <v>-17.96656903888913</v>
       </c>
       <c r="G441">
-        <v>297.8026173230223</v>
-      </c>
-      <c r="H441">
         <v>0.2797614410380952</v>
       </c>
     </row>
-    <row r="442" spans="1:8">
+    <row r="442" spans="1:7">
       <c r="A442">
         <v>7463.5755</v>
       </c>
@@ -11881,16 +10555,13 @@
         <v>8186886089.921233</v>
       </c>
       <c r="F442">
-        <v>3049782.608079666</v>
+        <v>75.92687677754233</v>
       </c>
       <c r="G442">
-        <v>293.2220547212236</v>
-      </c>
-      <c r="H442">
         <v>0.2439329172833247</v>
       </c>
     </row>
-    <row r="443" spans="1:8">
+    <row r="443" spans="1:7">
       <c r="A443">
         <v>7475.6121</v>
       </c>
@@ -11907,16 +10578,13 @@
         <v>3674645835.497848</v>
       </c>
       <c r="F443">
-        <v>11544543.90291288</v>
+        <v>287.8744759450972</v>
       </c>
       <c r="G443">
-        <v>224.5752912276861</v>
-      </c>
-      <c r="H443">
         <v>0.1416315628643768</v>
       </c>
     </row>
-    <row r="444" spans="1:8">
+    <row r="444" spans="1:7">
       <c r="A444">
         <v>7478.4348</v>
       </c>
@@ -11933,16 +10601,13 @@
         <v>4110653387.928495</v>
       </c>
       <c r="F444">
-        <v>1304245.876438956</v>
+        <v>32.53491689324593</v>
       </c>
       <c r="G444">
-        <v>152.3328571949302</v>
-      </c>
-      <c r="H444">
         <v>0.1474377567648847</v>
       </c>
     </row>
-    <row r="445" spans="1:8">
+    <row r="445" spans="1:7">
       <c r="A445">
         <v>7483.993</v>
       </c>
@@ -11959,16 +10624,13 @@
         <v>3172024463.29296</v>
       </c>
       <c r="F445">
-        <v>18005734.95848579</v>
+        <v>449.4940070407432</v>
       </c>
       <c r="G445">
-        <v>264.3816239301195</v>
-      </c>
-      <c r="H445">
         <v>0.1129858997326331</v>
       </c>
     </row>
-    <row r="446" spans="1:8">
+    <row r="446" spans="1:7">
       <c r="A446">
         <v>7493.7117</v>
       </c>
@@ -11985,16 +10647,13 @@
         <v>11097295206.72467</v>
       </c>
       <c r="F446">
-        <v>-8414010.256969824</v>
+        <v>-210.3196573399862</v>
       </c>
       <c r="G446">
-        <v>380.055767460319</v>
-      </c>
-      <c r="H446">
         <v>0.5009975304793197</v>
       </c>
     </row>
-    <row r="447" spans="1:8">
+    <row r="447" spans="1:7">
       <c r="A447">
         <v>7497.1314</v>
       </c>
@@ -12011,16 +10670,13 @@
         <v>5853123079.947883</v>
       </c>
       <c r="F447">
-        <v>-28131770.25731316</v>
+        <v>-703.5133059657569</v>
       </c>
       <c r="G447">
-        <v>575.8217596913773</v>
-      </c>
-      <c r="H447">
         <v>0.6755947312053567</v>
       </c>
     </row>
-    <row r="448" spans="1:8">
+    <row r="448" spans="1:7">
       <c r="A448">
         <v>7500.5954</v>
       </c>
@@ -12037,16 +10693,13 @@
         <v>5250288921.769056</v>
       </c>
       <c r="F448">
-        <v>4754515.597482095</v>
+        <v>118.9547021332457</v>
       </c>
       <c r="G448">
-        <v>207.8396045337686</v>
-      </c>
-      <c r="H448">
         <v>0.164264007736417</v>
       </c>
     </row>
-    <row r="449" spans="1:8">
+    <row r="449" spans="1:7">
       <c r="A449">
         <v>7508.0813</v>
       </c>
@@ -12063,16 +10716,13 @@
         <v>4239965114.322686</v>
       </c>
       <c r="F449">
-        <v>13393157.529569</v>
+        <v>335.4220649869272</v>
       </c>
       <c r="G449">
-        <v>267.5263343763079</v>
-      </c>
-      <c r="H449">
         <v>0.1576106777017845</v>
       </c>
     </row>
-    <row r="450" spans="1:8">
+    <row r="450" spans="1:7">
       <c r="A450">
         <v>7509.3335</v>
       </c>
@@ -12089,16 +10739,13 @@
         <v>10945928959.82665</v>
       </c>
       <c r="F450">
-        <v>-8883305.050764252</v>
+        <v>-222.5131944219128</v>
       </c>
       <c r="G450">
-        <v>347.3270143878042</v>
-      </c>
-      <c r="H450">
         <v>0.4534800014335328</v>
       </c>
     </row>
-    <row r="451" spans="1:8">
+    <row r="451" spans="1:7">
       <c r="A451">
         <v>7513.0887</v>
       </c>
@@ -12115,16 +10762,13 @@
         <v>5279304336.256651</v>
       </c>
       <c r="F451">
-        <v>-25364803.20749626</v>
+        <v>-635.6677316914067</v>
       </c>
       <c r="G451">
-        <v>590.5598290749705</v>
-      </c>
-      <c r="H451">
         <v>0.7011375644231126</v>
       </c>
     </row>
-    <row r="452" spans="1:8">
+    <row r="452" spans="1:7">
       <c r="A452">
         <v>7533.2189</v>
       </c>
@@ -12141,16 +10785,13 @@
         <v>9909655380.49449</v>
       </c>
       <c r="F452">
-        <v>-14348686.88454142</v>
+        <v>-360.5560016395859</v>
       </c>
       <c r="G452">
-        <v>473.573156164945</v>
-      </c>
-      <c r="H452">
         <v>0.5828285510477349</v>
       </c>
     </row>
-    <row r="453" spans="1:8">
+    <row r="453" spans="1:7">
       <c r="A453">
         <v>7543.9894</v>
       </c>
@@ -12167,16 +10808,13 @@
         <v>2286064314.158804</v>
       </c>
       <c r="F453">
-        <v>17837008.30877105</v>
+        <v>448.8515710623177</v>
       </c>
       <c r="G453">
-        <v>254.3311806618962</v>
-      </c>
-      <c r="H453">
         <v>0.09079385459493095</v>
       </c>
     </row>
-    <row r="454" spans="1:8">
+    <row r="454" spans="1:7">
       <c r="A454">
         <v>7549.975</v>
       </c>
@@ -12193,16 +10831,13 @@
         <v>4563876809.994122</v>
       </c>
       <c r="F454">
-        <v>4533049.852747462</v>
+        <v>114.1604550753276</v>
       </c>
       <c r="G454">
-        <v>266.0418701200632</v>
-      </c>
-      <c r="H454">
         <v>0.1724918826570881</v>
       </c>
     </row>
-    <row r="455" spans="1:8">
+    <row r="455" spans="1:7">
       <c r="A455">
         <v>7565.0931</v>
       </c>
@@ -12219,16 +10854,13 @@
         <v>4114797871.081561</v>
       </c>
       <c r="F455">
-        <v>-2092482.607439377</v>
+        <v>-52.80265058259383</v>
       </c>
       <c r="G455">
-        <v>202.1047878190345</v>
-      </c>
-      <c r="H455">
         <v>0.1354957736513572</v>
       </c>
     </row>
-    <row r="456" spans="1:8">
+    <row r="456" spans="1:7">
       <c r="A456">
         <v>7570.9838</v>
       </c>
@@ -12245,16 +10877,13 @@
         <v>10838088226.61301</v>
       </c>
       <c r="F456">
-        <v>-10431137.36630133</v>
+        <v>-263.4291735803337</v>
       </c>
       <c r="G456">
-        <v>407.8548308927116</v>
-      </c>
-      <c r="H456">
         <v>0.5381991165591049</v>
       </c>
     </row>
-    <row r="457" spans="1:8">
+    <row r="457" spans="1:7">
       <c r="A457">
         <v>7588.1072</v>
       </c>
@@ -12271,16 +10900,13 @@
         <v>7236817728.679172</v>
       </c>
       <c r="F457">
-        <v>-20900110.94964657</v>
+        <v>-529.0078877813705</v>
       </c>
       <c r="G457">
-        <v>553.1148020513306</v>
-      </c>
-      <c r="H457">
         <v>0.6394301068031066</v>
       </c>
     </row>
-    <row r="458" spans="1:8">
+    <row r="458" spans="1:7">
       <c r="A458">
         <v>7590.3944</v>
       </c>
@@ -12297,16 +10923,13 @@
         <v>5354467001.628204</v>
       </c>
       <c r="F458">
-        <v>-206971.5823852211</v>
+        <v>-5.240282810964004</v>
       </c>
       <c r="G458">
-        <v>252.7762893361213</v>
-      </c>
-      <c r="H458">
         <v>0.2093770910788972</v>
       </c>
     </row>
-    <row r="459" spans="1:8">
+    <row r="459" spans="1:7">
       <c r="A459">
         <v>7620.0869</v>
       </c>
@@ -12323,16 +10946,13 @@
         <v>2929229253.075706</v>
       </c>
       <c r="F459">
-        <v>7025126.649697298</v>
+        <v>178.5639310929469</v>
       </c>
       <c r="G459">
-        <v>247.8570795854087</v>
-      </c>
-      <c r="H459">
         <v>0.1427889339645912</v>
       </c>
     </row>
-    <row r="460" spans="1:8">
+    <row r="460" spans="1:7">
       <c r="A460">
         <v>7712.4865</v>
       </c>
@@ -12349,16 +10969,13 @@
         <v>11129793591.47611</v>
       </c>
       <c r="F460">
-        <v>-8565384.619439717</v>
+        <v>-220.3541054344424</v>
       </c>
       <c r="G460">
-        <v>388.7105124995614</v>
-      </c>
-      <c r="H460">
         <v>0.4914615824476677</v>
       </c>
     </row>
-    <row r="461" spans="1:8">
+    <row r="461" spans="1:7">
       <c r="A461">
         <v>7721.173</v>
       </c>
@@ -12375,16 +10992,13 @@
         <v>6054903719.335782</v>
       </c>
       <c r="F461">
-        <v>3859324.550525118</v>
+        <v>99.39722233893306</v>
       </c>
       <c r="G461">
-        <v>252.3775826414882</v>
-      </c>
-      <c r="H461">
         <v>0.2245503697318828</v>
       </c>
     </row>
-    <row r="462" spans="1:8">
+    <row r="462" spans="1:7">
       <c r="A462">
         <v>7725.3335</v>
       </c>
@@ -12401,16 +11015,13 @@
         <v>11674325695.3803</v>
       </c>
       <c r="F462">
-        <v>-1470143.36189985</v>
+        <v>-37.88407500790911</v>
       </c>
       <c r="G462">
-        <v>322.0932017271632</v>
-      </c>
-      <c r="H462">
         <v>0.3632078291658772</v>
       </c>
     </row>
-    <row r="463" spans="1:8">
+    <row r="463" spans="1:7">
       <c r="A463">
         <v>7739.7955</v>
       </c>
@@ -12427,16 +11038,13 @@
         <v>746917741.67029</v>
       </c>
       <c r="F463">
-        <v>83022753.6611363</v>
+        <v>2143.414441332065</v>
       </c>
       <c r="G463">
-        <v>162.682376215862</v>
-      </c>
-      <c r="H463">
         <v>0.02653174997208652</v>
       </c>
     </row>
-    <row r="464" spans="1:8">
+    <row r="464" spans="1:7">
       <c r="A464">
         <v>7747.6455</v>
       </c>
@@ -12453,16 +11061,13 @@
         <v>4707608786.898621</v>
       </c>
       <c r="F464">
-        <v>2175223.226688494</v>
+        <v>56.21513702441381</v>
       </c>
       <c r="G464">
-        <v>278.6015051092205</v>
-      </c>
-      <c r="H464">
         <v>0.1736953929844248</v>
       </c>
     </row>
-    <row r="465" spans="1:8">
+    <row r="465" spans="1:7">
       <c r="A465">
         <v>7748.7262</v>
       </c>
@@ -12479,16 +11084,13 @@
         <v>4015161257.194639</v>
       </c>
       <c r="F465">
-        <v>10378232.68453361</v>
+        <v>268.2460880464317</v>
       </c>
       <c r="G465">
-        <v>263.0869463685414</v>
-      </c>
-      <c r="H465">
         <v>0.1485678667965966</v>
       </c>
     </row>
-    <row r="466" spans="1:8">
+    <row r="466" spans="1:7">
       <c r="A466">
         <v>7753.2422</v>
       </c>
@@ -12505,16 +11107,13 @@
         <v>8554097016.054304</v>
       </c>
       <c r="F466">
-        <v>-2614382.829637098</v>
+        <v>-67.61332964642713</v>
       </c>
       <c r="G466">
-        <v>340.2671505125766</v>
-      </c>
-      <c r="H466">
         <v>0.3492343510070526</v>
       </c>
     </row>
-    <row r="467" spans="1:8">
+    <row r="467" spans="1:7">
       <c r="A467">
         <v>7782.6983</v>
       </c>
@@ -12531,16 +11130,13 @@
         <v>7353186641.309758</v>
       </c>
       <c r="F467">
-        <v>-23019501.85963562</v>
+        <v>-597.5939690476115</v>
       </c>
       <c r="G467">
-        <v>546.9893267614135</v>
-      </c>
-      <c r="H467">
         <v>0.6289229212182752</v>
       </c>
     </row>
-    <row r="468" spans="1:8">
+    <row r="468" spans="1:7">
       <c r="A468">
         <v>7804.6198</v>
       </c>
@@ -12557,16 +11153,13 @@
         <v>3624115906.463933</v>
       </c>
       <c r="F468">
-        <v>13816884.57671598</v>
+        <v>359.700889616975</v>
       </c>
       <c r="G468">
-        <v>230.4730780011295</v>
-      </c>
-      <c r="H468">
         <v>0.1266210543654368</v>
       </c>
     </row>
-    <row r="469" spans="1:8">
+    <row r="469" spans="1:7">
       <c r="A469">
         <v>7810.0575</v>
       </c>
@@ -12583,16 +11176,13 @@
         <v>9556764967.012693</v>
       </c>
       <c r="F469">
-        <v>-2595228.451017265</v>
+        <v>-67.60978773332326</v>
       </c>
       <c r="G469">
-        <v>310.9220271046865</v>
-      </c>
-      <c r="H469">
         <v>0.4305987197497483</v>
       </c>
     </row>
-    <row r="470" spans="1:8">
+    <row r="470" spans="1:7">
       <c r="A470">
         <v>7812.9639</v>
       </c>
@@ -12609,16 +11199,13 @@
         <v>3874967759.080205</v>
       </c>
       <c r="F470">
-        <v>5549158.563754943</v>
+        <v>144.6180882857291</v>
       </c>
       <c r="G470">
-        <v>253.2496307526172</v>
-      </c>
-      <c r="H470">
         <v>0.1694816346557407</v>
       </c>
     </row>
-    <row r="471" spans="1:8">
+    <row r="471" spans="1:7">
       <c r="A471">
         <v>7822.9553</v>
       </c>
@@ -12635,16 +11222,13 @@
         <v>1687678936.339648</v>
       </c>
       <c r="F471">
-        <v>19491802.51046773</v>
+        <v>508.6306484070187</v>
       </c>
       <c r="G471">
-        <v>260.5906126537344</v>
-      </c>
-      <c r="H471">
         <v>0.04853020969302713</v>
       </c>
     </row>
-    <row r="472" spans="1:8">
+    <row r="472" spans="1:7">
       <c r="A472">
         <v>7834.3517</v>
       </c>
@@ -12661,16 +11245,13 @@
         <v>6977380148.974051</v>
       </c>
       <c r="F472">
-        <v>-22756674.38876458</v>
+        <v>-594.6918367197388</v>
       </c>
       <c r="G472">
-        <v>566.3427617277607</v>
-      </c>
-      <c r="H472">
         <v>0.638909229696091</v>
       </c>
     </row>
-    <row r="473" spans="1:8">
+    <row r="473" spans="1:7">
       <c r="A473">
         <v>7846.7172</v>
       </c>
@@ -12687,16 +11268,13 @@
         <v>3058126861.048535</v>
       </c>
       <c r="F473">
-        <v>5283553.176603395</v>
+        <v>138.2909066898623</v>
       </c>
       <c r="G473">
-        <v>168.1068377486629</v>
-      </c>
-      <c r="H473">
         <v>0.1034034249971277</v>
       </c>
     </row>
-    <row r="474" spans="1:8">
+    <row r="474" spans="1:7">
       <c r="A474">
         <v>7857.56</v>
       </c>
@@ -12713,16 +11291,13 @@
         <v>5557685890.200953</v>
       </c>
       <c r="F474">
-        <v>-3119533.451478652</v>
+        <v>-81.76303394550821</v>
       </c>
       <c r="G474">
-        <v>240.3662823221559</v>
-      </c>
-      <c r="H474">
         <v>0.2172608462926084</v>
       </c>
     </row>
-    <row r="475" spans="1:8">
+    <row r="475" spans="1:7">
       <c r="A475">
         <v>7915.0437</v>
       </c>
@@ -12739,16 +11314,13 @@
         <v>13048368414.91627</v>
       </c>
       <c r="F475">
-        <v>-5482678.654874719</v>
+        <v>-144.7524277090239</v>
       </c>
       <c r="G475">
-        <v>310.5855443248964</v>
-      </c>
-      <c r="H475">
         <v>0.3998781385079311</v>
       </c>
     </row>
-    <row r="476" spans="1:8">
+    <row r="476" spans="1:7">
       <c r="A476">
         <v>7943.2736</v>
       </c>
@@ -12765,16 +11337,13 @@
         <v>11208586428.15492</v>
       </c>
       <c r="F476">
-        <v>-377379.5821357472</v>
+        <v>-9.999025532344788</v>
       </c>
       <c r="G476">
-        <v>317.0300777387063</v>
-      </c>
-      <c r="H476">
         <v>0.3530895527692454</v>
       </c>
     </row>
-    <row r="477" spans="1:8">
+    <row r="477" spans="1:7">
       <c r="A477">
         <v>7948.0326</v>
       </c>
@@ -12791,16 +11360,13 @@
         <v>6195298998.834575</v>
       </c>
       <c r="F477">
-        <v>-27320886.8158157</v>
+        <v>-724.3268632962911</v>
       </c>
       <c r="G477">
-        <v>595.9614252734825</v>
-      </c>
-      <c r="H477">
         <v>0.6463170469558642</v>
       </c>
     </row>
-    <row r="478" spans="1:8">
+    <row r="478" spans="1:7">
       <c r="A478">
         <v>7957.1226</v>
       </c>
@@ -12817,16 +11383,13 @@
         <v>2393040702.621309</v>
       </c>
       <c r="F478">
-        <v>38979025.12084102</v>
+        <v>1034.586326903536</v>
       </c>
       <c r="G478">
-        <v>286.3375110689166</v>
-      </c>
-      <c r="H478">
         <v>0.07079499978164883</v>
       </c>
     </row>
-    <row r="479" spans="1:8">
+    <row r="479" spans="1:7">
       <c r="A479">
         <v>7957.8805</v>
       </c>
@@ -12843,12 +11406,9 @@
         <v>5120584143.456322</v>
       </c>
       <c r="F479">
-        <v>7587727.133988104</v>
+        <v>201.4135972541021</v>
       </c>
       <c r="G479">
-        <v>256.1723205549114</v>
-      </c>
-      <c r="H479">
         <v>0.1955442885894566</v>
       </c>
     </row>
